--- a/research/traditional_assets/database/data/canada/canada_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ31"/>
+  <dimension ref="A1:AQ34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08740000000000001</v>
+        <v>0.1065</v>
       </c>
       <c r="E2">
-        <v>0.06280000000000001</v>
+        <v>0.11465</v>
       </c>
       <c r="F2">
-        <v>0.1873</v>
+        <v>0.14275</v>
       </c>
       <c r="G2">
-        <v>0.1223563850786638</v>
+        <v>0.1074140875298778</v>
       </c>
       <c r="H2">
-        <v>0.1132695231455427</v>
+        <v>0.09753359105565274</v>
       </c>
       <c r="I2">
-        <v>0.09167690926292238</v>
+        <v>0.1294133875314078</v>
       </c>
       <c r="J2">
-        <v>0.08135130175132317</v>
+        <v>0.1157705789621059</v>
       </c>
       <c r="K2">
-        <v>1473.402</v>
+        <v>2256.649</v>
       </c>
       <c r="L2">
-        <v>0.3094056328800262</v>
+        <v>0.4212987016866331</v>
       </c>
       <c r="M2">
-        <v>984.501</v>
+        <v>1275.7028</v>
       </c>
       <c r="N2">
-        <v>0.04809120369058702</v>
+        <v>0.06554761710245949</v>
       </c>
       <c r="O2">
-        <v>0.6681822068926199</v>
+        <v>0.5653084728728305</v>
       </c>
       <c r="P2">
-        <v>496.797</v>
+        <v>542.6608</v>
       </c>
       <c r="Q2">
-        <v>0.02426769065737116</v>
+        <v>0.02788276574678236</v>
       </c>
       <c r="R2">
-        <v>0.3371768193609076</v>
+        <v>0.2404719564274285</v>
       </c>
       <c r="S2">
-        <v>487.704</v>
+        <v>733.042</v>
       </c>
       <c r="T2">
-        <v>0.4953819244470041</v>
+        <v>0.5746181634154914</v>
       </c>
       <c r="U2">
-        <v>1362.59</v>
+        <v>1146.845</v>
       </c>
       <c r="V2">
-        <v>0.06656020993046932</v>
+        <v>0.05892670058878145</v>
       </c>
       <c r="W2">
-        <v>0.160884577441631</v>
+        <v>0.08451653887303852</v>
       </c>
       <c r="X2">
-        <v>0.02578635796633163</v>
+        <v>0.05370207315633253</v>
       </c>
       <c r="Y2">
-        <v>0.1350982194752994</v>
+        <v>0.03081446571670599</v>
       </c>
       <c r="Z2">
-        <v>0.07934069144973259</v>
+        <v>0.07980364085136087</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02372302694416927</v>
+        <v>0.04822841486309205</v>
       </c>
       <c r="AC2">
-        <v>-0.02312624138409212</v>
+        <v>-0.04822841486309205</v>
       </c>
       <c r="AD2">
-        <v>56665.918</v>
+        <v>58474.598</v>
       </c>
       <c r="AE2">
-        <v>0.684455067965653</v>
+        <v>0.2585373975233404</v>
       </c>
       <c r="AF2">
-        <v>56666.60245506796</v>
+        <v>58474.85653739752</v>
       </c>
       <c r="AG2">
-        <v>55304.01245506797</v>
+        <v>57328.01153739752</v>
       </c>
       <c r="AH2">
-        <v>0.734611965644306</v>
+        <v>0.7502828131680134</v>
       </c>
       <c r="AI2">
-        <v>0.8248284987418383</v>
+        <v>0.8296403936188463</v>
       </c>
       <c r="AJ2">
-        <v>0.7298397789690962</v>
+        <v>0.7465533431025644</v>
       </c>
       <c r="AK2">
-        <v>0.8212839143200165</v>
+        <v>0.8268225506441714</v>
       </c>
       <c r="AL2">
-        <v>79.953</v>
+        <v>368.354</v>
       </c>
       <c r="AM2">
-        <v>78.265</v>
+        <v>365.854</v>
       </c>
       <c r="AN2">
-        <v>113.945317589904</v>
+        <v>75.3153322333806</v>
       </c>
       <c r="AO2">
-        <v>5.456443160356709</v>
+        <v>1.881521579784664</v>
       </c>
       <c r="AP2">
-        <v>111.2067621173759</v>
+        <v>73.83852788895054</v>
       </c>
       <c r="AQ2">
-        <v>5.574126365552929</v>
+        <v>1.894378631913277</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Propel Holdings Inc. (TSX:PRL)</t>
+          <t>Montfort Capital Corp. (TSXV:MONT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,100 +725,115 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.1379080252479711</v>
+        <v>0.6876971608832808</v>
       </c>
       <c r="H3">
-        <v>0.1352569882777277</v>
+        <v>0.6876971608832808</v>
       </c>
       <c r="I3">
-        <v>0.151487826871055</v>
+        <v>0.6671924290220821</v>
       </c>
       <c r="J3">
-        <v>0.1066025448351869</v>
+        <v>0.6664427746074505</v>
       </c>
       <c r="K3">
-        <v>7.65</v>
+        <v>-0.554</v>
       </c>
       <c r="L3">
-        <v>0.06898106402164111</v>
+        <v>-0.08738170347003156</v>
       </c>
       <c r="M3">
-        <v>7.37</v>
+        <v>0.261</v>
       </c>
       <c r="N3">
-        <v>0.01993508249932378</v>
+        <v>0.008365384615384617</v>
       </c>
       <c r="O3">
-        <v>0.9633986928104575</v>
+        <v>-0.4711191335740072</v>
       </c>
       <c r="P3">
-        <v>7.37</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.01993508249932378</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.9633986928104575</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.261</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>3.41</v>
+        <v>3.97</v>
       </c>
       <c r="V3">
-        <v>0.009223694887746823</v>
+        <v>0.1272435897435898</v>
+      </c>
+      <c r="W3">
+        <v>-0.277</v>
       </c>
       <c r="X3">
-        <v>0.02387399150180006</v>
+        <v>0.0831181179510555</v>
+      </c>
+      <c r="Y3">
+        <v>-0.3601181179510555</v>
+      </c>
+      <c r="Z3">
+        <v>3.427027027027028</v>
+      </c>
+      <c r="AA3">
+        <v>2.283917400546615</v>
       </c>
       <c r="AB3">
-        <v>0.02372302694416927</v>
+        <v>0.05060649535046997</v>
+      </c>
+      <c r="AC3">
+        <v>2.233310905196145</v>
       </c>
       <c r="AD3">
-        <v>60</v>
+        <v>155.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>60</v>
+        <v>155.9</v>
       </c>
       <c r="AG3">
-        <v>56.59</v>
+        <v>151.93</v>
       </c>
       <c r="AH3">
-        <v>0.1396323016057715</v>
+        <v>0.8332442544094067</v>
       </c>
       <c r="AI3">
-        <v>0.6904487917146145</v>
+        <v>0.8261791202967674</v>
       </c>
       <c r="AJ3">
-        <v>0.1327500058645523</v>
+        <v>0.8296292251406105</v>
       </c>
       <c r="AK3">
-        <v>0.6778057252365552</v>
+        <v>0.8224435662859307</v>
       </c>
       <c r="AL3">
-        <v>5.73</v>
+        <v>1.98</v>
       </c>
       <c r="AM3">
-        <v>5.73</v>
+        <v>1.98</v>
       </c>
       <c r="AN3">
-        <v>3.550295857988166</v>
+        <v>35.75688073394495</v>
       </c>
       <c r="AO3">
-        <v>2.931937172774869</v>
+        <v>2.136363636363637</v>
       </c>
       <c r="AP3">
-        <v>3.348520710059172</v>
+        <v>34.84633027522936</v>
       </c>
       <c r="AQ3">
-        <v>2.931937172774869</v>
+        <v>2.136363636363637</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prophecy DeFi Inc. (CNSX:PDFI)</t>
+          <t>Propel Holdings Inc. (TSX:PRL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,100 +853,115 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.09109489051094891</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.07931873479318735</v>
       </c>
       <c r="I4">
-        <v>-3.755605381165919</v>
+        <v>0.09391727493917275</v>
       </c>
       <c r="J4">
-        <v>-3.755605381165919</v>
+        <v>0.0754983609572308</v>
       </c>
       <c r="K4">
-        <v>-3.29</v>
+        <v>7.87</v>
       </c>
       <c r="L4">
-        <v>-3.688340807174888</v>
+        <v>0.03829683698296837</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>10.2</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.05399682371625198</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.296060991105464</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>10.2</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.05399682371625198</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.296060991105464</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>2.05</v>
+        <v>6.33</v>
       </c>
       <c r="V4">
-        <v>0.04680365296803653</v>
+        <v>0.03350979354155638</v>
       </c>
       <c r="W4">
-        <v>137.0833333333333</v>
+        <v>0.2925650557620818</v>
       </c>
       <c r="X4">
-        <v>0.02299258869117853</v>
+        <v>0.05253419458295822</v>
       </c>
       <c r="Y4">
-        <v>137.0603407446422</v>
+        <v>0.2400308611791236</v>
       </c>
       <c r="Z4">
-        <v>-27.875</v>
+        <v>2.461372619475386</v>
       </c>
       <c r="AA4">
-        <v>104.6875</v>
+        <v>0.1858295984753974</v>
       </c>
       <c r="AB4">
-        <v>0.02341032393761801</v>
+        <v>0.04817972807776595</v>
       </c>
       <c r="AC4">
-        <v>104.6640896760624</v>
+        <v>0.1376498703976314</v>
       </c>
       <c r="AD4">
-        <v>0.408</v>
+        <v>118.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.408</v>
+        <v>118.7</v>
       </c>
       <c r="AG4">
-        <v>-1.642</v>
+        <v>112.37</v>
       </c>
       <c r="AH4">
-        <v>0.009229098805646036</v>
+        <v>0.385890767230169</v>
       </c>
       <c r="AI4">
-        <v>0.01441288681644765</v>
+        <v>0.6019269776876268</v>
       </c>
       <c r="AJ4">
-        <v>-0.0389487167322928</v>
+        <v>0.3729876854648654</v>
       </c>
       <c r="AK4">
-        <v>-0.06253332317769822</v>
+        <v>0.5887253104207052</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>7.33</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>7.33</v>
+      </c>
+      <c r="AN4">
+        <v>6.087179487179488</v>
+      </c>
+      <c r="AO4">
+        <v>2.633015006821283</v>
+      </c>
+      <c r="AP4">
+        <v>5.762564102564103</v>
+      </c>
+      <c r="AQ4">
+        <v>2.633015006821283</v>
       </c>
     </row>
     <row r="5">
@@ -942,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Midpoint Holdings Ltd. (TSXV:MPT)</t>
+          <t>TMX Group Limited (TSX:X)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -951,112 +981,124 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0771</v>
+        <v>0.169</v>
+      </c>
+      <c r="E5">
+        <v>0.193</v>
+      </c>
+      <c r="F5">
+        <v>0.0255</v>
       </c>
       <c r="G5">
-        <v>-2.009174311926606</v>
+        <v>0.4629343979675166</v>
       </c>
       <c r="H5">
-        <v>-2.036697247706422</v>
+        <v>0.4513202068777788</v>
       </c>
       <c r="I5">
-        <v>-2.196697895845181</v>
+        <v>0.6248979221486255</v>
       </c>
       <c r="J5">
-        <v>-2.196697895845181</v>
+        <v>0.5215592698588835</v>
       </c>
       <c r="K5">
-        <v>-0.723</v>
+        <v>384.9</v>
       </c>
       <c r="L5">
-        <v>-2.211009174311926</v>
+        <v>0.3492423555031304</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>199.8</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.03583663659354654</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>0.519095869056898</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>132.6</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.02378347353505641</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>0.3445050662509743</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>67.20000000000002</v>
+      </c>
+      <c r="T5">
+        <v>0.3363363363363364</v>
       </c>
       <c r="U5">
-        <v>2.14</v>
+        <v>292.1</v>
       </c>
       <c r="V5">
-        <v>0.2018867924528302</v>
+        <v>0.05239179954441914</v>
       </c>
       <c r="W5">
-        <v>-1.558189655172414</v>
+        <v>0.1324045407636739</v>
       </c>
       <c r="X5">
-        <v>0.02295881336317731</v>
+        <v>0.04915740525594396</v>
       </c>
       <c r="Y5">
-        <v>-1.581148468535591</v>
+        <v>0.08324713550772993</v>
       </c>
       <c r="Z5">
-        <v>-1.623643101220208</v>
+        <v>0.3080642907058001</v>
       </c>
       <c r="AA5">
-        <v>3.566653384053974</v>
+        <v>0.1606737865301119</v>
       </c>
       <c r="AB5">
-        <v>0.02311468122053505</v>
+        <v>0.04741369945277707</v>
       </c>
       <c r="AC5">
-        <v>3.543538702833439</v>
+        <v>0.1132600870773349</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>814.3</v>
       </c>
       <c r="AE5">
-        <v>0.0366010597068706</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.0366010597068706</v>
+        <v>814.3</v>
       </c>
       <c r="AG5">
-        <v>-2.103398940293129</v>
+        <v>522.1999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.003441048461008961</v>
+        <v>0.1274414673844998</v>
       </c>
       <c r="AI5">
-        <v>0.01721106059822789</v>
+        <v>0.2139066932856993</v>
       </c>
       <c r="AJ5">
-        <v>-0.2475576910710806</v>
+        <v>0.08564165641656415</v>
       </c>
       <c r="AK5">
-        <v>156.982484754534</v>
+        <v>0.1485759808803027</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>330.7</v>
       </c>
       <c r="AM5">
-        <v>-0.001</v>
+        <v>329.53</v>
       </c>
       <c r="AN5">
-        <v>-0</v>
+        <v>1.071024595554386</v>
+      </c>
+      <c r="AO5">
+        <v>2.082552162080435</v>
       </c>
       <c r="AP5">
-        <v>3.009154421020214</v>
+        <v>0.6868341444166776</v>
       </c>
       <c r="AQ5">
-        <v>751</v>
+        <v>2.089946287136224</v>
       </c>
     </row>
     <row r="6">
@@ -1067,7 +1109,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TIMIA Capital Corp. (TSXV:TCA)</t>
+          <t>Dominion Lending Centres Inc. (TSX:DLCG)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,112 +1118,118 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.625</v>
+        <v>0.0553</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.6109154929577466</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.6109154929577466</v>
       </c>
       <c r="I6">
-        <v>0.6517412935323385</v>
+        <v>0.4348591549295775</v>
       </c>
       <c r="J6">
-        <v>0.6383230904302021</v>
+        <v>0.2200312989045383</v>
       </c>
       <c r="K6">
-        <v>-0.773</v>
+        <v>5.58</v>
       </c>
       <c r="L6">
-        <v>-0.1922885572139304</v>
+        <v>0.09823943661971832</v>
       </c>
       <c r="M6">
-        <v>0.207</v>
+        <v>7.68</v>
       </c>
       <c r="N6">
-        <v>0.01269938650306748</v>
+        <v>0.06719160104986877</v>
       </c>
       <c r="O6">
-        <v>-0.2677878395860284</v>
+        <v>1.376344086021505</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>2.12</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.01854768153980752</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>0.3799283154121864</v>
       </c>
       <c r="S6">
-        <v>0.207</v>
+        <v>5.56</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>0.7239583333333333</v>
       </c>
       <c r="U6">
-        <v>7.06</v>
+        <v>12.6</v>
       </c>
       <c r="V6">
-        <v>0.4331288343558282</v>
+        <v>0.1102362204724409</v>
       </c>
       <c r="W6">
-        <v>-0.4068421052631579</v>
+        <v>0.1430769230769231</v>
       </c>
       <c r="X6">
-        <v>0.02459670602369775</v>
+        <v>0.05484198371379341</v>
       </c>
       <c r="Y6">
-        <v>-0.4314388112868557</v>
+        <v>0.08823493936312966</v>
       </c>
       <c r="Z6">
-        <v>1.063492063492063</v>
+        <v>0.5916666666666666</v>
       </c>
       <c r="AA6">
-        <v>0.6788515406162464</v>
+        <v>0.1301851851851852</v>
       </c>
       <c r="AB6">
-        <v>0.02369329154352125</v>
+        <v>0.04819175039538243</v>
       </c>
       <c r="AC6">
-        <v>0.6551582490727251</v>
+        <v>0.08199343478980273</v>
       </c>
       <c r="AD6">
-        <v>4.69</v>
+        <v>109.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>4.69</v>
+        <v>109.5</v>
       </c>
       <c r="AG6">
-        <v>-2.369999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.2234397332062887</v>
+        <v>0.4892761394101877</v>
       </c>
       <c r="AI6">
-        <v>0.1314093583636873</v>
+        <v>0.8099112426035504</v>
       </c>
       <c r="AJ6">
-        <v>-0.1701363962670495</v>
+        <v>0.4588068181818182</v>
       </c>
       <c r="AK6">
-        <v>-0.08278030038421233</v>
+        <v>0.7903752039151712</v>
       </c>
       <c r="AL6">
-        <v>0.746</v>
+        <v>24.9</v>
       </c>
       <c r="AM6">
-        <v>0.746</v>
+        <v>24.9</v>
+      </c>
+      <c r="AN6">
+        <v>3.711864406779661</v>
       </c>
       <c r="AO6">
-        <v>3.512064343163539</v>
+        <v>0.9919678714859438</v>
+      </c>
+      <c r="AP6">
+        <v>3.284745762711865</v>
       </c>
       <c r="AQ6">
-        <v>3.512064343163539</v>
+        <v>0.9919678714859438</v>
       </c>
     </row>
     <row r="7">
@@ -1192,7 +1240,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fineqia International Inc. (CNSX:FNQ)</t>
+          <t>Findev Inc. (TSXV:FDI)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1207,97 +1255,103 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>-1.883817427385892</v>
+        <v>0.9124423963133641</v>
       </c>
       <c r="J7">
-        <v>-1.883817427385892</v>
+        <v>0.9124423963133641</v>
       </c>
       <c r="K7">
-        <v>-0.203</v>
+        <v>3.79</v>
       </c>
       <c r="L7">
-        <v>-0.8423236514522823</v>
+        <v>1.746543778801843</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>0.626</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.07228637413394919</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>0.1651715039577836</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>0.626</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.07228637413394919</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>0.1651715039577836</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>0.01</v>
+        <v>0.197</v>
       </c>
       <c r="V7">
-        <v>0.001663893510815308</v>
+        <v>0.02274826789838337</v>
       </c>
       <c r="W7">
-        <v>0.2368728121353559</v>
+        <v>0.2445161290322581</v>
       </c>
       <c r="X7">
-        <v>0.02529724661909323</v>
+        <v>0.04813485421146283</v>
       </c>
       <c r="Y7">
-        <v>0.2115755655162627</v>
+        <v>0.1963812748207952</v>
       </c>
       <c r="Z7">
-        <v>-0.2855450236966824</v>
+        <v>0.1420621931260229</v>
       </c>
       <c r="AA7">
-        <v>0.537914691943128</v>
+        <v>0.1296235679214403</v>
       </c>
       <c r="AB7">
-        <v>0.03777388584647523</v>
+        <v>0.04813485421146283</v>
       </c>
       <c r="AC7">
-        <v>0.5001408060966528</v>
+        <v>0.08148871370997743</v>
       </c>
       <c r="AD7">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>2.45</v>
+        <v>-0.197</v>
       </c>
       <c r="AH7">
-        <v>0.2904368358913814</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>1.921875</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>0.2895981087470449</v>
+        <v>-0.02327779747134586</v>
       </c>
       <c r="AK7">
-        <v>1.929133858267716</v>
+        <v>-0.01145149101900831</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AM7">
-        <v>-0.015</v>
+        <v>0.001</v>
+      </c>
+      <c r="AO7">
+        <v>1980</v>
       </c>
       <c r="AQ7">
-        <v>30.26666666666667</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="8">
@@ -1308,7 +1362,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Findev Inc. (TSXV:FDI)</t>
+          <t>Goldmoney Inc. (TSX:XAU)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1316,74 +1370,77 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D8">
+        <v>-0.0488</v>
+      </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.02756967213114754</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.02540983606557377</v>
       </c>
       <c r="I8">
-        <v>0.9138755980861244</v>
+        <v>0.03168032786885246</v>
       </c>
       <c r="J8">
-        <v>0.9138755980861244</v>
+        <v>0.03168032786885246</v>
       </c>
       <c r="K8">
-        <v>1.82</v>
+        <v>-2.86</v>
       </c>
       <c r="L8">
-        <v>0.8708133971291867</v>
+        <v>-0.01172131147540984</v>
       </c>
       <c r="M8">
-        <v>0.679</v>
+        <v>2.11</v>
       </c>
       <c r="N8">
-        <v>0.06405660377358491</v>
+        <v>0.02268817204301075</v>
       </c>
       <c r="O8">
-        <v>0.3730769230769231</v>
+        <v>-0.7377622377622377</v>
       </c>
       <c r="P8">
-        <v>0.679</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.06405660377358491</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.3730769230769231</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8">
-        <v>0.225</v>
+        <v>20.8</v>
       </c>
       <c r="V8">
-        <v>0.02122641509433962</v>
+        <v>0.2236559139784946</v>
       </c>
       <c r="W8">
-        <v>0.1338235294117647</v>
+        <v>-0.02015503875968992</v>
       </c>
       <c r="X8">
-        <v>0.02293891894203839</v>
+        <v>0.04813485421146283</v>
       </c>
       <c r="Y8">
-        <v>0.1108846104697263</v>
+        <v>-0.06828989297115276</v>
       </c>
       <c r="Z8">
-        <v>0.1585856286516427</v>
+        <v>2.70509977827051</v>
       </c>
       <c r="AA8">
-        <v>0.144927536231884</v>
+        <v>0.08569844789356984</v>
       </c>
       <c r="AB8">
-        <v>0.02293891894203839</v>
+        <v>0.04813485421146283</v>
       </c>
       <c r="AC8">
-        <v>0.1219886172898456</v>
+        <v>0.03756359368210701</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -1395,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>-0.225</v>
+        <v>-20.8</v>
       </c>
       <c r="AH8">
         <v>0</v>
@@ -1404,22 +1461,28 @@
         <v>0</v>
       </c>
       <c r="AJ8">
-        <v>-0.02168674698795181</v>
+        <v>-0.2880886426592798</v>
       </c>
       <c r="AK8">
-        <v>-0.01472995090016367</v>
+        <v>-0.1975308641975309</v>
       </c>
       <c r="AL8">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="AM8">
-        <v>0.001</v>
+        <v>-0.517</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
       </c>
       <c r="AO8">
-        <v>1910</v>
+        <v>1546</v>
+      </c>
+      <c r="AP8">
+        <v>-2.427071178529755</v>
       </c>
       <c r="AQ8">
-        <v>1910</v>
+        <v>-14.95164410058027</v>
       </c>
     </row>
     <row r="9">
@@ -1430,7 +1493,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TMX Group Limited (TSX:X)</t>
+          <t>Solution Financial Inc. (TSX:SFI)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1438,122 +1501,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D9">
-        <v>0.0493</v>
-      </c>
-      <c r="F9">
-        <v>0.0906</v>
-      </c>
       <c r="G9">
-        <v>0.6735003796507214</v>
+        <v>0.08918918918918919</v>
       </c>
       <c r="H9">
-        <v>0.6569222981523665</v>
+        <v>0.08918918918918919</v>
       </c>
       <c r="I9">
-        <v>0.5360668185269551</v>
+        <v>0.08851351351351351</v>
       </c>
       <c r="J9">
-        <v>0.3728779015940359</v>
+        <v>0.07573143175749038</v>
       </c>
       <c r="K9">
-        <v>255</v>
+        <v>0.789</v>
       </c>
       <c r="L9">
-        <v>0.3227031131359149</v>
+        <v>0.05331081081081081</v>
       </c>
       <c r="M9">
-        <v>216.1</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N9">
-        <v>0.03815324858757062</v>
+        <v>0.03136363636363636</v>
       </c>
       <c r="O9">
-        <v>0.8474509803921569</v>
+        <v>0.8745247148288973</v>
       </c>
       <c r="P9">
-        <v>130.8</v>
+        <v>0.279</v>
       </c>
       <c r="Q9">
-        <v>0.02309322033898305</v>
+        <v>0.01268181818181818</v>
       </c>
       <c r="R9">
-        <v>0.5129411764705882</v>
+        <v>0.3536121673003803</v>
       </c>
       <c r="S9">
-        <v>85.30000000000001</v>
+        <v>0.4109999999999999</v>
       </c>
       <c r="T9">
-        <v>0.3947246645071726</v>
+        <v>0.5956521739130434</v>
       </c>
       <c r="U9">
-        <v>206</v>
+        <v>0.122</v>
       </c>
       <c r="V9">
-        <v>0.03637005649717514</v>
+        <v>0.005545454545454545</v>
       </c>
       <c r="W9">
-        <v>0.09413762551683402</v>
+        <v>0.07373831775700936</v>
       </c>
       <c r="X9">
-        <v>0.02383052331222413</v>
+        <v>0.05076982896842575</v>
       </c>
       <c r="Y9">
-        <v>0.07030710220460989</v>
+        <v>0.02296848878858361</v>
       </c>
       <c r="Z9">
-        <v>0.2410248589293885</v>
+        <v>0.997977073499663</v>
       </c>
       <c r="AA9">
-        <v>0.0898728436295889</v>
+        <v>0.0755782326372797</v>
       </c>
       <c r="AB9">
-        <v>0.02293651736980802</v>
+        <v>0.04816665248696719</v>
       </c>
       <c r="AC9">
-        <v>0.06693632625978088</v>
+        <v>0.0274115801503125</v>
       </c>
       <c r="AD9">
-        <v>876.5</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>876.5</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="AG9">
-        <v>670.5</v>
+        <v>8.157999999999999</v>
       </c>
       <c r="AH9">
-        <v>0.134011161226206</v>
+        <v>0.273447820343461</v>
       </c>
       <c r="AI9">
-        <v>0.2316638033566803</v>
+        <v>0.4385593220338983</v>
       </c>
       <c r="AJ9">
-        <v>0.1058489225668956</v>
+        <v>0.2705086544200543</v>
       </c>
       <c r="AK9">
-        <v>0.1874213836477987</v>
+        <v>0.434907772683655</v>
       </c>
       <c r="AL9">
-        <v>69.40000000000001</v>
+        <v>0.375</v>
       </c>
       <c r="AM9">
-        <v>68.21000000000001</v>
+        <v>0.375</v>
       </c>
       <c r="AN9">
-        <v>1.813948675496689</v>
+        <v>6.225563909774436</v>
       </c>
       <c r="AO9">
-        <v>6.103746397694525</v>
+        <v>3.493333333333334</v>
       </c>
       <c r="AP9">
-        <v>1.387624172185431</v>
+        <v>6.133834586466165</v>
       </c>
       <c r="AQ9">
-        <v>6.210233103650491</v>
+        <v>3.493333333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1564,7 +1621,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Solution Financial Inc. (TSX:SFI)</t>
+          <t>First National Financial Corporation (TSX:FN)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1572,116 +1629,110 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D10">
+        <v>0.0605</v>
+      </c>
+      <c r="E10">
+        <v>-0.0336</v>
+      </c>
       <c r="G10">
-        <v>0.0687116564417178</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>0.0687116564417178</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>0.08773006134969324</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>0.0523774524691733</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>0.601</v>
+        <v>143.5</v>
       </c>
       <c r="L10">
-        <v>0.03687116564417178</v>
+        <v>0.2646624861674658</v>
       </c>
       <c r="M10">
-        <v>0.418</v>
+        <v>103</v>
       </c>
       <c r="N10">
-        <v>0.01375</v>
+        <v>0.0638284687364442</v>
       </c>
       <c r="O10">
-        <v>0.6955074875207987</v>
+        <v>0.7177700348432056</v>
       </c>
       <c r="P10">
-        <v>0.261</v>
+        <v>103</v>
       </c>
       <c r="Q10">
-        <v>0.008585526315789474</v>
+        <v>0.0638284687364442</v>
       </c>
       <c r="R10">
-        <v>0.4342762063227954</v>
+        <v>0.7177700348432056</v>
       </c>
       <c r="S10">
-        <v>0.157</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>0.3755980861244019</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>0.09506578947368421</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>0.08056300268096514</v>
+        <v>0.3322528363047002</v>
       </c>
       <c r="X10">
-        <v>0.02426939493102639</v>
+        <v>0.1787473221590779</v>
       </c>
       <c r="Y10">
-        <v>0.05629360774993875</v>
+        <v>0.1535055141456223</v>
       </c>
       <c r="Z10">
-        <v>1.007416563658838</v>
+        <v>0.01694131468601389</v>
       </c>
       <c r="AA10">
-        <v>0.05276591317969869</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.02293555701710822</v>
+        <v>0.0427640296975634</v>
       </c>
       <c r="AC10">
-        <v>0.02983035616259047</v>
+        <v>-0.0427640296975634</v>
       </c>
       <c r="AD10">
-        <v>7.02</v>
+        <v>30105</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>7.02</v>
+        <v>30105</v>
       </c>
       <c r="AG10">
-        <v>4.129999999999999</v>
+        <v>30105</v>
       </c>
       <c r="AH10">
-        <v>0.1876002137894174</v>
+        <v>0.9491246488664415</v>
       </c>
       <c r="AI10">
-        <v>0.3961625282167043</v>
+        <v>0.9834828458115816</v>
       </c>
       <c r="AJ10">
-        <v>0.1196061395887634</v>
+        <v>0.9491246488664415</v>
       </c>
       <c r="AK10">
-        <v>0.2784895482130816</v>
+        <v>0.9834828458115816</v>
       </c>
       <c r="AL10">
-        <v>0.391</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>0.391</v>
-      </c>
-      <c r="AN10">
-        <v>4.808219178082192</v>
-      </c>
-      <c r="AO10">
-        <v>3.657289002557544</v>
-      </c>
-      <c r="AP10">
-        <v>2.828767123287671</v>
-      </c>
-      <c r="AQ10">
-        <v>3.657289002557544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1692,7 +1743,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>First National Financial Corporation (TSX:FN)</t>
+          <t>Chesswood Group Limited (TSX:CHW)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1701,10 +1752,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.09080000000000001</v>
+        <v>0.216</v>
       </c>
       <c r="E11">
-        <v>0.0558</v>
+        <v>0.142</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1719,85 +1770,85 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>175.4</v>
+        <v>21.7</v>
       </c>
       <c r="L11">
-        <v>0.2979446237472397</v>
+        <v>0.1942703670546106</v>
       </c>
       <c r="M11">
-        <v>103.8</v>
+        <v>8.41</v>
       </c>
       <c r="N11">
-        <v>0.0527064080430588</v>
+        <v>0.05621657754010696</v>
       </c>
       <c r="O11">
-        <v>0.5917901938426453</v>
+        <v>0.3875576036866359</v>
       </c>
       <c r="P11">
-        <v>103.8</v>
+        <v>5.83</v>
       </c>
       <c r="Q11">
-        <v>0.0527064080430588</v>
+        <v>0.03897058823529412</v>
       </c>
       <c r="R11">
-        <v>0.5917901938426453</v>
+        <v>0.2686635944700461</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>0.3067776456599287</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>9.02</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>0.06029411764705882</v>
       </c>
       <c r="W11">
-        <v>0.503299856527977</v>
+        <v>0.1655225019069413</v>
       </c>
       <c r="X11">
-        <v>0.1151503506621835</v>
+        <v>0.1216795904747341</v>
       </c>
       <c r="Y11">
-        <v>0.3881495058657936</v>
+        <v>0.04384291143220717</v>
       </c>
       <c r="Z11">
-        <v>0.02059320462726195</v>
+        <v>0.1110073143584036</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.0229220521349975</v>
+        <v>0.04296800257685214</v>
       </c>
       <c r="AC11">
-        <v>-0.0229220521349975</v>
+        <v>-0.04296800257685214</v>
       </c>
       <c r="AD11">
-        <v>31519.2</v>
+        <v>1571.5</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>31519.2</v>
+        <v>1571.5</v>
       </c>
       <c r="AG11">
-        <v>31519.2</v>
+        <v>1562.48</v>
       </c>
       <c r="AH11">
-        <v>0.941191927999379</v>
+        <v>0.9130788449247574</v>
       </c>
       <c r="AI11">
-        <v>0.9841108276794439</v>
+        <v>0.9048770656993148</v>
       </c>
       <c r="AJ11">
-        <v>0.941191927999379</v>
+        <v>0.9126209055651605</v>
       </c>
       <c r="AK11">
-        <v>0.9841108276794439</v>
+        <v>0.9043804408223745</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1814,7 +1865,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Terra Firma Capital Corporation (TSXV:TII)</t>
+          <t>Accord Financial Corp. (TSX:ACD)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1823,10 +1874,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.007940000000000001</v>
+        <v>0.104</v>
       </c>
       <c r="E12">
-        <v>0.0314</v>
+        <v>0.08410000000000001</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1835,34 +1886,34 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>0.0001586338727222007</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>0.0001487830420244864</v>
       </c>
       <c r="K12">
-        <v>2.82</v>
+        <v>6.31</v>
       </c>
       <c r="L12">
-        <v>0.3988684582743988</v>
+        <v>0.2062091503267974</v>
       </c>
       <c r="M12">
-        <v>0.877</v>
+        <v>1.71</v>
       </c>
       <c r="N12">
-        <v>0.0334732824427481</v>
+        <v>0.0351129363449692</v>
       </c>
       <c r="O12">
-        <v>0.3109929078014185</v>
+        <v>0.2709984152139461</v>
       </c>
       <c r="P12">
-        <v>0.877</v>
+        <v>1.71</v>
       </c>
       <c r="Q12">
-        <v>0.0334732824427481</v>
+        <v>0.0351129363449692</v>
       </c>
       <c r="R12">
-        <v>0.3109929078014185</v>
+        <v>0.2709984152139461</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1871,61 +1922,67 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>2.36</v>
+        <v>7.07</v>
       </c>
       <c r="V12">
-        <v>0.0900763358778626</v>
+        <v>0.1451745379876797</v>
       </c>
       <c r="W12">
-        <v>0.06962962962962962</v>
+        <v>0.08237597911227154</v>
       </c>
       <c r="X12">
-        <v>0.04405014491723794</v>
+        <v>0.0878423523544134</v>
       </c>
       <c r="Y12">
-        <v>0.02557948471239168</v>
+        <v>-0.005466373242141859</v>
       </c>
       <c r="Z12">
-        <v>0.05834777585210861</v>
+        <v>0.09153024325218224</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.361814802830089e-05</v>
       </c>
       <c r="AB12">
-        <v>0.02292484049634764</v>
+        <v>0.04332432314789308</v>
       </c>
       <c r="AC12">
-        <v>-0.02292484049634764</v>
+        <v>-0.04331070499986479</v>
       </c>
       <c r="AD12">
-        <v>96</v>
+        <v>276.2</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>0.005729017473503295</v>
       </c>
       <c r="AF12">
-        <v>96</v>
+        <v>276.2057290174735</v>
       </c>
       <c r="AG12">
-        <v>93.64</v>
+        <v>269.1357290174735</v>
       </c>
       <c r="AH12">
-        <v>0.7855973813420621</v>
+        <v>0.850110368483589</v>
       </c>
       <c r="AI12">
-        <v>0.6931407942238267</v>
+        <v>0.7730235106416838</v>
       </c>
       <c r="AJ12">
-        <v>0.7813751668891855</v>
+        <v>0.8467761942606439</v>
       </c>
       <c r="AK12">
-        <v>0.6878213603643309</v>
+        <v>0.7684416714779152</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
         <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>46033.33333333333</v>
+      </c>
+      <c r="AP12">
+        <v>44855.95483624558</v>
       </c>
     </row>
     <row r="13">
@@ -1945,10 +2002,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.101</v>
+        <v>0.0665</v>
       </c>
       <c r="E13">
-        <v>0.116</v>
+        <v>0.0443</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1963,28 +2020,28 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>55.7</v>
+        <v>34.5</v>
       </c>
       <c r="L13">
-        <v>0.6792682926829269</v>
+        <v>0.5511182108626198</v>
       </c>
       <c r="M13">
-        <v>23</v>
+        <v>27.4</v>
       </c>
       <c r="N13">
-        <v>0.05702950657079097</v>
+        <v>0.07206733298264072</v>
       </c>
       <c r="O13">
-        <v>0.4129263913824057</v>
+        <v>0.7942028985507246</v>
       </c>
       <c r="P13">
-        <v>23</v>
+        <v>27.4</v>
       </c>
       <c r="Q13">
-        <v>0.05702950657079097</v>
+        <v>0.07206733298264072</v>
       </c>
       <c r="R13">
-        <v>0.4129263913824057</v>
+        <v>0.7942028985507246</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1993,55 +2050,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>97.5</v>
+        <v>27.6</v>
       </c>
       <c r="V13">
-        <v>0.2417555169848748</v>
+        <v>0.07259337190952131</v>
       </c>
       <c r="W13">
-        <v>0.2229783827061649</v>
+        <v>0.110612375761462</v>
       </c>
       <c r="X13">
-        <v>0.04092947115732742</v>
+        <v>0.07238104544022357</v>
       </c>
       <c r="Y13">
-        <v>0.1820489115488375</v>
+        <v>0.03823133032123845</v>
       </c>
       <c r="Z13">
-        <v>0.08702111853974319</v>
+        <v>0.04247811630589673</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.02292534530881299</v>
+        <v>0.04374400729351936</v>
       </c>
       <c r="AC13">
-        <v>-0.02292534530881299</v>
+        <v>-0.04374400729351936</v>
       </c>
       <c r="AD13">
-        <v>1259.3</v>
+        <v>1316.7</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>1259.3</v>
+        <v>1316.7</v>
       </c>
       <c r="AG13">
-        <v>1161.8</v>
+        <v>1289.1</v>
       </c>
       <c r="AH13">
-        <v>0.7574281246240828</v>
+        <v>0.7759443691437327</v>
       </c>
       <c r="AI13">
-        <v>0.8014893075356416</v>
+        <v>0.8032576866764275</v>
       </c>
       <c r="AJ13">
-        <v>0.7423167848699763</v>
+        <v>0.7722398610195891</v>
       </c>
       <c r="AK13">
-        <v>0.7883558390445817</v>
+        <v>0.7998883097542815</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2067,10 +2124,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.0362</v>
+        <v>-0.00275</v>
       </c>
       <c r="E14">
-        <v>-0.0131</v>
+        <v>-0.0366</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2085,85 +2142,85 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>29.5</v>
+        <v>31.7</v>
       </c>
       <c r="L14">
-        <v>0.7007125890736342</v>
+        <v>0.673036093418259</v>
       </c>
       <c r="M14">
-        <v>41.77</v>
+        <v>38.98</v>
       </c>
       <c r="N14">
-        <v>0.06700352903432788</v>
+        <v>0.08834995466908431</v>
       </c>
       <c r="O14">
-        <v>1.415932203389831</v>
+        <v>1.229652996845426</v>
       </c>
       <c r="P14">
-        <v>40.5</v>
+        <v>37.9</v>
       </c>
       <c r="Q14">
-        <v>0.06496631376323388</v>
+        <v>0.08590208522212149</v>
       </c>
       <c r="R14">
-        <v>1.372881355932203</v>
+        <v>1.195583596214511</v>
       </c>
       <c r="S14">
-        <v>1.270000000000003</v>
+        <v>1.079999999999998</v>
       </c>
       <c r="T14">
-        <v>0.030404596600431</v>
+        <v>0.02770651616213439</v>
       </c>
       <c r="U14">
-        <v>0.419</v>
+        <v>1.44</v>
       </c>
       <c r="V14">
-        <v>0.000672120628809753</v>
+        <v>0.003263825929283772</v>
       </c>
       <c r="W14">
-        <v>0.05609431450846169</v>
+        <v>0.0582078589790672</v>
       </c>
       <c r="X14">
-        <v>0.02988630231710534</v>
+        <v>0.06378744973648595</v>
       </c>
       <c r="Y14">
-        <v>0.02620801219135635</v>
+        <v>-0.005579590757418748</v>
       </c>
       <c r="Z14">
-        <v>0.032342321579473</v>
+        <v>0.03634592991177431</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.02292912257719927</v>
+        <v>0.04422496695414514</v>
       </c>
       <c r="AC14">
-        <v>-0.02292912257719927</v>
+        <v>-0.04422496695414514</v>
       </c>
       <c r="AD14">
-        <v>751.7</v>
+        <v>986.4</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>751.7</v>
+        <v>986.4</v>
       </c>
       <c r="AG14">
-        <v>751.2810000000001</v>
+        <v>984.9599999999999</v>
       </c>
       <c r="AH14">
-        <v>0.5466511526434442</v>
+        <v>0.6909498458952088</v>
       </c>
       <c r="AI14">
-        <v>0.5798812003394276</v>
+        <v>0.6595787362086258</v>
       </c>
       <c r="AJ14">
-        <v>0.5465129728278779</v>
+        <v>0.6906377966006619</v>
       </c>
       <c r="AK14">
-        <v>0.5797453624213952</v>
+        <v>0.6592506325047186</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2189,10 +2246,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.103</v>
+        <v>0.09970000000000001</v>
       </c>
       <c r="E15">
-        <v>0.103</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2207,28 +2264,28 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>32.5</v>
+        <v>31.9</v>
       </c>
       <c r="L15">
-        <v>0.8165829145728644</v>
+        <v>0.7915632754342432</v>
       </c>
       <c r="M15">
-        <v>27.6</v>
+        <v>24.5</v>
       </c>
       <c r="N15">
-        <v>0.05811749842072016</v>
+        <v>0.07138694638694638</v>
       </c>
       <c r="O15">
-        <v>0.8492307692307692</v>
+        <v>0.768025078369906</v>
       </c>
       <c r="P15">
-        <v>27.6</v>
+        <v>24.5</v>
       </c>
       <c r="Q15">
-        <v>0.05811749842072016</v>
+        <v>0.07138694638694638</v>
       </c>
       <c r="R15">
-        <v>0.8492307692307692</v>
+        <v>0.768025078369906</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2237,55 +2294,55 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>0.01261655011655012</v>
       </c>
       <c r="W15">
-        <v>0.0934982738780207</v>
+        <v>0.0859375</v>
       </c>
       <c r="X15">
-        <v>0.02578635796633163</v>
+        <v>0.0538181810980746</v>
       </c>
       <c r="Y15">
-        <v>0.06771191591168907</v>
+        <v>0.0321193189019254</v>
       </c>
       <c r="Z15">
-        <v>0.07529322739311388</v>
+        <v>0.06651262584584915</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.02293299167948022</v>
+        <v>0.04559944476175491</v>
       </c>
       <c r="AC15">
-        <v>-0.02293299167948022</v>
+        <v>-0.04559944476175491</v>
       </c>
       <c r="AD15">
-        <v>234.7</v>
+        <v>278.6</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>234.7</v>
+        <v>278.6</v>
       </c>
       <c r="AG15">
-        <v>234.7</v>
+        <v>274.27</v>
       </c>
       <c r="AH15">
-        <v>0.3307497181510711</v>
+        <v>0.4480540366677389</v>
       </c>
       <c r="AI15">
-        <v>0.3873576497771909</v>
+        <v>0.4432776451869531</v>
       </c>
       <c r="AJ15">
-        <v>0.3307497181510711</v>
+        <v>0.4441835230861419</v>
       </c>
       <c r="AK15">
-        <v>0.3873576497771909</v>
+        <v>0.4394155438422225</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2311,10 +2368,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.07679999999999999</v>
+        <v>0.109</v>
       </c>
       <c r="E16">
-        <v>0.0688</v>
+        <v>0.0587</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2329,28 +2386,28 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="L16">
-        <v>0.8124999999999999</v>
+        <v>0.7491961414790996</v>
       </c>
       <c r="M16">
-        <v>22.9</v>
+        <v>23.3</v>
       </c>
       <c r="N16">
-        <v>0.06132833422603107</v>
+        <v>0.08553597650513951</v>
       </c>
       <c r="O16">
-        <v>0.9786324786324786</v>
+        <v>1</v>
       </c>
       <c r="P16">
-        <v>22.9</v>
+        <v>23.3</v>
       </c>
       <c r="Q16">
-        <v>0.06132833422603107</v>
+        <v>0.08553597650513951</v>
       </c>
       <c r="R16">
-        <v>0.9786324786324786</v>
+        <v>1</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2365,49 +2422,49 @@
         <v>0</v>
       </c>
       <c r="W16">
-        <v>0.09782608695652174</v>
+        <v>0.08309557774607704</v>
       </c>
       <c r="X16">
-        <v>0.02553735052514459</v>
+        <v>0.05242189628875358</v>
       </c>
       <c r="Y16">
-        <v>0.07228873643137715</v>
+        <v>0.03067368145732346</v>
       </c>
       <c r="Z16">
-        <v>0.07686148919135309</v>
+        <v>0.06929590017825313</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.02293334890902577</v>
+        <v>0.04598577993865317</v>
       </c>
       <c r="AC16">
-        <v>-0.02293334890902577</v>
+        <v>-0.04598577993865317</v>
       </c>
       <c r="AD16">
-        <v>168.4</v>
+        <v>166.8</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>168.4</v>
+        <v>166.8</v>
       </c>
       <c r="AG16">
-        <v>168.4</v>
+        <v>166.8</v>
       </c>
       <c r="AH16">
-        <v>0.3108157991878923</v>
+        <v>0.3797814207650274</v>
       </c>
       <c r="AI16">
-        <v>0.3752228163992871</v>
+        <v>0.3645901639344263</v>
       </c>
       <c r="AJ16">
-        <v>0.3108157991878923</v>
+        <v>0.3797814207650274</v>
       </c>
       <c r="AK16">
-        <v>0.3752228163992871</v>
+        <v>0.3645901639344263</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2424,7 +2481,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Axis Auto Finance Inc. (TSXV:AXIS)</t>
+          <t>ECN Capital Corp. (TSX:ECN)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2433,7 +2490,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>1.446</v>
+        <v>0.172</v>
+      </c>
+      <c r="E17">
+        <v>0.7759999999999999</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2442,100 +2502,97 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0.01686802217976409</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>0.01168616576614056</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>1.73</v>
+        <v>943.4</v>
       </c>
       <c r="L17">
-        <v>0.1130718954248366</v>
+        <v>3.997457627118644</v>
       </c>
       <c r="M17">
-        <v>-0</v>
+        <v>16.1098</v>
       </c>
       <c r="N17">
-        <v>-0</v>
+        <v>0.03189427836072065</v>
       </c>
       <c r="O17">
-        <v>-0</v>
+        <v>0.01707631969472122</v>
       </c>
       <c r="P17">
-        <v>-0</v>
+        <v>5.4098</v>
       </c>
       <c r="Q17">
-        <v>-0</v>
+        <v>0.01071035438527024</v>
       </c>
       <c r="R17">
-        <v>-0</v>
+        <v>0.005734365062539749</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>10.7</v>
+      </c>
+      <c r="T17">
+        <v>0.6641919825199567</v>
       </c>
       <c r="U17">
-        <v>3.28</v>
+        <v>19.1</v>
       </c>
       <c r="V17">
-        <v>0.05985401459854015</v>
+        <v>0.03781429419916849</v>
       </c>
       <c r="W17">
-        <v>0.06731517509727626</v>
+        <v>1.374617514206615</v>
       </c>
       <c r="X17">
-        <v>0.03269838422292742</v>
+        <v>0.06226881407994726</v>
       </c>
       <c r="Y17">
-        <v>0.03461679087434884</v>
+        <v>1.312348700126668</v>
       </c>
       <c r="Z17">
-        <v>0.1656299525225858</v>
+        <v>0.207582021285953</v>
       </c>
       <c r="AA17">
-        <v>0.001935579081016928</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.02506182046510905</v>
+        <v>0.0482126200103498</v>
       </c>
       <c r="AC17">
-        <v>-0.02312624138409212</v>
+        <v>-0.0482126200103498</v>
       </c>
       <c r="AD17">
-        <v>92.2</v>
+        <v>1019.7</v>
       </c>
       <c r="AE17">
-        <v>0.6245963032480472</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>92.82459630324804</v>
+        <v>1019.7</v>
       </c>
       <c r="AG17">
-        <v>89.54459630324804</v>
+        <v>1000.6</v>
       </c>
       <c r="AH17">
-        <v>0.6287881466078272</v>
+        <v>0.6687434417628541</v>
       </c>
       <c r="AI17">
-        <v>0.7607039819461155</v>
+        <v>0.8315935410210407</v>
       </c>
       <c r="AJ17">
-        <v>0.6203529511775226</v>
+        <v>0.6645414093112838</v>
       </c>
       <c r="AK17">
-        <v>0.7540940732542514</v>
+        <v>0.8289288377102146</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
         <v>0</v>
-      </c>
-      <c r="AN17">
-        <v>240.7310704960836</v>
-      </c>
-      <c r="AP17">
-        <v>233.7979015750602</v>
       </c>
     </row>
     <row r="18">
@@ -2546,7 +2603,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IOU Financial Inc. (TSXV:IOU)</t>
+          <t>Home Capital Group Inc. (TSX:HCG)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2555,7 +2612,10 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.08400000000000001</v>
+        <v>0.08890000000000001</v>
+      </c>
+      <c r="E18">
+        <v>0.4379999999999999</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2570,82 +2630,85 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>2.95</v>
+        <v>123.5</v>
       </c>
       <c r="L18">
-        <v>0.295</v>
+        <v>0.3461322869955157</v>
       </c>
       <c r="M18">
-        <v>-0</v>
+        <v>343.8</v>
       </c>
       <c r="N18">
-        <v>-0</v>
+        <v>0.2845084409136048</v>
       </c>
       <c r="O18">
-        <v>-0</v>
+        <v>2.783805668016194</v>
       </c>
       <c r="P18">
-        <v>-0</v>
+        <v>13.6</v>
       </c>
       <c r="Q18">
-        <v>-0</v>
+        <v>0.01125455147302218</v>
       </c>
       <c r="R18">
-        <v>-0</v>
+        <v>0.1101214574898785</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>330.2</v>
+      </c>
+      <c r="T18">
+        <v>0.9604421175101803</v>
       </c>
       <c r="U18">
-        <v>8.19</v>
+        <v>321.4</v>
       </c>
       <c r="V18">
-        <v>0.4333333333333333</v>
+        <v>0.2659715326050976</v>
       </c>
       <c r="W18">
-        <v>0.3836150845253576</v>
+        <v>0.086032741205155</v>
       </c>
       <c r="X18">
-        <v>0.02521002795774562</v>
+        <v>0.06890884456686323</v>
       </c>
       <c r="Y18">
-        <v>0.358405056567612</v>
+        <v>0.01712389663829177</v>
       </c>
       <c r="Z18">
-        <v>0.649772579597141</v>
+        <v>0.09890231733008095</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.02389347437908344</v>
+        <v>0.04822182890584012</v>
       </c>
       <c r="AC18">
-        <v>-0.02389347437908344</v>
+        <v>-0.04822182890584012</v>
       </c>
       <c r="AD18">
-        <v>7.45</v>
+        <v>3585.6</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>7.45</v>
+        <v>3585.6</v>
       </c>
       <c r="AG18">
-        <v>-0.7399999999999993</v>
+        <v>3264.2</v>
       </c>
       <c r="AH18">
-        <v>0.2827324478178369</v>
+        <v>0.7479349186483104</v>
       </c>
       <c r="AI18">
-        <v>0.387012987012987</v>
+        <v>0.7632508833922261</v>
       </c>
       <c r="AJ18">
-        <v>-0.04074889867841406</v>
+        <v>0.7298215802888699</v>
       </c>
       <c r="AK18">
-        <v>-0.06690777576853518</v>
+        <v>0.7458641806050635</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2662,7 +2725,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Marble Financial Inc. (CNSX:MRBL)</t>
+          <t>EQB Inc. (TSX:EQB)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2670,8 +2733,14 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D19">
+        <v>0.154</v>
+      </c>
+      <c r="E19">
+        <v>0.135</v>
+      </c>
       <c r="G19">
-        <v>0.2065217391304348</v>
+        <v>0</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -2683,82 +2752,85 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>-4.01</v>
+        <v>221.7</v>
       </c>
       <c r="L19">
-        <v>-14.52898550724638</v>
+        <v>0.4284885968303054</v>
       </c>
       <c r="M19">
-        <v>-0</v>
+        <v>26.5</v>
       </c>
       <c r="N19">
-        <v>-0</v>
+        <v>0.01684464785151284</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>0.1195308976093821</v>
       </c>
       <c r="P19">
-        <v>-0</v>
+        <v>26.5</v>
       </c>
       <c r="Q19">
-        <v>-0</v>
+        <v>0.01684464785151284</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>0.1195308976093821</v>
       </c>
       <c r="S19">
         <v>0</v>
       </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
       <c r="U19">
-        <v>0.143</v>
+        <v>217.8</v>
       </c>
       <c r="V19">
-        <v>0.0149581589958159</v>
+        <v>0.1384439359267735</v>
       </c>
       <c r="W19">
-        <v>1.684873949579832</v>
+        <v>0.1557210086394605</v>
       </c>
       <c r="X19">
-        <v>0.02614516798462819</v>
+        <v>0.09157646027106217</v>
       </c>
       <c r="Y19">
-        <v>1.658728781595204</v>
+        <v>0.06414454836839836</v>
       </c>
       <c r="Z19">
-        <v>0.1319311663479924</v>
+        <v>0.04820332224675554</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.02414599379839122</v>
+        <v>0.04823500082034399</v>
       </c>
       <c r="AC19">
-        <v>-0.02414599379839122</v>
+        <v>-0.04823500082034399</v>
       </c>
       <c r="AD19">
-        <v>5.32</v>
+        <v>9761.6</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>5.32</v>
+        <v>9761.6</v>
       </c>
       <c r="AG19">
-        <v>5.177</v>
+        <v>9543.800000000001</v>
       </c>
       <c r="AH19">
-        <v>0.3575268817204301</v>
+        <v>0.8612061968451141</v>
       </c>
       <c r="AI19">
-        <v>2.244725738396625</v>
+        <v>0.8611074355377952</v>
       </c>
       <c r="AJ19">
-        <v>0.3512926647214494</v>
+        <v>0.8584870018889987</v>
       </c>
       <c r="AK19">
-        <v>2.324651998203862</v>
+        <v>0.8583866238543663</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2775,7 +2847,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mogo Inc. (TSX:MOGO)</t>
+          <t>IOU Financial Inc. (TSXV:IOU)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2784,10 +2856,10 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.09699999999999999</v>
+        <v>0.366</v>
       </c>
       <c r="G20">
-        <v>0.5734767025089607</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -2799,10 +2871,10 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>-5.09</v>
+        <v>2.46</v>
       </c>
       <c r="L20">
-        <v>-0.1824372759856631</v>
+        <v>0.1651006711409396</v>
       </c>
       <c r="M20">
         <v>-0</v>
@@ -2811,7 +2883,7 @@
         <v>-0</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P20">
         <v>-0</v>
@@ -2820,61 +2892,61 @@
         <v>-0</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
       <c r="U20">
-        <v>36</v>
+        <v>8.07</v>
       </c>
       <c r="V20">
-        <v>0.1378254211332312</v>
+        <v>0.6725</v>
       </c>
       <c r="W20">
-        <v>2.044176706827309</v>
+        <v>0.2084745762711864</v>
       </c>
       <c r="X20">
-        <v>0.02456240347147372</v>
+        <v>0.05084196193278705</v>
       </c>
       <c r="Y20">
-        <v>2.019614303355835</v>
+        <v>0.1576326143383994</v>
       </c>
       <c r="Z20">
-        <v>0.4550644266840645</v>
+        <v>1.347197106690778</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.0250807327306551</v>
+        <v>0.0489619917784522</v>
       </c>
       <c r="AC20">
-        <v>-0.0250807327306551</v>
+        <v>-0.0489619917784522</v>
       </c>
       <c r="AD20">
-        <v>73.59999999999999</v>
+        <v>4.64</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>73.59999999999999</v>
+        <v>4.64</v>
       </c>
       <c r="AG20">
-        <v>37.59999999999999</v>
+        <v>-3.430000000000001</v>
       </c>
       <c r="AH20">
-        <v>0.2198327359617682</v>
+        <v>0.2788461538461538</v>
       </c>
       <c r="AI20">
-        <v>0.2565353781805507</v>
+        <v>0.2399172699069286</v>
       </c>
       <c r="AJ20">
-        <v>0.1258366800535475</v>
+        <v>-0.4002333722287049</v>
       </c>
       <c r="AK20">
-        <v>0.1498605021921084</v>
+        <v>-0.3043478260869566</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -2891,7 +2963,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Accord Financial Corp. (TSX:ACD)</t>
+          <t>Axis Auto Finance Inc. (TSX:AXIS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2900,10 +2972,7 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.133</v>
-      </c>
-      <c r="E21">
-        <v>0.06280000000000001</v>
+        <v>0.399</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2912,91 +2981,91 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0.0002650817313662243</v>
+        <v>0.008352329187353321</v>
       </c>
       <c r="J21">
-        <v>0.0002518873478905631</v>
+        <v>0.008352329187353321</v>
       </c>
       <c r="K21">
-        <v>7.67</v>
+        <v>-0.054</v>
       </c>
       <c r="L21">
-        <v>0.1941772151898734</v>
+        <v>-0.003913043478260869</v>
       </c>
       <c r="M21">
-        <v>1.35</v>
+        <v>2.85</v>
       </c>
       <c r="N21">
-        <v>0.02376760563380282</v>
+        <v>0.06581986143187067</v>
       </c>
       <c r="O21">
-        <v>0.1760104302477184</v>
+        <v>-52.77777777777778</v>
       </c>
       <c r="P21">
-        <v>1.35</v>
+        <v>-0</v>
       </c>
       <c r="Q21">
-        <v>0.02376760563380282</v>
+        <v>-0</v>
       </c>
       <c r="R21">
-        <v>0.1760104302477184</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21">
-        <v>5.99</v>
+        <v>2.39</v>
       </c>
       <c r="V21">
-        <v>0.1054577464788733</v>
+        <v>0.05519630484988453</v>
       </c>
       <c r="W21">
-        <v>0.1131268436578171</v>
+        <v>-0.001849315068493151</v>
       </c>
       <c r="X21">
-        <v>0.05074400537873724</v>
+        <v>0.06574905945060838</v>
       </c>
       <c r="Y21">
-        <v>0.06238283827907987</v>
+        <v>-0.06759837451910153</v>
       </c>
       <c r="Z21">
-        <v>0.1581881512915963</v>
+        <v>0.1323630681960191</v>
       </c>
       <c r="AA21">
-        <v>3.984559389655134e-05</v>
+        <v>0.001105539917821249</v>
       </c>
       <c r="AB21">
-        <v>0.02573558885475878</v>
+        <v>0.05025746416766542</v>
       </c>
       <c r="AC21">
-        <v>-0.02569574326086223</v>
+        <v>-0.04915192424984417</v>
       </c>
       <c r="AD21">
-        <v>274.1</v>
+        <v>108.7</v>
       </c>
       <c r="AE21">
-        <v>0.01264635805517071</v>
+        <v>0.2386892860726209</v>
       </c>
       <c r="AF21">
-        <v>274.1126463580552</v>
+        <v>108.9386892860726</v>
       </c>
       <c r="AG21">
-        <v>268.1226463580552</v>
+        <v>106.5486892860726</v>
       </c>
       <c r="AH21">
-        <v>0.8283534926055951</v>
+        <v>0.7155782133762679</v>
       </c>
       <c r="AI21">
-        <v>0.775177723933829</v>
+        <v>0.7490351420301524</v>
       </c>
       <c r="AJ21">
-        <v>0.8251891622924673</v>
+        <v>0.7110418502404318</v>
       </c>
       <c r="AK21">
-        <v>0.7713037374495041</v>
+        <v>0.7448421220623258</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3005,10 +3074,10 @@
         <v>0</v>
       </c>
       <c r="AN21">
-        <v>21084.61538461539</v>
+        <v>666.8711656441718</v>
       </c>
       <c r="AP21">
-        <v>20624.81895061963</v>
+        <v>653.6729404053535</v>
       </c>
     </row>
     <row r="22">
@@ -3019,7 +3088,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chesswood Group Limited (TSX:CHW)</t>
+          <t>Element Fleet Management Corp. (TSX:EFN)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3028,10 +3097,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.11</v>
+        <v>0.0337</v>
       </c>
       <c r="E22">
-        <v>-0.0311</v>
+        <v>0.0399</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3046,85 +3115,85 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>16.8</v>
+        <v>293.6</v>
       </c>
       <c r="L22">
-        <v>0.2343096234309623</v>
+        <v>0.2489401390537561</v>
       </c>
       <c r="M22">
-        <v>7.529999999999999</v>
+        <v>296.705</v>
       </c>
       <c r="N22">
-        <v>0.03994694960212201</v>
+        <v>0.0554557688353924</v>
       </c>
       <c r="O22">
-        <v>0.4482142857142857</v>
+        <v>1.010575613079019</v>
       </c>
       <c r="P22">
-        <v>3.4</v>
+        <v>88.705</v>
       </c>
       <c r="Q22">
-        <v>0.01803713527851459</v>
+        <v>0.01657944414331906</v>
       </c>
       <c r="R22">
-        <v>0.2023809523809524</v>
+        <v>0.3021287465940054</v>
       </c>
       <c r="S22">
-        <v>4.129999999999999</v>
+        <v>208</v>
       </c>
       <c r="T22">
-        <v>0.548472775564409</v>
+        <v>0.7010330125882611</v>
       </c>
       <c r="U22">
-        <v>4.76</v>
+        <v>40.1</v>
       </c>
       <c r="V22">
-        <v>0.02525198938992042</v>
+        <v>0.007494906827654524</v>
       </c>
       <c r="W22">
-        <v>0.1666666666666667</v>
+        <v>0.1242225513010366</v>
       </c>
       <c r="X22">
-        <v>0.05070771748977726</v>
+        <v>0.05638867078589178</v>
       </c>
       <c r="Y22">
-        <v>0.1159589491768894</v>
+        <v>0.06783388051514483</v>
       </c>
       <c r="Z22">
-        <v>0.1277027749082749</v>
+        <v>0.1384109846262176</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.02573496168748027</v>
+        <v>0.04973978720916776</v>
       </c>
       <c r="AC22">
-        <v>-0.02573496168748027</v>
+        <v>-0.04973978720916776</v>
       </c>
       <c r="AD22">
-        <v>908.5</v>
+        <v>6307.6</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>908.5</v>
+        <v>6307.6</v>
       </c>
       <c r="AG22">
-        <v>903.74</v>
+        <v>6267.5</v>
       </c>
       <c r="AH22">
-        <v>0.8281677301731997</v>
+        <v>0.5410579950076772</v>
       </c>
       <c r="AI22">
-        <v>0.8642503805175038</v>
+        <v>0.7071776128439132</v>
       </c>
       <c r="AJ22">
-        <v>0.8274188822969311</v>
+        <v>0.5394739107232006</v>
       </c>
       <c r="AK22">
-        <v>0.8636328886510454</v>
+        <v>0.7058551912876015</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3141,7 +3210,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Equitable Group Inc. (TSX:EQB)</t>
+          <t>Terra Firma Capital Corporation (TSXV:TII)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3150,10 +3219,10 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.173</v>
+        <v>0.104</v>
       </c>
       <c r="E23">
-        <v>0.173</v>
+        <v>0.328</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3168,28 +3237,28 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>224.5</v>
+        <v>2.67</v>
       </c>
       <c r="L23">
-        <v>0.4511655948553054</v>
+        <v>0.3593539703903096</v>
       </c>
       <c r="M23">
-        <v>19.8</v>
+        <v>1.01</v>
       </c>
       <c r="N23">
-        <v>0.01067212849673907</v>
+        <v>0.04590909090909091</v>
       </c>
       <c r="O23">
-        <v>0.08819599109131404</v>
+        <v>0.3782771535580525</v>
       </c>
       <c r="P23">
-        <v>19.8</v>
+        <v>1.01</v>
       </c>
       <c r="Q23">
-        <v>0.01067212849673907</v>
+        <v>0.04590909090909091</v>
       </c>
       <c r="R23">
-        <v>0.08819599109131404</v>
+        <v>0.3782771535580525</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -3198,55 +3267,55 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>511.3</v>
+        <v>13</v>
       </c>
       <c r="V23">
-        <v>0.2755888535546812</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="W23">
-        <v>0.1992367767128151</v>
+        <v>0.06282352941176471</v>
       </c>
       <c r="X23">
-        <v>0.05330558873257291</v>
+        <v>0.07652129724541118</v>
       </c>
       <c r="Y23">
-        <v>0.1459311879802422</v>
+        <v>-0.01369776783364647</v>
       </c>
       <c r="Z23">
-        <v>0.05315046837782123</v>
+        <v>0.05457617158807111</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.02577667749197193</v>
+        <v>0.05051428542625042</v>
       </c>
       <c r="AC23">
-        <v>-0.02577667749197193</v>
+        <v>-0.05051428542625042</v>
       </c>
       <c r="AD23">
-        <v>9778.4</v>
+        <v>89.2</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>9778.4</v>
+        <v>89.2</v>
       </c>
       <c r="AG23">
-        <v>9267.1</v>
+        <v>76.2</v>
       </c>
       <c r="AH23">
-        <v>0.8405236511170135</v>
+        <v>0.802158273381295</v>
       </c>
       <c r="AI23">
-        <v>0.8685425993036311</v>
+        <v>0.6686656671664167</v>
       </c>
       <c r="AJ23">
-        <v>0.833192476443933</v>
+        <v>0.7759674134419552</v>
       </c>
       <c r="AK23">
-        <v>0.8622884312977455</v>
+        <v>0.632890365448505</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3263,7 +3332,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rifco Inc. (TSXV:RFC)</t>
+          <t>Marble Financial Inc. (CNSX:MRBL)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3271,14 +3340,8 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D24">
-        <v>0.047</v>
-      </c>
-      <c r="E24">
-        <v>0.106</v>
-      </c>
       <c r="G24">
-        <v>0</v>
+        <v>0.4621848739495799</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -3290,19 +3353,19 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>4.17</v>
+        <v>-3.3</v>
       </c>
       <c r="L24">
-        <v>0.2916083916083916</v>
+        <v>-27.73109243697479</v>
       </c>
       <c r="M24">
-        <v>-0</v>
+        <v>0.073</v>
       </c>
       <c r="N24">
-        <v>-0</v>
+        <v>0.01084695393759287</v>
       </c>
       <c r="O24">
-        <v>-0</v>
+        <v>-0.02212121212121212</v>
       </c>
       <c r="P24">
         <v>-0</v>
@@ -3311,61 +3374,64 @@
         <v>-0</v>
       </c>
       <c r="R24">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>0.073</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
       </c>
       <c r="U24">
-        <v>8.25</v>
+        <v>0.101</v>
       </c>
       <c r="V24">
-        <v>0.375</v>
+        <v>0.0150074294205052</v>
       </c>
       <c r="W24">
-        <v>0.1853333333333333</v>
+        <v>1.11864406779661</v>
       </c>
       <c r="X24">
-        <v>0.06065124534319033</v>
+        <v>0.05358596521459046</v>
       </c>
       <c r="Y24">
-        <v>0.124682087990143</v>
+        <v>1.06505810258202</v>
       </c>
       <c r="Z24">
-        <v>0.1007965038415451</v>
+        <v>0.05343511450381679</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.02586765279044443</v>
+        <v>0.05314340400118578</v>
       </c>
       <c r="AC24">
-        <v>-0.02586765279044443</v>
+        <v>-0.05314340400118578</v>
       </c>
       <c r="AD24">
-        <v>144</v>
+        <v>5.24</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>144</v>
+        <v>5.24</v>
       </c>
       <c r="AG24">
-        <v>135.75</v>
+        <v>5.139</v>
       </c>
       <c r="AH24">
-        <v>0.8674698795180723</v>
+        <v>0.4377610693400167</v>
       </c>
       <c r="AI24">
-        <v>0.8669476219145094</v>
+        <v>3.824817518248175</v>
       </c>
       <c r="AJ24">
-        <v>0.8605388272583201</v>
+        <v>0.4329766618923246</v>
       </c>
       <c r="AK24">
-        <v>0.8599936648717137</v>
+        <v>4.049645390070922</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3382,7 +3448,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Element Fleet Management Corp. (TSX:EFN)</t>
+          <t>goeasy Ltd. (TSX:GSY)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3391,13 +3457,16 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.0194</v>
+        <v>0.163</v>
       </c>
       <c r="E25">
-        <v>-0.00158</v>
+        <v>0.328</v>
+      </c>
+      <c r="F25">
+        <v>0.26</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>0.03391684901531729</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -3409,91 +3478,94 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>268.7</v>
+        <v>117.7</v>
       </c>
       <c r="L25">
-        <v>0.2331251084504598</v>
+        <v>0.2575492341356674</v>
       </c>
       <c r="M25">
-        <v>420.56</v>
+        <v>132.4</v>
       </c>
       <c r="N25">
-        <v>0.1007908737957149</v>
+        <v>0.1023975251353442</v>
       </c>
       <c r="O25">
-        <v>1.565165612206922</v>
+        <v>1.124893797790994</v>
       </c>
       <c r="P25">
-        <v>84.45999999999999</v>
+        <v>34.9</v>
       </c>
       <c r="Q25">
-        <v>0.020241575995782</v>
+        <v>0.02699149265274555</v>
       </c>
       <c r="R25">
-        <v>0.3143282471157425</v>
+        <v>0.2965165675446049</v>
       </c>
       <c r="S25">
-        <v>336.1</v>
+        <v>97.5</v>
       </c>
       <c r="T25">
-        <v>0.7991725318622789</v>
+        <v>0.736404833836858</v>
       </c>
       <c r="U25">
-        <v>82.09999999999999</v>
+        <v>53.9</v>
       </c>
       <c r="V25">
-        <v>0.01967598140248286</v>
+        <v>0.04168600154679041</v>
       </c>
       <c r="W25">
-        <v>0.1110881428807673</v>
+        <v>0.1843382928739233</v>
       </c>
       <c r="X25">
-        <v>0.0323302833094249</v>
+        <v>0.05679612613527718</v>
       </c>
       <c r="Y25">
-        <v>0.0787578595713424</v>
+        <v>0.1275421667386461</v>
       </c>
       <c r="Z25">
-        <v>0.1141515880797456</v>
+        <v>0.2889661713563073</v>
       </c>
       <c r="AA25">
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.02641925292916152</v>
+        <v>0.05740656540583329</v>
       </c>
       <c r="AC25">
-        <v>-0.02641925292916152</v>
+        <v>-0.05740656540583329</v>
       </c>
       <c r="AD25">
-        <v>6801.3</v>
+        <v>1599.6</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>6801.3</v>
+        <v>1599.6</v>
       </c>
       <c r="AG25">
-        <v>6719.2</v>
+        <v>1545.7</v>
       </c>
       <c r="AH25">
-        <v>0.6197705464784624</v>
+        <v>0.5529973034640115</v>
       </c>
       <c r="AI25">
-        <v>0.7107193613108176</v>
+        <v>0.7349751883844883</v>
       </c>
       <c r="AJ25">
-        <v>0.616904460236141</v>
+        <v>0.5445098108289005</v>
       </c>
       <c r="AK25">
-        <v>0.7082160737812911</v>
+        <v>0.7282449941107184</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>-0.753</v>
+      </c>
+      <c r="AQ25">
+        <v>-0</v>
       </c>
     </row>
     <row r="26">
@@ -3504,7 +3576,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>goeasy Ltd. (TSX:GSY)</t>
+          <t>Mogo Inc. (TSX:MOGO)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3513,13 +3585,10 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.148</v>
-      </c>
-      <c r="E26">
-        <v>0.518</v>
+        <v>0.158</v>
       </c>
       <c r="G26">
-        <v>0.03060984224158229</v>
+        <v>0.6200607902735562</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -3531,85 +3600,85 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>192.9</v>
+        <v>-87.7</v>
       </c>
       <c r="L26">
-        <v>0.4542029668000942</v>
+        <v>-2.66565349544073</v>
       </c>
       <c r="M26">
-        <v>31.84</v>
+        <v>0.696</v>
       </c>
       <c r="N26">
-        <v>0.01387484748126198</v>
+        <v>0.0166109785202864</v>
       </c>
       <c r="O26">
-        <v>0.1650596163815448</v>
+        <v>-0.007936145952109463</v>
       </c>
       <c r="P26">
-        <v>26.6</v>
+        <v>-0</v>
       </c>
       <c r="Q26">
-        <v>0.01159142408924525</v>
+        <v>-0</v>
       </c>
       <c r="R26">
-        <v>0.1378952825298082</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>5.240000000000002</v>
+        <v>0.696</v>
       </c>
       <c r="T26">
-        <v>0.1645728643216081</v>
+        <v>1</v>
       </c>
       <c r="U26">
-        <v>98.59999999999999</v>
+        <v>25.7</v>
       </c>
       <c r="V26">
-        <v>0.04296670733833013</v>
+        <v>0.6133651551312649</v>
       </c>
       <c r="W26">
-        <v>0.6265021110750244</v>
+        <v>-0.4111579934364745</v>
       </c>
       <c r="X26">
-        <v>0.02591337159321285</v>
+        <v>0.05941354142996655</v>
       </c>
       <c r="Y26">
-        <v>0.6005887394818116</v>
+        <v>-0.470571534866441</v>
       </c>
       <c r="Z26">
-        <v>0.4630396860008723</v>
+        <v>0.1611954924056835</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.02787628224805427</v>
+        <v>0.06505075307052649</v>
       </c>
       <c r="AC26">
-        <v>-0.02787628224805427</v>
+        <v>-0.06505075307052649</v>
       </c>
       <c r="AD26">
-        <v>1184.7</v>
+        <v>67.5</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>1184.7</v>
+        <v>67.5</v>
       </c>
       <c r="AG26">
-        <v>1086.1</v>
+        <v>41.8</v>
       </c>
       <c r="AH26">
-        <v>0.3404799540163817</v>
+        <v>0.6170018281535649</v>
       </c>
       <c r="AI26">
-        <v>0.6497915752523037</v>
+        <v>0.3320216428922774</v>
       </c>
       <c r="AJ26">
-        <v>0.3212458221183708</v>
+        <v>0.4994026284348865</v>
       </c>
       <c r="AK26">
-        <v>0.6297692218485447</v>
+        <v>0.2353603603603603</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -3626,7 +3695,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Home Capital Group Inc. (TSX:HCG)</t>
+          <t>Everyday People Financial Corp. (TSXV:EPF)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3634,41 +3703,32 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D27">
-        <v>0.00637</v>
-      </c>
-      <c r="E27">
-        <v>-0.0151</v>
-      </c>
-      <c r="F27">
-        <v>0.284</v>
-      </c>
       <c r="G27">
-        <v>0</v>
+        <v>-0.2767441860465116</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>-0.2767441860465116</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>-0.3631646371159258</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>-0.3631646371159258</v>
       </c>
       <c r="K27">
-        <v>195.7</v>
+        <v>-13.5</v>
       </c>
       <c r="L27">
-        <v>0.4142675698560542</v>
+        <v>-1.046511627906977</v>
       </c>
       <c r="M27">
-        <v>55.3</v>
+        <v>-0</v>
       </c>
       <c r="N27">
-        <v>0.04117953682329287</v>
+        <v>-0</v>
       </c>
       <c r="O27">
-        <v>0.2825753704649974</v>
+        <v>0</v>
       </c>
       <c r="P27">
         <v>-0</v>
@@ -3677,70 +3737,79 @@
         <v>-0</v>
       </c>
       <c r="R27">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>55.3</v>
-      </c>
-      <c r="T27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>231</v>
+        <v>0.47</v>
       </c>
       <c r="V27">
-        <v>0.1720157867302107</v>
+        <v>0.01437308868501529</v>
       </c>
       <c r="W27">
-        <v>0.160884577441631</v>
+        <v>-0.391304347826087</v>
       </c>
       <c r="X27">
-        <v>0.0332492279677031</v>
+        <v>0.04973936130287607</v>
       </c>
       <c r="Y27">
-        <v>0.1276353494739279</v>
+        <v>-0.4410437091289631</v>
       </c>
       <c r="Z27">
-        <v>0.1451528652634813</v>
+        <v>0.7153107913270997</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>-0.259775583957412</v>
       </c>
       <c r="AB27">
-        <v>0.03224158878479137</v>
+        <v>0.04868791282806543</v>
       </c>
       <c r="AC27">
-        <v>-0.03224158878479137</v>
+        <v>-0.3084634967854774</v>
       </c>
       <c r="AD27">
-        <v>2403.1</v>
+        <v>7.48</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>0.01411909397721617</v>
       </c>
       <c r="AF27">
-        <v>2403.1</v>
+        <v>7.494119093977217</v>
       </c>
       <c r="AG27">
-        <v>2172.1</v>
+        <v>7.024119093977217</v>
       </c>
       <c r="AH27">
-        <v>0.6415109450080085</v>
+        <v>0.1864481487069125</v>
       </c>
       <c r="AI27">
-        <v>0.6260355337883603</v>
+        <v>0.225088372899251</v>
       </c>
       <c r="AJ27">
-        <v>0.6179516358463727</v>
+        <v>0.1768225263185806</v>
       </c>
       <c r="AK27">
-        <v>0.6020900321543409</v>
+        <v>0.213992615426077</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>1.07</v>
+      </c>
+      <c r="AN27">
+        <v>-2.099943851768669</v>
+      </c>
+      <c r="AO27">
+        <v>-4.383177570093458</v>
+      </c>
+      <c r="AP27">
+        <v>-1.971959318915558</v>
+      </c>
+      <c r="AQ27">
+        <v>-4.383177570093458</v>
       </c>
     </row>
     <row r="28">
@@ -3751,7 +3820,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lendified Holdings Inc. (TSXV:LHI)</t>
+          <t>FRNT Financial Inc. (TSXV:FRNT)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3760,100 +3829,115 @@
         </is>
       </c>
       <c r="G28">
-        <v>-0.2038934426229508</v>
+        <v>-5.445783132530121</v>
       </c>
       <c r="H28">
-        <v>-0</v>
+        <v>-5.542168674698795</v>
       </c>
       <c r="I28">
-        <v>-0</v>
+        <v>-5.602409638554217</v>
       </c>
       <c r="J28">
-        <v>-0</v>
+        <v>-5.602409638554217</v>
       </c>
       <c r="K28">
-        <v>-2.38</v>
+        <v>-2.26</v>
       </c>
       <c r="L28">
-        <v>2.438524590163934</v>
+        <v>-6.80722891566265</v>
       </c>
       <c r="M28">
-        <v>-0</v>
+        <v>0.031</v>
       </c>
       <c r="N28">
-        <v>-0</v>
+        <v>0.003510758776896942</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>-0.01371681415929204</v>
       </c>
       <c r="P28">
-        <v>-0</v>
+        <v>0.031</v>
       </c>
       <c r="Q28">
-        <v>-0</v>
+        <v>0.003510758776896942</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>-0.01371681415929204</v>
       </c>
       <c r="S28">
         <v>0</v>
       </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
       <c r="U28">
-        <v>0.796</v>
+        <v>2.1</v>
       </c>
       <c r="V28">
-        <v>0.1142037302725969</v>
+        <v>0.2378255945639864</v>
       </c>
       <c r="W28">
-        <v>0.2051724137931034</v>
+        <v>-0.5750636132315521</v>
       </c>
       <c r="X28">
-        <v>0.02784909630345092</v>
+        <v>0.0484187056673833</v>
       </c>
       <c r="Y28">
-        <v>0.1773233174896525</v>
+        <v>-0.6234823188989354</v>
       </c>
       <c r="Z28">
-        <v>-0.1972912876490803</v>
+        <v>0.09405099150141642</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>-0.5269121813031161</v>
       </c>
       <c r="AB28">
-        <v>0.04644039217771771</v>
+        <v>0.04825043219884573</v>
       </c>
       <c r="AC28">
-        <v>-0.04644039217771771</v>
+        <v>-0.5751626135019619</v>
       </c>
       <c r="AD28">
-        <v>5.94</v>
+        <v>0.358</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>5.94</v>
+        <v>0.358</v>
       </c>
       <c r="AG28">
-        <v>5.144</v>
+        <v>-1.742</v>
       </c>
       <c r="AH28">
-        <v>0.4601084430673896</v>
+        <v>0.03896386591205921</v>
       </c>
       <c r="AI28">
-        <v>5.165217391304346</v>
+        <v>0.06059580230196344</v>
       </c>
       <c r="AJ28">
-        <v>0.4246326564305762</v>
+        <v>-0.2457674943566591</v>
       </c>
       <c r="AK28">
-        <v>14.53107344632768</v>
+        <v>-0.4574579831932774</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>0.023</v>
+      </c>
+      <c r="AN28">
+        <v>-0.1935135135135135</v>
+      </c>
+      <c r="AO28">
+        <v>-80.86956521739131</v>
+      </c>
+      <c r="AP28">
+        <v>0.9416216216216216</v>
+      </c>
+      <c r="AQ28">
+        <v>-80.86956521739131</v>
       </c>
     </row>
     <row r="29">
@@ -3864,7 +3948,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Goldmoney Inc. (TSX:XAU)</t>
+          <t>Fineqia International Inc. (CNSX:FNQ)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3872,26 +3956,8 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D29">
-        <v>-0.0167</v>
-      </c>
-      <c r="G29">
-        <v>0.01686668728734921</v>
-      </c>
-      <c r="H29">
-        <v>0.01497061552737395</v>
-      </c>
-      <c r="I29">
-        <v>-0.01385709866996598</v>
-      </c>
-      <c r="J29">
-        <v>-0.01385709866996598</v>
-      </c>
       <c r="K29">
-        <v>-3.35</v>
-      </c>
-      <c r="L29">
-        <v>-0.01036189297865759</v>
+        <v>-1.19</v>
       </c>
       <c r="M29">
         <v>-0</v>
@@ -3915,73 +3981,67 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>25.1</v>
+        <v>0.075</v>
       </c>
       <c r="V29">
-        <v>0.2114574557708509</v>
+        <v>0.01164596273291925</v>
       </c>
       <c r="W29">
-        <v>-0.0246504782928624</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="X29">
-        <v>0.02299231208411621</v>
+        <v>0.04877517592697738</v>
       </c>
       <c r="Y29">
-        <v>-0.04764279037697861</v>
+        <v>1.117891490739689</v>
       </c>
       <c r="Z29">
-        <v>3.495135135135135</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>-0.04843243243243243</v>
+        <v>-1.352459016393443</v>
       </c>
       <c r="AB29">
-        <v>0.02296991891889327</v>
+        <v>0.04838341627112454</v>
       </c>
       <c r="AC29">
-        <v>-0.07140235135132571</v>
+        <v>-1.400842432664567</v>
       </c>
       <c r="AD29">
-        <v>1.1</v>
+        <v>0.589</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>1.1</v>
+        <v>0.589</v>
       </c>
       <c r="AG29">
-        <v>-24</v>
+        <v>0.514</v>
       </c>
       <c r="AH29">
-        <v>0.009181969949916529</v>
+        <v>0.08379570351401337</v>
       </c>
       <c r="AI29">
-        <v>0.007703081232492998</v>
+        <v>0.6239406779661016</v>
       </c>
       <c r="AJ29">
-        <v>-0.2534318901795142</v>
+        <v>0.07391429393155018</v>
       </c>
       <c r="AK29">
-        <v>-0.2039082412914189</v>
+        <v>0.5914844649021864</v>
       </c>
       <c r="AL29">
-        <v>0.025</v>
+        <v>0.005</v>
       </c>
       <c r="AM29">
-        <v>-0.457</v>
-      </c>
-      <c r="AN29">
-        <v>-0.2777777777777778</v>
+        <v>0.002</v>
       </c>
       <c r="AO29">
-        <v>-179.2</v>
-      </c>
-      <c r="AP29">
-        <v>6.060606060606061</v>
+        <v>-330</v>
       </c>
       <c r="AQ29">
-        <v>9.803063457330417</v>
+        <v>-824.9999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -3992,7 +4052,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Mint Corporation (TSXV:MIT)</t>
+          <t>PowerBand Solutions Inc. (TSXV:PBX)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4000,8 +4060,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D30">
+        <v>1.557</v>
+      </c>
+      <c r="G30">
+        <v>-0.5442953020134228</v>
+      </c>
+      <c r="H30">
+        <v>-0.5442953020134228</v>
+      </c>
+      <c r="I30">
+        <v>-0.9060402684563759</v>
+      </c>
+      <c r="J30">
+        <v>-0.9060402684563759</v>
+      </c>
       <c r="K30">
-        <v>-5.2</v>
+        <v>-19.7</v>
+      </c>
+      <c r="L30">
+        <v>-1.322147651006711</v>
       </c>
       <c r="M30">
         <v>-0</v>
@@ -4025,73 +4103,73 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>0.017</v>
+        <v>13.3</v>
       </c>
       <c r="V30">
-        <v>0.001164383561643836</v>
+        <v>0.9300699300699301</v>
       </c>
       <c r="W30">
-        <v>0.3005780346820809</v>
+        <v>-2.545219638242894</v>
       </c>
       <c r="X30">
-        <v>0.02524380236715754</v>
+        <v>0.05024498821415889</v>
       </c>
       <c r="Y30">
-        <v>0.2753342323149234</v>
+        <v>-2.595464626457053</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>2.299382716049382</v>
       </c>
       <c r="AA30">
-        <v>-0.2480501494332162</v>
+        <v>-2.083333333333333</v>
       </c>
       <c r="AB30">
-        <v>0.02572281984750222</v>
+        <v>0.06544463092221775</v>
       </c>
       <c r="AC30">
-        <v>-0.2737729692807185</v>
+        <v>-2.148777964255551</v>
       </c>
       <c r="AD30">
-        <v>5.83</v>
+        <v>4.31</v>
       </c>
       <c r="AE30">
-        <v>0.01061134695556453</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>5.840611346955565</v>
+        <v>4.31</v>
       </c>
       <c r="AG30">
-        <v>5.823611346955564</v>
+        <v>-8.990000000000002</v>
       </c>
       <c r="AH30">
-        <v>0.2857356488912191</v>
+        <v>0.2315959161740999</v>
       </c>
       <c r="AI30">
-        <v>-0.3505897766475493</v>
+        <v>0.2579293836026331</v>
       </c>
       <c r="AJ30">
-        <v>0.2851411167214391</v>
+        <v>-1.693032015065914</v>
       </c>
       <c r="AK30">
-        <v>-0.3492129781883207</v>
+        <v>-2.636363636363638</v>
       </c>
       <c r="AL30">
-        <v>3.66</v>
+        <v>0.998</v>
       </c>
       <c r="AM30">
-        <v>3.66</v>
+        <v>0.998</v>
       </c>
       <c r="AN30">
-        <v>530</v>
+        <v>-0.3265151515151515</v>
       </c>
       <c r="AO30">
-        <v>-0.08169398907103824</v>
+        <v>-13.52705410821643</v>
       </c>
       <c r="AP30">
-        <v>529.4192133595968</v>
+        <v>0.6810606060606063</v>
       </c>
       <c r="AQ30">
-        <v>-0.08169398907103824</v>
+        <v>-13.52705410821643</v>
       </c>
     </row>
     <row r="31">
@@ -4102,97 +4180,430 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>WonderFi Technologies Inc. (TSX:WNDR)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G31">
+        <v>-5.489406779661017</v>
+      </c>
+      <c r="H31">
+        <v>-5.741525423728814</v>
+      </c>
+      <c r="I31">
+        <v>-6.546610169491525</v>
+      </c>
+      <c r="J31">
+        <v>-6.546610169491525</v>
+      </c>
+      <c r="K31">
+        <v>-25.9</v>
+      </c>
+      <c r="L31">
+        <v>-5.487288135593221</v>
+      </c>
+      <c r="M31">
+        <v>3.75</v>
+      </c>
+      <c r="N31">
+        <v>0.1689189189189189</v>
+      </c>
+      <c r="O31">
+        <v>-0.1447876447876448</v>
+      </c>
+      <c r="P31">
+        <v>-0</v>
+      </c>
+      <c r="Q31">
+        <v>-0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>3.75</v>
+      </c>
+      <c r="T31">
+        <v>1</v>
+      </c>
+      <c r="U31">
+        <v>6.04</v>
+      </c>
+      <c r="V31">
+        <v>0.2720720720720721</v>
+      </c>
+      <c r="W31">
+        <v>-1.321428571428571</v>
+      </c>
+      <c r="X31">
+        <v>0.04928594265307902</v>
+      </c>
+      <c r="Y31">
+        <v>-1.37071451408165</v>
+      </c>
+      <c r="Z31">
+        <v>1.32920304139679</v>
+      </c>
+      <c r="AA31">
+        <v>-8.701774148127292</v>
+      </c>
+      <c r="AB31">
+        <v>0.048553691562799</v>
+      </c>
+      <c r="AC31">
+        <v>-8.75032783969009</v>
+      </c>
+      <c r="AD31">
+        <v>3.65</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>3.65</v>
+      </c>
+      <c r="AG31">
+        <v>-2.39</v>
+      </c>
+      <c r="AH31">
+        <v>0.1411992263056093</v>
+      </c>
+      <c r="AI31">
+        <v>0.02942361950826279</v>
+      </c>
+      <c r="AJ31">
+        <v>-0.1206461383139829</v>
+      </c>
+      <c r="AK31">
+        <v>-0.02025252097279891</v>
+      </c>
+      <c r="AL31">
+        <v>0.012</v>
+      </c>
+      <c r="AM31">
+        <v>-0.03999999999999999</v>
+      </c>
+      <c r="AN31">
+        <v>-0.1346863468634686</v>
+      </c>
+      <c r="AO31">
+        <v>-2575</v>
+      </c>
+      <c r="AP31">
+        <v>0.08819188191881919</v>
+      </c>
+      <c r="AQ31">
+        <v>772.5000000000001</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CoinSmart Financial Inc. (NEOE:SMRT)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G32">
+        <v>0.2638095238095238</v>
+      </c>
+      <c r="H32">
+        <v>0.2638095238095238</v>
+      </c>
+      <c r="I32">
+        <v>-0.1523809523809524</v>
+      </c>
+      <c r="J32">
+        <v>-0.1523809523809524</v>
+      </c>
+      <c r="K32">
+        <v>-8.92</v>
+      </c>
+      <c r="L32">
+        <v>-0.8495238095238096</v>
+      </c>
+      <c r="M32">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="N32">
+        <v>0.015203426124197</v>
+      </c>
+      <c r="O32">
+        <v>-0.007959641255605381</v>
+      </c>
+      <c r="P32">
+        <v>-0</v>
+      </c>
+      <c r="Q32">
+        <v>-0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="T32">
+        <v>1</v>
+      </c>
+      <c r="U32">
+        <v>20.2</v>
+      </c>
+      <c r="V32">
+        <v>4.325481798715203</v>
+      </c>
+      <c r="W32">
+        <v>-6.281690140845071</v>
+      </c>
+      <c r="X32">
+        <v>0.04920526415369803</v>
+      </c>
+      <c r="Y32">
+        <v>-6.330895404998769</v>
+      </c>
+      <c r="AB32">
+        <v>0.05386930416006125</v>
+      </c>
+      <c r="AD32">
+        <v>0.714</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0.714</v>
+      </c>
+      <c r="AG32">
+        <v>-19.486</v>
+      </c>
+      <c r="AH32">
+        <v>0.1326151560178306</v>
+      </c>
+      <c r="AI32">
+        <v>0.09125766871165644</v>
+      </c>
+      <c r="AJ32">
+        <v>1.315199784017279</v>
+      </c>
+      <c r="AK32">
+        <v>1.574499030381383</v>
+      </c>
+      <c r="AL32">
+        <v>0.034</v>
+      </c>
+      <c r="AM32">
+        <v>0.034</v>
+      </c>
+      <c r="AN32">
+        <v>-0.4407407407407407</v>
+      </c>
+      <c r="AO32">
+        <v>-47.05882352941176</v>
+      </c>
+      <c r="AP32">
+        <v>12.02839506172839</v>
+      </c>
+      <c r="AQ32">
+        <v>-47.05882352941176</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>Automotive Finco Corp. (TSXV:AFCC.H)</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="K31">
-        <v>-1.09</v>
-      </c>
-      <c r="M31">
-        <v>3.4</v>
-      </c>
-      <c r="N31">
-        <v>0.1065830721003135</v>
-      </c>
-      <c r="O31">
-        <v>-3.119266055045871</v>
-      </c>
-      <c r="P31">
-        <v>3.4</v>
-      </c>
-      <c r="Q31">
-        <v>0.1065830721003135</v>
-      </c>
-      <c r="R31">
-        <v>-3.119266055045871</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31">
-        <v>23</v>
-      </c>
-      <c r="V31">
-        <v>0.7210031347962382</v>
-      </c>
-      <c r="W31">
-        <v>-0.03645484949832777</v>
-      </c>
-      <c r="X31">
-        <v>0.02293891894203839</v>
-      </c>
-      <c r="Y31">
-        <v>-0.05939376844036615</v>
-      </c>
-      <c r="Z31">
-        <v>0</v>
-      </c>
-      <c r="AA31">
-        <v>-2.556666666666691</v>
-      </c>
-      <c r="AB31">
-        <v>0.02293891894203839</v>
-      </c>
-      <c r="AC31">
-        <v>-2.579605585608729</v>
-      </c>
-      <c r="AD31">
-        <v>0</v>
-      </c>
-      <c r="AE31">
-        <v>0</v>
-      </c>
-      <c r="AF31">
-        <v>0</v>
-      </c>
-      <c r="AG31">
-        <v>-23</v>
-      </c>
-      <c r="AH31">
-        <v>0</v>
-      </c>
-      <c r="AI31">
-        <v>0</v>
-      </c>
-      <c r="AJ31">
-        <v>-2.584269662921349</v>
-      </c>
-      <c r="AK31">
-        <v>76.66666666666649</v>
-      </c>
-      <c r="AL31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>0</v>
+      <c r="K33">
+        <v>-0.6820000000000001</v>
+      </c>
+      <c r="M33">
+        <v>3.04</v>
+      </c>
+      <c r="N33">
+        <v>0.1345132743362832</v>
+      </c>
+      <c r="O33">
+        <v>-4.457478005865102</v>
+      </c>
+      <c r="P33">
+        <v>3.04</v>
+      </c>
+      <c r="Q33">
+        <v>0.1345132743362832</v>
+      </c>
+      <c r="R33">
+        <v>-4.457478005865102</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>17.5</v>
+      </c>
+      <c r="V33">
+        <v>0.7743362831858407</v>
+      </c>
+      <c r="W33">
+        <v>-0.03004405286343613</v>
+      </c>
+      <c r="X33">
+        <v>0.04813485421146283</v>
+      </c>
+      <c r="Y33">
+        <v>-0.07817890707489895</v>
+      </c>
+      <c r="AB33">
+        <v>0.04813485421146283</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33">
+        <v>-17.5</v>
+      </c>
+      <c r="AH33">
+        <v>0</v>
+      </c>
+      <c r="AI33">
+        <v>0</v>
+      </c>
+      <c r="AJ33">
+        <v>-3.431372549019607</v>
+      </c>
+      <c r="AK33">
+        <v>58.33333333333319</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>The Mint Corporation (TSXV:MIT)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="K34">
+        <v>22.4</v>
+      </c>
+      <c r="M34">
+        <v>-0</v>
+      </c>
+      <c r="N34">
+        <v>-0</v>
+      </c>
+      <c r="O34">
+        <v>-0</v>
+      </c>
+      <c r="P34">
+        <v>-0</v>
+      </c>
+      <c r="Q34">
+        <v>-0</v>
+      </c>
+      <c r="R34">
+        <v>-0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0.02</v>
+      </c>
+      <c r="V34">
+        <v>0.001639344262295082</v>
+      </c>
+      <c r="W34">
+        <v>-0.9955555555555555</v>
+      </c>
+      <c r="X34">
+        <v>0.0482708599767159</v>
+      </c>
+      <c r="Y34">
+        <v>-1.043826415532271</v>
+      </c>
+      <c r="AB34">
+        <v>0.0495591273390636</v>
+      </c>
+      <c r="AD34">
+        <v>0.237</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0.237</v>
+      </c>
+      <c r="AG34">
+        <v>0.217</v>
+      </c>
+      <c r="AH34">
+        <v>0.019056042453968</v>
+      </c>
+      <c r="AI34">
+        <v>0.124278972207656</v>
+      </c>
+      <c r="AJ34">
+        <v>0.01747604091165338</v>
+      </c>
+      <c r="AK34">
+        <v>0.1149973502914679</v>
+      </c>
+      <c r="AL34">
+        <v>0.921</v>
+      </c>
+      <c r="AM34">
+        <v>0.921</v>
+      </c>
+      <c r="AO34">
+        <v>-0.3159609120521172</v>
+      </c>
+      <c r="AQ34">
+        <v>-0.3159609120521172</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/canada/canada_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ34"/>
+  <dimension ref="A1:AQ35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1065</v>
+        <v>0.09210000000000002</v>
       </c>
       <c r="E2">
-        <v>0.11465</v>
+        <v>0.0556</v>
       </c>
       <c r="F2">
-        <v>0.14275</v>
+        <v>0.0605</v>
       </c>
       <c r="G2">
-        <v>0.1074140875298778</v>
+        <v>0.2379909838960878</v>
       </c>
       <c r="H2">
-        <v>0.09753359105565274</v>
+        <v>0.2271916472015743</v>
       </c>
       <c r="I2">
-        <v>0.1294133875314078</v>
+        <v>0.3233898627296683</v>
       </c>
       <c r="J2">
-        <v>0.1157705789621059</v>
+        <v>0.2974757794502547</v>
       </c>
       <c r="K2">
-        <v>2256.649</v>
+        <v>621.436</v>
       </c>
       <c r="L2">
-        <v>0.4212987016866331</v>
+        <v>0.109534945863189</v>
       </c>
       <c r="M2">
-        <v>1275.7028</v>
+        <v>675.0120000000001</v>
       </c>
       <c r="N2">
-        <v>0.06554761710245949</v>
+        <v>0.03776320485866742</v>
       </c>
       <c r="O2">
-        <v>0.5653084728728305</v>
+        <v>1.086213222278722</v>
       </c>
       <c r="P2">
-        <v>542.6608</v>
+        <v>483.651</v>
       </c>
       <c r="Q2">
-        <v>0.02788276574678236</v>
+        <v>0.02705761052114534</v>
       </c>
       <c r="R2">
-        <v>0.2404719564274285</v>
+        <v>0.778279661944271</v>
       </c>
       <c r="S2">
-        <v>733.042</v>
+        <v>191.361</v>
       </c>
       <c r="T2">
-        <v>0.5746181634154914</v>
+        <v>0.2834927379068817</v>
       </c>
       <c r="U2">
-        <v>1146.845</v>
+        <v>860.3389999999999</v>
       </c>
       <c r="V2">
-        <v>0.05892670058878145</v>
+        <v>0.0481312301187254</v>
       </c>
       <c r="W2">
-        <v>0.08451653887303852</v>
+        <v>-0.009811320754716982</v>
       </c>
       <c r="X2">
-        <v>0.05370207315633253</v>
+        <v>0.05400647716106724</v>
       </c>
       <c r="Y2">
-        <v>0.03081446571670599</v>
+        <v>-0.06381779791578422</v>
       </c>
       <c r="Z2">
-        <v>0.07980364085136087</v>
+        <v>0.1248851248284711</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04822841486309205</v>
+        <v>0.04898511901041185</v>
       </c>
       <c r="AC2">
-        <v>-0.04822841486309205</v>
+        <v>-0.04606435886215744</v>
       </c>
       <c r="AD2">
-        <v>58474.598</v>
+        <v>43566.966</v>
       </c>
       <c r="AE2">
-        <v>0.2585373975233404</v>
+        <v>1.098296150244505</v>
       </c>
       <c r="AF2">
-        <v>58474.85653739752</v>
+        <v>43568.06429615025</v>
       </c>
       <c r="AG2">
-        <v>57328.01153739752</v>
+        <v>42707.72529615025</v>
       </c>
       <c r="AH2">
-        <v>0.7502828131680134</v>
+        <v>0.7090818803830929</v>
       </c>
       <c r="AI2">
-        <v>0.8296403936188463</v>
+        <v>0.820933364005811</v>
       </c>
       <c r="AJ2">
-        <v>0.7465533431025644</v>
+        <v>0.7049505247651445</v>
       </c>
       <c r="AK2">
-        <v>0.8268225506441714</v>
+        <v>0.8179826850771378</v>
       </c>
       <c r="AL2">
-        <v>368.354</v>
+        <v>1350.402</v>
       </c>
       <c r="AM2">
-        <v>365.854</v>
+        <v>1315.001</v>
       </c>
       <c r="AN2">
-        <v>75.3153322333806</v>
+        <v>21.53548040762578</v>
       </c>
       <c r="AO2">
-        <v>1.881521579784664</v>
+        <v>1.358646536364727</v>
       </c>
       <c r="AP2">
-        <v>73.83852788895054</v>
+        <v>21.11075123683177</v>
       </c>
       <c r="AQ2">
-        <v>1.894378631913277</v>
+        <v>1.395222513138773</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Montfort Capital Corp. (TSXV:MONT)</t>
+          <t>Automotive Finco Corp. (TSXV:AFCC.H)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,116 +724,101 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.241</v>
+      </c>
+      <c r="E3">
+        <v>-0.111</v>
+      </c>
       <c r="G3">
-        <v>0.6876971608832808</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.6876971608832808</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.6671924290220821</v>
+        <v>0.7869822485207101</v>
       </c>
       <c r="J3">
-        <v>0.6664427746074505</v>
+        <v>0.7869822485207101</v>
       </c>
       <c r="K3">
-        <v>-0.554</v>
+        <v>1.03</v>
       </c>
       <c r="L3">
-        <v>-0.08738170347003156</v>
+        <v>0.6094674556213018</v>
       </c>
       <c r="M3">
-        <v>0.261</v>
+        <v>1.25</v>
       </c>
       <c r="N3">
-        <v>0.008365384615384617</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="O3">
-        <v>-0.4711191335740072</v>
+        <v>1.213592233009709</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>1.25</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.213592233009709</v>
       </c>
       <c r="S3">
-        <v>0.261</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>3.97</v>
+        <v>0.318</v>
       </c>
       <c r="V3">
-        <v>0.1272435897435898</v>
+        <v>0.04711111111111111</v>
       </c>
       <c r="W3">
-        <v>-0.277</v>
+        <v>0.05988372093023256</v>
       </c>
       <c r="X3">
-        <v>0.0831181179510555</v>
+        <v>0.04981714963548235</v>
       </c>
       <c r="Y3">
-        <v>-0.3601181179510555</v>
-      </c>
-      <c r="Z3">
-        <v>3.427027027027028</v>
-      </c>
-      <c r="AA3">
-        <v>2.283917400546615</v>
+        <v>0.01006657129475021</v>
       </c>
       <c r="AB3">
-        <v>0.05060649535046997</v>
-      </c>
-      <c r="AC3">
-        <v>2.233310905196145</v>
+        <v>0.04981714963548235</v>
       </c>
       <c r="AD3">
-        <v>155.9</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>155.9</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>151.93</v>
+        <v>-0.318</v>
       </c>
       <c r="AH3">
-        <v>0.8332442544094067</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.8261791202967674</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.8296292251406105</v>
+        <v>-0.04944029850746268</v>
       </c>
       <c r="AK3">
-        <v>0.8224435662859307</v>
+        <v>-0.01850774065882901</v>
       </c>
       <c r="AL3">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>1.98</v>
-      </c>
-      <c r="AN3">
-        <v>35.75688073394495</v>
-      </c>
-      <c r="AO3">
-        <v>2.136363636363637</v>
-      </c>
-      <c r="AP3">
-        <v>34.84633027522936</v>
-      </c>
-      <c r="AQ3">
-        <v>2.136363636363637</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Propel Holdings Inc. (TSX:PRL)</t>
+          <t>Payfare Inc. (TSX:PAY)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,115 +838,115 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.09109489051094891</v>
+        <v>-0.02567882079131109</v>
       </c>
       <c r="H4">
-        <v>0.07931873479318735</v>
+        <v>-0.02567882079131109</v>
       </c>
       <c r="I4">
-        <v>0.09391727493917275</v>
+        <v>0.04918541505042669</v>
       </c>
       <c r="J4">
-        <v>0.0754983609572308</v>
+        <v>0.04862312691206441</v>
       </c>
       <c r="K4">
-        <v>7.87</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="L4">
-        <v>0.03829683698296837</v>
+        <v>0.06377036462373933</v>
       </c>
       <c r="M4">
-        <v>10.2</v>
+        <v>1.4</v>
       </c>
       <c r="N4">
-        <v>0.05399682371625198</v>
+        <v>0.006230529595015576</v>
       </c>
       <c r="O4">
-        <v>1.296060991105464</v>
+        <v>0.170316301703163</v>
       </c>
       <c r="P4">
-        <v>10.2</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.05399682371625198</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>1.296060991105464</v>
+        <v>-0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>6.33</v>
+        <v>41.7</v>
       </c>
       <c r="V4">
-        <v>0.03350979354155638</v>
+        <v>0.1855807743658211</v>
       </c>
       <c r="W4">
-        <v>0.2925650557620818</v>
+        <v>0.2341880341880342</v>
       </c>
       <c r="X4">
-        <v>0.05253419458295822</v>
+        <v>0.04981714963548235</v>
       </c>
       <c r="Y4">
-        <v>0.2400308611791236</v>
+        <v>0.1843708845525519</v>
       </c>
       <c r="Z4">
-        <v>2.461372619475386</v>
+        <v>20.99690503339305</v>
       </c>
       <c r="AA4">
-        <v>0.1858295984753974</v>
+        <v>1.020935178199234</v>
       </c>
       <c r="AB4">
-        <v>0.04817972807776595</v>
+        <v>0.04981714963548235</v>
       </c>
       <c r="AC4">
-        <v>0.1376498703976314</v>
+        <v>0.9711180285637521</v>
       </c>
       <c r="AD4">
-        <v>118.7</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>118.7</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>112.37</v>
+        <v>-41.7</v>
       </c>
       <c r="AH4">
-        <v>0.385890767230169</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.6019269776876268</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.3729876854648654</v>
+        <v>-0.2278688524590164</v>
       </c>
       <c r="AK4">
-        <v>0.5887253104207052</v>
+        <v>-6.318181818181824</v>
       </c>
       <c r="AL4">
-        <v>7.33</v>
+        <v>0.001</v>
       </c>
       <c r="AM4">
-        <v>7.33</v>
+        <v>-1.419</v>
       </c>
       <c r="AN4">
-        <v>6.087179487179488</v>
+        <v>0</v>
       </c>
       <c r="AO4">
-        <v>2.633015006821283</v>
+        <v>6340</v>
       </c>
       <c r="AP4">
-        <v>5.762564102564103</v>
+        <v>-6.546310832025118</v>
       </c>
       <c r="AQ4">
-        <v>2.633015006821283</v>
+        <v>-4.467935165609584</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +957,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TMX Group Limited (TSX:X)</t>
+          <t>DATA Communications Management Corp. (TSX:DCM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,124 +966,115 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.169</v>
-      </c>
-      <c r="E5">
-        <v>0.193</v>
-      </c>
-      <c r="F5">
-        <v>0.0255</v>
+        <v>0.0423</v>
       </c>
       <c r="G5">
-        <v>0.4629343979675166</v>
+        <v>0.08065074420214607</v>
       </c>
       <c r="H5">
-        <v>0.4513202068777788</v>
+        <v>0.08065074420214607</v>
       </c>
       <c r="I5">
-        <v>0.6248979221486255</v>
+        <v>0.08030460366908966</v>
       </c>
       <c r="J5">
-        <v>0.5215592698588835</v>
+        <v>0.08030460366908966</v>
       </c>
       <c r="K5">
-        <v>384.9</v>
+        <v>-4.3</v>
       </c>
       <c r="L5">
-        <v>0.3492423555031304</v>
+        <v>-0.0148840429214261</v>
       </c>
       <c r="M5">
-        <v>199.8</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.03583663659354654</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.519095869056898</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>132.6</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.02378347353505641</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.3445050662509743</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>67.20000000000002</v>
-      </c>
-      <c r="T5">
-        <v>0.3363363363363364</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>292.1</v>
+        <v>16.5</v>
       </c>
       <c r="V5">
-        <v>0.05239179954441914</v>
+        <v>0.1510989010989011</v>
       </c>
       <c r="W5">
-        <v>0.1324045407636739</v>
+        <v>-0.3282442748091603</v>
       </c>
       <c r="X5">
-        <v>0.04915740525594396</v>
+        <v>0.06453669715327343</v>
       </c>
       <c r="Y5">
-        <v>0.08324713550772993</v>
+        <v>-0.3927809719624337</v>
       </c>
       <c r="Z5">
-        <v>0.3080642907058001</v>
+        <v>5.52601377199694</v>
       </c>
       <c r="AA5">
-        <v>0.1606737865301119</v>
+        <v>0.4437643458301454</v>
       </c>
       <c r="AB5">
-        <v>0.04741369945277707</v>
+        <v>0.04701665483145095</v>
       </c>
       <c r="AC5">
-        <v>0.1132600870773349</v>
+        <v>0.3967476909986944</v>
       </c>
       <c r="AD5">
-        <v>814.3</v>
+        <v>198.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>814.3</v>
+        <v>198.5</v>
       </c>
       <c r="AG5">
-        <v>522.1999999999999</v>
+        <v>182</v>
       </c>
       <c r="AH5">
-        <v>0.1274414673844998</v>
+        <v>0.645108872278193</v>
       </c>
       <c r="AI5">
-        <v>0.2139066932856993</v>
+        <v>0.8656781508940252</v>
       </c>
       <c r="AJ5">
-        <v>0.08564165641656415</v>
+        <v>0.625</v>
       </c>
       <c r="AK5">
-        <v>0.1485759808803027</v>
+        <v>0.8552631578947368</v>
       </c>
       <c r="AL5">
-        <v>330.7</v>
+        <v>8.24</v>
       </c>
       <c r="AM5">
-        <v>329.53</v>
+        <v>8.24</v>
       </c>
       <c r="AN5">
-        <v>1.071024595554386</v>
+        <v>6.98943661971831</v>
       </c>
       <c r="AO5">
-        <v>2.082552162080435</v>
+        <v>2.815533980582524</v>
       </c>
       <c r="AP5">
-        <v>0.6868341444166776</v>
+        <v>6.408450704225352</v>
       </c>
       <c r="AQ5">
-        <v>2.089946287136224</v>
+        <v>2.815533980582524</v>
       </c>
     </row>
     <row r="6">
@@ -1109,7 +1085,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dominion Lending Centres Inc. (TSX:DLCG)</t>
+          <t>TMX Group Limited (TSX:X)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1118,118 +1094,124 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0553</v>
+        <v>0.238</v>
+      </c>
+      <c r="E6">
+        <v>-0.0223</v>
+      </c>
+      <c r="F6">
+        <v>0.0605</v>
       </c>
       <c r="G6">
-        <v>0.6109154929577466</v>
+        <v>0.5066942311478638</v>
       </c>
       <c r="H6">
-        <v>0.6109154929577466</v>
+        <v>0.4990647765308132</v>
       </c>
       <c r="I6">
-        <v>0.4348591549295775</v>
+        <v>0.7689998031108486</v>
       </c>
       <c r="J6">
-        <v>0.2200312989045383</v>
+        <v>0.6147061026471953</v>
       </c>
       <c r="K6">
-        <v>5.58</v>
+        <v>276.3</v>
       </c>
       <c r="L6">
-        <v>0.09823943661971832</v>
+        <v>0.1360011813349085</v>
       </c>
       <c r="M6">
-        <v>7.68</v>
+        <v>173.3</v>
       </c>
       <c r="N6">
-        <v>0.06719160104986877</v>
+        <v>0.0258144280756111</v>
       </c>
       <c r="O6">
-        <v>1.376344086021505</v>
+        <v>0.6272167933405719</v>
       </c>
       <c r="P6">
-        <v>2.12</v>
+        <v>142.9</v>
       </c>
       <c r="Q6">
-        <v>0.01854768153980752</v>
+        <v>0.02128610370458642</v>
       </c>
       <c r="R6">
-        <v>0.3799283154121864</v>
+        <v>0.5171914585595367</v>
       </c>
       <c r="S6">
-        <v>5.56</v>
+        <v>30.40000000000001</v>
       </c>
       <c r="T6">
-        <v>0.7239583333333333</v>
+        <v>0.1754183496826313</v>
       </c>
       <c r="U6">
-        <v>12.6</v>
+        <v>408.4</v>
       </c>
       <c r="V6">
-        <v>0.1102362204724409</v>
+        <v>0.06083446293179211</v>
       </c>
       <c r="W6">
-        <v>0.1430769230769231</v>
+        <v>0.09759457454699587</v>
       </c>
       <c r="X6">
-        <v>0.05484198371379341</v>
+        <v>0.05105399055554019</v>
       </c>
       <c r="Y6">
-        <v>0.08823493936312966</v>
+        <v>0.04654058399145568</v>
       </c>
       <c r="Z6">
-        <v>0.5916666666666666</v>
+        <v>0.6058509527927713</v>
       </c>
       <c r="AA6">
-        <v>0.1301851851851852</v>
+        <v>0.3724202779763343</v>
       </c>
       <c r="AB6">
-        <v>0.04819175039538243</v>
+        <v>0.04867591036782767</v>
       </c>
       <c r="AC6">
-        <v>0.08199343478980273</v>
+        <v>0.3237443676085067</v>
       </c>
       <c r="AD6">
-        <v>109.5</v>
+        <v>1025.4</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>109.5</v>
+        <v>1025.4</v>
       </c>
       <c r="AG6">
-        <v>96.90000000000001</v>
+        <v>617.0000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.4892761394101877</v>
+        <v>0.1325028751599106</v>
       </c>
       <c r="AI6">
-        <v>0.8099112426035504</v>
+        <v>0.2436092369096265</v>
       </c>
       <c r="AJ6">
-        <v>0.4588068181818182</v>
+        <v>0.08417117989713928</v>
       </c>
       <c r="AK6">
-        <v>0.7903752039151712</v>
+        <v>0.1623342454220164</v>
       </c>
       <c r="AL6">
-        <v>24.9</v>
+        <v>1194.7</v>
       </c>
       <c r="AM6">
-        <v>24.9</v>
+        <v>1180</v>
       </c>
       <c r="AN6">
-        <v>3.711864406779661</v>
+        <v>0.6270792563600783</v>
       </c>
       <c r="AO6">
-        <v>0.9919678714859438</v>
+        <v>1.307692307692308</v>
       </c>
       <c r="AP6">
-        <v>3.284745762711865</v>
+        <v>0.3773238747553816</v>
       </c>
       <c r="AQ6">
-        <v>0.9919678714859438</v>
+        <v>1.323983050847457</v>
       </c>
     </row>
     <row r="7">
@@ -1240,7 +1222,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Findev Inc. (TSXV:FDI)</t>
+          <t>Propel Holdings Inc. (TSX:PRL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1249,40 +1231,40 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.1198939929328622</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.1084805653710247</v>
       </c>
       <c r="I7">
-        <v>0.9124423963133641</v>
+        <v>0.1897526501766784</v>
       </c>
       <c r="J7">
-        <v>0.9124423963133641</v>
+        <v>0.1402093290515214</v>
       </c>
       <c r="K7">
-        <v>3.79</v>
+        <v>24.3</v>
       </c>
       <c r="L7">
-        <v>1.746543778801843</v>
+        <v>0.08586572438162544</v>
       </c>
       <c r="M7">
-        <v>0.626</v>
+        <v>9.9</v>
       </c>
       <c r="N7">
-        <v>0.07228637413394919</v>
+        <v>0.02936814001779887</v>
       </c>
       <c r="O7">
-        <v>0.1651715039577836</v>
+        <v>0.4074074074074074</v>
       </c>
       <c r="P7">
-        <v>0.626</v>
+        <v>9.9</v>
       </c>
       <c r="Q7">
-        <v>0.07228637413394919</v>
+        <v>0.02936814001779887</v>
       </c>
       <c r="R7">
-        <v>0.1651715039577836</v>
+        <v>0.4074074074074074</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1291,67 +1273,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.197</v>
+        <v>9.07</v>
       </c>
       <c r="V7">
-        <v>0.02274826789838337</v>
+        <v>0.02690596262236725</v>
       </c>
       <c r="W7">
-        <v>0.2445161290322581</v>
+        <v>0.3095541401273885</v>
       </c>
       <c r="X7">
-        <v>0.04813485421146283</v>
+        <v>0.05400647716106724</v>
       </c>
       <c r="Y7">
-        <v>0.1963812748207952</v>
+        <v>0.2555476629663213</v>
       </c>
       <c r="Z7">
-        <v>0.1420621931260229</v>
+        <v>1.482684549693509</v>
       </c>
       <c r="AA7">
-        <v>0.1296235679214403</v>
+        <v>0.2078862059075839</v>
       </c>
       <c r="AB7">
-        <v>0.04813485421146283</v>
+        <v>0.04833701030497706</v>
       </c>
       <c r="AC7">
-        <v>0.08148871370997743</v>
+        <v>0.1595491956026069</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>174.4</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>174.4</v>
       </c>
       <c r="AG7">
-        <v>-0.197</v>
+        <v>165.33</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.3409579667644184</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>0.6473645137342243</v>
       </c>
       <c r="AJ7">
-        <v>-0.02327779747134586</v>
+        <v>0.3290607646836375</v>
       </c>
       <c r="AK7">
-        <v>-0.01145149101900831</v>
+        <v>0.6350785541428187</v>
       </c>
       <c r="AL7">
-        <v>0.001</v>
+        <v>20.4</v>
       </c>
       <c r="AM7">
-        <v>0.001</v>
+        <v>20.4</v>
+      </c>
+      <c r="AN7">
+        <v>3.235621521335807</v>
       </c>
       <c r="AO7">
-        <v>1980</v>
+        <v>2.632352941176471</v>
+      </c>
+      <c r="AP7">
+        <v>3.06734693877551</v>
       </c>
       <c r="AQ7">
-        <v>1980</v>
+        <v>2.632352941176471</v>
       </c>
     </row>
     <row r="8">
@@ -1362,7 +1350,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Goldmoney Inc. (TSX:XAU)</t>
+          <t>Montfort Capital Corp. (TSXV:MONT)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1370,119 +1358,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D8">
-        <v>-0.0488</v>
-      </c>
       <c r="G8">
-        <v>0.02756967213114754</v>
+        <v>0.4097938144329897</v>
       </c>
       <c r="H8">
-        <v>0.02540983606557377</v>
+        <v>0.4097938144329897</v>
       </c>
       <c r="I8">
-        <v>0.03168032786885246</v>
+        <v>0.6675257731958762</v>
       </c>
       <c r="J8">
-        <v>0.03168032786885246</v>
+        <v>0.6675257731958762</v>
       </c>
       <c r="K8">
-        <v>-2.86</v>
+        <v>-4.95</v>
       </c>
       <c r="L8">
-        <v>-0.01172131147540984</v>
+        <v>-0.1275773195876289</v>
       </c>
       <c r="M8">
-        <v>2.11</v>
+        <v>1.133</v>
       </c>
       <c r="N8">
-        <v>0.02268817204301075</v>
+        <v>0.1197674418604651</v>
       </c>
       <c r="O8">
-        <v>-0.7377622377622377</v>
+        <v>-0.2288888888888889</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>1.06</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.1120507399577167</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>-0.2141414141414141</v>
       </c>
       <c r="S8">
-        <v>2.11</v>
+        <v>0.07299999999999995</v>
       </c>
       <c r="T8">
-        <v>1</v>
+        <v>0.06443071491615177</v>
       </c>
       <c r="U8">
-        <v>20.8</v>
+        <v>4.98</v>
       </c>
       <c r="V8">
-        <v>0.2236559139784946</v>
+        <v>0.5264270613107822</v>
       </c>
       <c r="W8">
-        <v>-0.02015503875968992</v>
+        <v>-0.38671875</v>
       </c>
       <c r="X8">
-        <v>0.04813485421146283</v>
+        <v>0.2520860774648049</v>
       </c>
       <c r="Y8">
-        <v>-0.06828989297115276</v>
+        <v>-0.6388048274648049</v>
       </c>
       <c r="Z8">
-        <v>2.70509977827051</v>
+        <v>0.2455230019616528</v>
       </c>
       <c r="AA8">
-        <v>0.08569844789356984</v>
+        <v>0.1638929317218249</v>
       </c>
       <c r="AB8">
-        <v>0.04813485421146283</v>
+        <v>0.04752933502122827</v>
       </c>
       <c r="AC8">
-        <v>0.03756359368210701</v>
+        <v>0.1163635967005966</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>236.3</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>236.3</v>
       </c>
       <c r="AG8">
-        <v>-20.8</v>
+        <v>231.32</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>0.9615071614583333</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>0.8781122259383128</v>
       </c>
       <c r="AJ8">
-        <v>-0.2880886426592798</v>
+        <v>0.9607110225101753</v>
       </c>
       <c r="AK8">
-        <v>-0.1975308641975309</v>
+        <v>0.8758140239285174</v>
       </c>
       <c r="AL8">
-        <v>0.005</v>
+        <v>26.1</v>
       </c>
       <c r="AM8">
-        <v>-0.517</v>
+        <v>26.1</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>8.6875</v>
       </c>
       <c r="AO8">
-        <v>1546</v>
+        <v>0.9923371647509578</v>
       </c>
       <c r="AP8">
-        <v>-2.427071178529755</v>
+        <v>8.504411764705884</v>
       </c>
       <c r="AQ8">
-        <v>-14.95164410058027</v>
+        <v>0.9923371647509578</v>
       </c>
     </row>
     <row r="9">
@@ -1493,7 +1478,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Solution Financial Inc. (TSX:SFI)</t>
+          <t>Nuvei Corporation (TSX:NVEI)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1501,116 +1486,119 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="F9">
+        <v>0.131</v>
+      </c>
       <c r="G9">
-        <v>0.08918918918918919</v>
+        <v>0.1741526591347478</v>
       </c>
       <c r="H9">
-        <v>0.08918918918918919</v>
+        <v>0.1741526591347478</v>
       </c>
       <c r="I9">
-        <v>0.08851351351351351</v>
+        <v>0.1291448516579407</v>
       </c>
       <c r="J9">
-        <v>0.07573143175749038</v>
+        <v>0.06457242582897033</v>
       </c>
       <c r="K9">
-        <v>0.789</v>
+        <v>-11.6</v>
       </c>
       <c r="L9">
-        <v>0.05331081081081081</v>
+        <v>-0.0106549095251217</v>
       </c>
       <c r="M9">
-        <v>0.6899999999999999</v>
+        <v>127.4</v>
       </c>
       <c r="N9">
-        <v>0.03136363636363636</v>
+        <v>0.0347347183597797</v>
       </c>
       <c r="O9">
-        <v>0.8745247148288973</v>
+        <v>-10.98275862068966</v>
       </c>
       <c r="P9">
-        <v>0.279</v>
+        <v>13.9</v>
       </c>
       <c r="Q9">
-        <v>0.01268181818181818</v>
+        <v>0.003789737717432793</v>
       </c>
       <c r="R9">
-        <v>0.3536121673003803</v>
+        <v>-1.198275862068966</v>
       </c>
       <c r="S9">
-        <v>0.4109999999999999</v>
+        <v>113.5</v>
       </c>
       <c r="T9">
-        <v>0.5956521739130434</v>
+        <v>0.890894819466248</v>
       </c>
       <c r="U9">
-        <v>0.122</v>
+        <v>121</v>
       </c>
       <c r="V9">
-        <v>0.005545454545454545</v>
+        <v>0.03298980315175309</v>
       </c>
       <c r="W9">
-        <v>0.07373831775700936</v>
+        <v>-0.00595482546201232</v>
       </c>
       <c r="X9">
-        <v>0.05076982896842575</v>
+        <v>0.05255520778990053</v>
       </c>
       <c r="Y9">
-        <v>0.02296848878858361</v>
+        <v>-0.05851003325191285</v>
       </c>
       <c r="Z9">
-        <v>0.997977073499663</v>
+        <v>1.794461842755892</v>
       </c>
       <c r="AA9">
-        <v>0.0755782326372797</v>
+        <v>0.1158727542442723</v>
       </c>
       <c r="AB9">
-        <v>0.04816665248696719</v>
+        <v>0.05144722054152346</v>
       </c>
       <c r="AC9">
-        <v>0.0274115801503125</v>
+        <v>0.06442553370274881</v>
       </c>
       <c r="AD9">
-        <v>8.279999999999999</v>
+        <v>1240.2</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>8.279999999999999</v>
+        <v>1240.2</v>
       </c>
       <c r="AG9">
-        <v>8.157999999999999</v>
+        <v>1119.2</v>
       </c>
       <c r="AH9">
-        <v>0.273447820343461</v>
+        <v>0.2526894865525672</v>
       </c>
       <c r="AI9">
-        <v>0.4385593220338983</v>
+        <v>0.3809553064045462</v>
       </c>
       <c r="AJ9">
-        <v>0.2705086544200543</v>
+        <v>0.233799874660539</v>
       </c>
       <c r="AK9">
-        <v>0.434907772683655</v>
+        <v>0.357058542032222</v>
       </c>
       <c r="AL9">
-        <v>0.375</v>
+        <v>86.5</v>
       </c>
       <c r="AM9">
-        <v>0.375</v>
+        <v>70.2</v>
       </c>
       <c r="AN9">
-        <v>6.225563909774436</v>
+        <v>5.099506578947369</v>
       </c>
       <c r="AO9">
-        <v>3.493333333333334</v>
+        <v>1.625433526011561</v>
       </c>
       <c r="AP9">
-        <v>6.133834586466165</v>
+        <v>4.601973684210527</v>
       </c>
       <c r="AQ9">
-        <v>3.493333333333334</v>
+        <v>2.002849002849003</v>
       </c>
     </row>
     <row r="10">
@@ -1621,7 +1609,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>First National Financial Corporation (TSX:FN)</t>
+          <t>Findev Inc. (TSXV:FDI)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1630,10 +1618,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0605</v>
+        <v>-0.223</v>
       </c>
       <c r="E10">
-        <v>-0.0336</v>
+        <v>-0.0513</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1642,34 +1630,34 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>0.918032786885246</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>0.5835682101428435</v>
       </c>
       <c r="K10">
-        <v>143.5</v>
+        <v>1.09</v>
       </c>
       <c r="L10">
-        <v>0.2646624861674658</v>
+        <v>0.4467213114754099</v>
       </c>
       <c r="M10">
-        <v>103</v>
+        <v>0.635</v>
       </c>
       <c r="N10">
-        <v>0.0638284687364442</v>
+        <v>0.07810578105781057</v>
       </c>
       <c r="O10">
-        <v>0.7177700348432056</v>
+        <v>0.5825688073394495</v>
       </c>
       <c r="P10">
-        <v>103</v>
+        <v>0.635</v>
       </c>
       <c r="Q10">
-        <v>0.0638284687364442</v>
+        <v>0.07810578105781057</v>
       </c>
       <c r="R10">
-        <v>0.7177700348432056</v>
+        <v>0.5825688073394495</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1678,61 +1666,67 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>0.02730627306273063</v>
       </c>
       <c r="W10">
-        <v>0.3322528363047002</v>
+        <v>0.06264367816091955</v>
       </c>
       <c r="X10">
-        <v>0.1787473221590779</v>
+        <v>0.04981714963548235</v>
       </c>
       <c r="Y10">
-        <v>0.1535055141456223</v>
+        <v>0.0128265285254372</v>
       </c>
       <c r="Z10">
-        <v>0.01694131468601389</v>
+        <v>0.1418357263268035</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>0.08277082094684289</v>
       </c>
       <c r="AB10">
-        <v>0.0427640296975634</v>
+        <v>0.04981714963548235</v>
       </c>
       <c r="AC10">
-        <v>-0.0427640296975634</v>
+        <v>0.03295367131136055</v>
       </c>
       <c r="AD10">
-        <v>30105</v>
+        <v>0</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>30105</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>30105</v>
+        <v>-0.222</v>
       </c>
       <c r="AH10">
-        <v>0.9491246488664415</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>0.9834828458115816</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>0.9491246488664415</v>
+        <v>-0.02807283763277693</v>
       </c>
       <c r="AK10">
-        <v>0.9834828458115816</v>
+        <v>-0.01241749636424656</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>0.001</v>
+      </c>
+      <c r="AO10">
+        <v>2240</v>
+      </c>
+      <c r="AQ10">
+        <v>2240</v>
       </c>
     </row>
     <row r="11">
@@ -1743,7 +1737,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chesswood Group Limited (TSX:CHW)</t>
+          <t>Dominion Lending Centres Inc. (TSX:DLCG)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1752,109 +1746,118 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.216</v>
-      </c>
-      <c r="E11">
-        <v>0.142</v>
+        <v>-0.0698</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>0.5434298440979956</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>0.5434298440979956</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>0.2628062360801782</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>0.1314031180400891</v>
       </c>
       <c r="K11">
-        <v>21.7</v>
+        <v>0.39</v>
       </c>
       <c r="L11">
-        <v>0.1942703670546106</v>
+        <v>0.00868596881959911</v>
       </c>
       <c r="M11">
-        <v>8.41</v>
+        <v>4.662</v>
       </c>
       <c r="N11">
-        <v>0.05621657754010696</v>
+        <v>0.04557184750733138</v>
       </c>
       <c r="O11">
-        <v>0.3875576036866359</v>
+        <v>11.95384615384615</v>
       </c>
       <c r="P11">
-        <v>5.83</v>
+        <v>4.29</v>
       </c>
       <c r="Q11">
-        <v>0.03897058823529412</v>
+        <v>0.04193548387096774</v>
       </c>
       <c r="R11">
-        <v>0.2686635944700461</v>
+        <v>11</v>
       </c>
       <c r="S11">
-        <v>2.58</v>
+        <v>0.3719999999999999</v>
       </c>
       <c r="T11">
-        <v>0.3067776456599287</v>
+        <v>0.07979407979407976</v>
       </c>
       <c r="U11">
-        <v>9.02</v>
+        <v>5.78</v>
       </c>
       <c r="V11">
-        <v>0.06029411764705882</v>
+        <v>0.05650048875855328</v>
       </c>
       <c r="W11">
-        <v>0.1655225019069413</v>
+        <v>0.01529411764705882</v>
       </c>
       <c r="X11">
-        <v>0.1216795904747341</v>
+        <v>0.0590150157050585</v>
       </c>
       <c r="Y11">
-        <v>0.04384291143220717</v>
+        <v>-0.04372089805799968</v>
       </c>
       <c r="Z11">
-        <v>0.1110073143584036</v>
+        <v>0.572704081632653</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>0.07525510204081633</v>
       </c>
       <c r="AB11">
-        <v>0.04296800257685214</v>
+        <v>0.04750850842850107</v>
       </c>
       <c r="AC11">
-        <v>-0.04296800257685214</v>
+        <v>0.02774659361231525</v>
       </c>
       <c r="AD11">
-        <v>1571.5</v>
+        <v>116.2</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>1571.5</v>
+        <v>116.2</v>
       </c>
       <c r="AG11">
-        <v>1562.48</v>
+        <v>110.42</v>
       </c>
       <c r="AH11">
-        <v>0.9130788449247574</v>
+        <v>0.5318077803203661</v>
       </c>
       <c r="AI11">
-        <v>0.9048770656993148</v>
+        <v>0.8414192614047792</v>
       </c>
       <c r="AJ11">
-        <v>0.9126209055651605</v>
+        <v>0.5190861226024821</v>
       </c>
       <c r="AK11">
-        <v>0.9043804408223745</v>
+        <v>0.8344921402660218</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>2.22</v>
+      </c>
+      <c r="AN11">
+        <v>6.678160919540231</v>
+      </c>
+      <c r="AO11">
+        <v>5.315315315315315</v>
+      </c>
+      <c r="AP11">
+        <v>6.345977011494253</v>
+      </c>
+      <c r="AQ11">
+        <v>5.315315315315315</v>
       </c>
     </row>
     <row r="12">
@@ -1865,7 +1868,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Accord Financial Corp. (TSX:ACD)</t>
+          <t>Automotive Properties Real Estate Investment Trust (TSX:APR.UN)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1874,46 +1877,49 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.104</v>
+        <v>0.147</v>
       </c>
       <c r="E12">
-        <v>0.08410000000000001</v>
+        <v>0.2</v>
+      </c>
+      <c r="F12">
+        <v>0.016</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>0.7297297297297298</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>0.7297297297297298</v>
       </c>
       <c r="I12">
-        <v>0.0001586338727222007</v>
+        <v>0.7792792792792793</v>
       </c>
       <c r="J12">
-        <v>0.0001487830420244864</v>
+        <v>0.7792792792792793</v>
       </c>
       <c r="K12">
-        <v>6.31</v>
+        <v>59</v>
       </c>
       <c r="L12">
-        <v>0.2062091503267974</v>
+        <v>0.885885885885886</v>
       </c>
       <c r="M12">
-        <v>1.71</v>
+        <v>29.2</v>
       </c>
       <c r="N12">
-        <v>0.0351129363449692</v>
+        <v>0.09004008633980881</v>
       </c>
       <c r="O12">
-        <v>0.2709984152139461</v>
+        <v>0.4949152542372881</v>
       </c>
       <c r="P12">
-        <v>1.71</v>
+        <v>29.2</v>
       </c>
       <c r="Q12">
-        <v>0.0351129363449692</v>
+        <v>0.09004008633980881</v>
       </c>
       <c r="R12">
-        <v>0.2709984152139461</v>
+        <v>0.4949152542372881</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1922,67 +1928,73 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>7.07</v>
+        <v>0.253</v>
       </c>
       <c r="V12">
-        <v>0.1451745379876797</v>
+        <v>0.0007801418439716312</v>
       </c>
       <c r="W12">
-        <v>0.08237597911227154</v>
+        <v>0.1571656899307406</v>
       </c>
       <c r="X12">
-        <v>0.0878423523544134</v>
+        <v>0.06154282123457129</v>
       </c>
       <c r="Y12">
-        <v>-0.005466373242141859</v>
+        <v>0.09562286869616927</v>
       </c>
       <c r="Z12">
-        <v>0.09153024325218224</v>
+        <v>0.08365678109808947</v>
       </c>
       <c r="AA12">
-        <v>1.361814802830089e-05</v>
+        <v>0.0651919960809436</v>
       </c>
       <c r="AB12">
-        <v>0.04332432314789308</v>
+        <v>0.04472250741198069</v>
       </c>
       <c r="AC12">
-        <v>-0.04331070499986479</v>
+        <v>0.02046948866896291</v>
       </c>
       <c r="AD12">
-        <v>276.2</v>
+        <v>469.6</v>
       </c>
       <c r="AE12">
-        <v>0.005729017473503295</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>276.2057290174735</v>
+        <v>469.6</v>
       </c>
       <c r="AG12">
-        <v>269.1357290174735</v>
+        <v>469.347</v>
       </c>
       <c r="AH12">
-        <v>0.850110368483589</v>
+        <v>0.5915102657765461</v>
       </c>
       <c r="AI12">
-        <v>0.7730235106416838</v>
+        <v>0.5300824020769839</v>
       </c>
       <c r="AJ12">
-        <v>0.8467761942606439</v>
+        <v>0.5913800467966237</v>
       </c>
       <c r="AK12">
-        <v>0.7684416714779152</v>
+        <v>0.529948162191031</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AN12">
-        <v>46033.33333333333</v>
+        <v>8.996168582375478</v>
+      </c>
+      <c r="AO12">
+        <v>7.10958904109589</v>
       </c>
       <c r="AP12">
-        <v>44855.95483624558</v>
+        <v>8.991321839080459</v>
+      </c>
+      <c r="AQ12">
+        <v>7.10958904109589</v>
       </c>
     </row>
     <row r="13">
@@ -1993,7 +2005,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MCAN Mortgage Corporation (TSX:MKP)</t>
+          <t>Solution Financial Inc. (TSX:SFI)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2002,109 +2014,118 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0665</v>
-      </c>
-      <c r="E13">
-        <v>0.0443</v>
+        <v>0.264</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>0.1051851851851852</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>0.1051851851851852</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>0.08148148148148149</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>0.08148148148148149</v>
       </c>
       <c r="K13">
-        <v>34.5</v>
+        <v>-0.104</v>
       </c>
       <c r="L13">
-        <v>0.5511182108626198</v>
+        <v>-0.007703703703703703</v>
       </c>
       <c r="M13">
-        <v>27.4</v>
+        <v>0.646</v>
       </c>
       <c r="N13">
-        <v>0.07206733298264072</v>
+        <v>0.03182266009852217</v>
       </c>
       <c r="O13">
-        <v>0.7942028985507246</v>
+        <v>-6.211538461538462</v>
       </c>
       <c r="P13">
-        <v>27.4</v>
+        <v>0.266</v>
       </c>
       <c r="Q13">
-        <v>0.07206733298264072</v>
+        <v>0.01310344827586207</v>
       </c>
       <c r="R13">
-        <v>0.7942028985507246</v>
+        <v>-2.557692307692308</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="U13">
-        <v>27.6</v>
+        <v>0.392</v>
       </c>
       <c r="V13">
-        <v>0.07259337190952131</v>
+        <v>0.01931034482758621</v>
       </c>
       <c r="W13">
-        <v>0.110612375761462</v>
+        <v>-0.009811320754716982</v>
       </c>
       <c r="X13">
-        <v>0.07238104544022357</v>
+        <v>0.05325962899485901</v>
       </c>
       <c r="Y13">
-        <v>0.03823133032123845</v>
+        <v>-0.063070949749576</v>
       </c>
       <c r="Z13">
-        <v>0.04247811630589673</v>
+        <v>0.7196929310160999</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>0.05864164623094147</v>
       </c>
       <c r="AB13">
-        <v>0.04374400729351936</v>
+        <v>0.04852216648273895</v>
       </c>
       <c r="AC13">
-        <v>-0.04374400729351936</v>
+        <v>0.01011947974820252</v>
       </c>
       <c r="AD13">
-        <v>1316.7</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>1316.7</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="AG13">
-        <v>1289.1</v>
+        <v>8.238000000000001</v>
       </c>
       <c r="AH13">
-        <v>0.7759443691437327</v>
+        <v>0.2983062564811614</v>
       </c>
       <c r="AI13">
-        <v>0.8032576866764275</v>
+        <v>0.4713271436373566</v>
       </c>
       <c r="AJ13">
-        <v>0.7722398610195891</v>
+        <v>0.288667741257271</v>
       </c>
       <c r="AK13">
-        <v>0.7998883097542815</v>
+        <v>0.4597611340551402</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="AN13">
+        <v>-176.1224489795918</v>
+      </c>
+      <c r="AO13">
+        <v>1.598837209302326</v>
+      </c>
+      <c r="AP13">
+        <v>-168.1224489795919</v>
+      </c>
+      <c r="AQ13">
+        <v>1.598837209302326</v>
       </c>
     </row>
     <row r="14">
@@ -2115,7 +2136,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Timbercreek Financial Corp. (TSX:TF)</t>
+          <t>First National Financial Corporation (TSX:FN)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2124,10 +2145,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>-0.00275</v>
+        <v>0.0951</v>
       </c>
       <c r="E14">
-        <v>-0.0366</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2142,85 +2163,85 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>31.7</v>
+        <v>185.7</v>
       </c>
       <c r="L14">
-        <v>0.673036093418259</v>
+        <v>0.3391780821917808</v>
       </c>
       <c r="M14">
-        <v>38.98</v>
+        <v>104.2</v>
       </c>
       <c r="N14">
-        <v>0.08834995466908431</v>
+        <v>0.05978884553591921</v>
       </c>
       <c r="O14">
-        <v>1.229652996845426</v>
+        <v>0.5611200861604739</v>
       </c>
       <c r="P14">
-        <v>37.9</v>
+        <v>104.2</v>
       </c>
       <c r="Q14">
-        <v>0.08590208522212149</v>
+        <v>0.05978884553591921</v>
       </c>
       <c r="R14">
-        <v>1.195583596214511</v>
+        <v>0.5611200861604739</v>
       </c>
       <c r="S14">
-        <v>1.079999999999998</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>0.02770651616213439</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>0.003263825929283772</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>0.0582078589790672</v>
+        <v>0.4271911663216011</v>
       </c>
       <c r="X14">
-        <v>0.06378744973648595</v>
+        <v>0.2007086865849451</v>
       </c>
       <c r="Y14">
-        <v>-0.005579590757418748</v>
+        <v>0.226482479736656</v>
       </c>
       <c r="Z14">
-        <v>0.03634592991177431</v>
+        <v>0.01789864951011642</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.04422496695414514</v>
+        <v>0.04164288259959562</v>
       </c>
       <c r="AC14">
-        <v>-0.04422496695414514</v>
+        <v>-0.04164288259959562</v>
       </c>
       <c r="AD14">
-        <v>986.4</v>
+        <v>32475.5</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>986.4</v>
+        <v>32475.5</v>
       </c>
       <c r="AG14">
-        <v>984.9599999999999</v>
+        <v>32475.5</v>
       </c>
       <c r="AH14">
-        <v>0.6909498458952088</v>
+        <v>0.9490681886592846</v>
       </c>
       <c r="AI14">
-        <v>0.6595787362086258</v>
+        <v>0.9820467383547229</v>
       </c>
       <c r="AJ14">
-        <v>0.6906377966006619</v>
+        <v>0.9490681886592846</v>
       </c>
       <c r="AK14">
-        <v>0.6592506325047186</v>
+        <v>0.9820467383547229</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2237,7 +2258,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Atrium Mortgage Investment Corporation (TSX:AI)</t>
+          <t>Accord Financial Corp. (TSX:ACD)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2246,10 +2267,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.09970000000000001</v>
-      </c>
-      <c r="E15">
-        <v>0.09429999999999999</v>
+        <v>-0.0434</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2264,28 +2282,28 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>31.9</v>
+        <v>-7.92</v>
       </c>
       <c r="L15">
-        <v>0.7915632754342432</v>
+        <v>-0.3882352941176471</v>
       </c>
       <c r="M15">
-        <v>24.5</v>
+        <v>1.9</v>
       </c>
       <c r="N15">
-        <v>0.07138694638694638</v>
+        <v>0.06354515050167224</v>
       </c>
       <c r="O15">
-        <v>0.768025078369906</v>
+        <v>-0.2398989898989899</v>
       </c>
       <c r="P15">
-        <v>24.5</v>
+        <v>1.9</v>
       </c>
       <c r="Q15">
-        <v>0.07138694638694638</v>
+        <v>0.06354515050167224</v>
       </c>
       <c r="R15">
-        <v>0.768025078369906</v>
+        <v>-0.2398989898989899</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2294,55 +2312,55 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>4.33</v>
+        <v>4.09</v>
       </c>
       <c r="V15">
-        <v>0.01261655011655012</v>
+        <v>0.1367892976588629</v>
       </c>
       <c r="W15">
-        <v>0.0859375</v>
+        <v>-0.1029908972691807</v>
       </c>
       <c r="X15">
-        <v>0.0538181810980746</v>
+        <v>0.1329868650199848</v>
       </c>
       <c r="Y15">
-        <v>0.0321193189019254</v>
+        <v>-0.2359777622891656</v>
       </c>
       <c r="Z15">
-        <v>0.06651262584584915</v>
+        <v>0.06076311321597712</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.04559944476175491</v>
+        <v>0.04196838474658025</v>
       </c>
       <c r="AC15">
-        <v>-0.04559944476175491</v>
+        <v>-0.04196838474658025</v>
       </c>
       <c r="AD15">
-        <v>278.6</v>
+        <v>307.1</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>278.6</v>
+        <v>307.1</v>
       </c>
       <c r="AG15">
-        <v>274.27</v>
+        <v>303.01</v>
       </c>
       <c r="AH15">
-        <v>0.4480540366677389</v>
+        <v>0.9112759643916915</v>
       </c>
       <c r="AI15">
-        <v>0.4432776451869531</v>
+        <v>0.8102902374670186</v>
       </c>
       <c r="AJ15">
-        <v>0.4441835230861419</v>
+        <v>0.9101859361388964</v>
       </c>
       <c r="AK15">
-        <v>0.4394155438422225</v>
+        <v>0.8082206396201754</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2359,7 +2377,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Firm Capital Mortgage Investment Corporation (TSX:FC)</t>
+          <t>MCAN Mortgage Corporation (TSX:MKP)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2368,10 +2386,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.109</v>
+        <v>0.13</v>
       </c>
       <c r="E16">
-        <v>0.0587</v>
+        <v>0.134</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2386,28 +2404,28 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>23.3</v>
+        <v>60.4</v>
       </c>
       <c r="L16">
-        <v>0.7491961414790996</v>
+        <v>0.6522678185745141</v>
       </c>
       <c r="M16">
-        <v>23.3</v>
+        <v>26.1</v>
       </c>
       <c r="N16">
-        <v>0.08553597650513951</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="O16">
-        <v>1</v>
+        <v>0.4321192052980133</v>
       </c>
       <c r="P16">
-        <v>23.3</v>
+        <v>26.1</v>
       </c>
       <c r="Q16">
-        <v>0.08553597650513951</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="R16">
-        <v>1</v>
+        <v>0.4321192052980133</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2416,55 +2434,55 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>37.3</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>0.08749706779263429</v>
       </c>
       <c r="W16">
-        <v>0.08309557774607704</v>
+        <v>0.1872868217054263</v>
       </c>
       <c r="X16">
-        <v>0.05242189628875358</v>
+        <v>0.07660211980960933</v>
       </c>
       <c r="Y16">
-        <v>0.03067368145732346</v>
+        <v>0.110684701895817</v>
       </c>
       <c r="Z16">
-        <v>0.06929590017825313</v>
+        <v>0.05745842640853809</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.04598577993865317</v>
+        <v>0.04320360890074953</v>
       </c>
       <c r="AC16">
-        <v>-0.04598577993865317</v>
+        <v>-0.04320360890074953</v>
       </c>
       <c r="AD16">
-        <v>166.8</v>
+        <v>1410.1</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>166.8</v>
+        <v>1410.1</v>
       </c>
       <c r="AG16">
-        <v>166.8</v>
+        <v>1372.8</v>
       </c>
       <c r="AH16">
-        <v>0.3797814207650274</v>
+        <v>0.7678610324548029</v>
       </c>
       <c r="AI16">
-        <v>0.3645901639344263</v>
+        <v>0.7833018553494057</v>
       </c>
       <c r="AJ16">
-        <v>0.3797814207650274</v>
+        <v>0.7630481907620477</v>
       </c>
       <c r="AK16">
-        <v>0.3645901639344263</v>
+        <v>0.7787168869476431</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2481,7 +2499,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ECN Capital Corp. (TSX:ECN)</t>
+          <t>Timbercreek Financial Corp. (TSX:TF)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2490,10 +2508,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.172</v>
+        <v>0.0517</v>
       </c>
       <c r="E17">
-        <v>0.7759999999999999</v>
+        <v>0.0551</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2508,85 +2526,85 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>943.4</v>
+        <v>49</v>
       </c>
       <c r="L17">
-        <v>3.997457627118644</v>
+        <v>0.7852564102564102</v>
       </c>
       <c r="M17">
-        <v>16.1098</v>
+        <v>46.47</v>
       </c>
       <c r="N17">
-        <v>0.03189427836072065</v>
+        <v>0.1104062722736992</v>
       </c>
       <c r="O17">
-        <v>0.01707631969472122</v>
+        <v>0.9483673469387754</v>
       </c>
       <c r="P17">
-        <v>5.4098</v>
+        <v>38.4</v>
       </c>
       <c r="Q17">
-        <v>0.01071035438527024</v>
+        <v>0.09123307198859587</v>
       </c>
       <c r="R17">
-        <v>0.005734365062539749</v>
+        <v>0.7836734693877551</v>
       </c>
       <c r="S17">
-        <v>10.7</v>
+        <v>8.07</v>
       </c>
       <c r="T17">
-        <v>0.6641919825199567</v>
+        <v>0.1736604260813428</v>
       </c>
       <c r="U17">
-        <v>19.1</v>
+        <v>24.5</v>
       </c>
       <c r="V17">
-        <v>0.03781429419916849</v>
+        <v>0.05820860061772393</v>
       </c>
       <c r="W17">
-        <v>1.374617514206615</v>
+        <v>0.09624828128069141</v>
       </c>
       <c r="X17">
-        <v>0.06226881407994726</v>
+        <v>0.06577187477598734</v>
       </c>
       <c r="Y17">
-        <v>1.312348700126668</v>
+        <v>0.03047640650470407</v>
       </c>
       <c r="Z17">
-        <v>0.207582021285953</v>
+        <v>0.04176539094815469</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.0482126200103498</v>
+        <v>0.04410389507255884</v>
       </c>
       <c r="AC17">
-        <v>-0.0482126200103498</v>
+        <v>-0.04410389507255884</v>
       </c>
       <c r="AD17">
-        <v>1019.7</v>
+        <v>829.3</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>1019.7</v>
+        <v>829.3</v>
       </c>
       <c r="AG17">
-        <v>1000.6</v>
+        <v>804.8</v>
       </c>
       <c r="AH17">
-        <v>0.6687434417628541</v>
+        <v>0.6633338665813471</v>
       </c>
       <c r="AI17">
-        <v>0.8315935410210407</v>
+        <v>0.6148884110625047</v>
       </c>
       <c r="AJ17">
-        <v>0.6645414093112838</v>
+        <v>0.656604389328547</v>
       </c>
       <c r="AK17">
-        <v>0.8289288377102146</v>
+        <v>0.6077631777677088</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2603,7 +2621,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Home Capital Group Inc. (TSX:HCG)</t>
+          <t>Chesswood Group Limited (TSX:CHW)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2612,10 +2630,10 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.08890000000000001</v>
+        <v>0.163</v>
       </c>
       <c r="E18">
-        <v>0.4379999999999999</v>
+        <v>-0.197</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2630,85 +2648,85 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>123.5</v>
+        <v>7.1</v>
       </c>
       <c r="L18">
-        <v>0.3461322869955157</v>
+        <v>0.0715005035246727</v>
       </c>
       <c r="M18">
-        <v>343.8</v>
+        <v>10.28</v>
       </c>
       <c r="N18">
-        <v>0.2845084409136048</v>
+        <v>0.09073256840247131</v>
       </c>
       <c r="O18">
-        <v>2.783805668016194</v>
+        <v>1.447887323943662</v>
       </c>
       <c r="P18">
-        <v>13.6</v>
+        <v>8.33</v>
       </c>
       <c r="Q18">
-        <v>0.01125455147302218</v>
+        <v>0.0735216240070609</v>
       </c>
       <c r="R18">
-        <v>0.1101214574898785</v>
+        <v>1.173239436619718</v>
       </c>
       <c r="S18">
-        <v>330.2</v>
+        <v>1.949999999999999</v>
       </c>
       <c r="T18">
-        <v>0.9604421175101803</v>
+        <v>0.1896887159533073</v>
       </c>
       <c r="U18">
-        <v>321.4</v>
+        <v>10.9</v>
       </c>
       <c r="V18">
-        <v>0.2659715326050976</v>
+        <v>0.09620476610767874</v>
       </c>
       <c r="W18">
-        <v>0.086032741205155</v>
+        <v>0.04637491835401698</v>
       </c>
       <c r="X18">
-        <v>0.06890884456686323</v>
+        <v>0.1598816833724856</v>
       </c>
       <c r="Y18">
-        <v>0.01712389663829177</v>
+        <v>-0.1135067650184686</v>
       </c>
       <c r="Z18">
-        <v>0.09890231733008095</v>
+        <v>0.0590937764077173</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.04822182890584012</v>
+        <v>0.04577352520782834</v>
       </c>
       <c r="AC18">
-        <v>-0.04822182890584012</v>
+        <v>-0.04577352520782834</v>
       </c>
       <c r="AD18">
-        <v>3585.6</v>
+        <v>1540</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>3585.6</v>
+        <v>1540</v>
       </c>
       <c r="AG18">
-        <v>3264.2</v>
+        <v>1529.1</v>
       </c>
       <c r="AH18">
-        <v>0.7479349186483104</v>
+        <v>0.9314703925482369</v>
       </c>
       <c r="AI18">
-        <v>0.7632508833922261</v>
+        <v>0.9021146974401032</v>
       </c>
       <c r="AJ18">
-        <v>0.7298215802888699</v>
+        <v>0.9310155869459328</v>
       </c>
       <c r="AK18">
-        <v>0.7458641806050635</v>
+        <v>0.9014856738592147</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2725,7 +2743,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EQB Inc. (TSX:EQB)</t>
+          <t>Atrium Mortgage Investment Corporation (TSX:AI)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2734,10 +2752,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.154</v>
+        <v>0.09210000000000002</v>
       </c>
       <c r="E19">
-        <v>0.135</v>
+        <v>0.098</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2752,28 +2770,28 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>221.7</v>
+        <v>39.1</v>
       </c>
       <c r="L19">
-        <v>0.4284885968303054</v>
+        <v>0.8390557939914163</v>
       </c>
       <c r="M19">
-        <v>26.5</v>
+        <v>25.7</v>
       </c>
       <c r="N19">
-        <v>0.01684464785151284</v>
+        <v>0.07347055460263006</v>
       </c>
       <c r="O19">
-        <v>0.1195308976093821</v>
+        <v>0.6572890025575447</v>
       </c>
       <c r="P19">
-        <v>26.5</v>
+        <v>25.7</v>
       </c>
       <c r="Q19">
-        <v>0.01684464785151284</v>
+        <v>0.07347055460263006</v>
       </c>
       <c r="R19">
-        <v>0.1195308976093821</v>
+        <v>0.6572890025575447</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2782,55 +2800,55 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>217.8</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>0.1384439359267735</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>0.1557210086394605</v>
+        <v>0.1117462132037725</v>
       </c>
       <c r="X19">
-        <v>0.09157646027106217</v>
+        <v>0.05606976000043283</v>
       </c>
       <c r="Y19">
-        <v>0.06414454836839836</v>
+        <v>0.05567645320333969</v>
       </c>
       <c r="Z19">
-        <v>0.04820332224675554</v>
+        <v>0.07465914734767773</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.04823500082034399</v>
+        <v>0.04606435886215744</v>
       </c>
       <c r="AC19">
-        <v>-0.04823500082034399</v>
+        <v>-0.04606435886215744</v>
       </c>
       <c r="AD19">
-        <v>9761.6</v>
+        <v>270.1</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>9761.6</v>
+        <v>270.1</v>
       </c>
       <c r="AG19">
-        <v>9543.800000000001</v>
+        <v>270.1</v>
       </c>
       <c r="AH19">
-        <v>0.8612061968451141</v>
+        <v>0.4357154379738667</v>
       </c>
       <c r="AI19">
-        <v>0.8611074355377952</v>
+        <v>0.4262941919191919</v>
       </c>
       <c r="AJ19">
-        <v>0.8584870018889987</v>
+        <v>0.4357154379738667</v>
       </c>
       <c r="AK19">
-        <v>0.8583866238543663</v>
+        <v>0.4262941919191919</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2847,7 +2865,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IOU Financial Inc. (TSXV:IOU)</t>
+          <t>Firm Capital Mortgage Investment Corporation (TSX:FC)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2856,7 +2874,10 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.366</v>
+        <v>0.08650000000000001</v>
+      </c>
+      <c r="E20">
+        <v>0.0556</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2871,82 +2892,85 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>2.46</v>
+        <v>25</v>
       </c>
       <c r="L20">
-        <v>0.1651006711409396</v>
+        <v>0.728862973760933</v>
       </c>
       <c r="M20">
-        <v>-0</v>
+        <v>24.2</v>
       </c>
       <c r="N20">
-        <v>-0</v>
+        <v>0.08548216178028964</v>
       </c>
       <c r="O20">
-        <v>-0</v>
+        <v>0.968</v>
       </c>
       <c r="P20">
-        <v>-0</v>
+        <v>24.2</v>
       </c>
       <c r="Q20">
-        <v>-0</v>
+        <v>0.08548216178028964</v>
       </c>
       <c r="R20">
-        <v>-0</v>
+        <v>0.968</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
       <c r="U20">
-        <v>8.07</v>
+        <v>34.3</v>
       </c>
       <c r="V20">
-        <v>0.6725</v>
+        <v>0.121158601200989</v>
       </c>
       <c r="W20">
-        <v>0.2084745762711864</v>
+        <v>0.08599931200550395</v>
       </c>
       <c r="X20">
-        <v>0.05084196193278705</v>
+        <v>0.05415627600701701</v>
       </c>
       <c r="Y20">
-        <v>0.1576326143383994</v>
+        <v>0.03184303599848694</v>
       </c>
       <c r="Z20">
-        <v>1.347197106690778</v>
+        <v>0.07497267759562841</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.0489619917784522</v>
+        <v>0.04681212906183652</v>
       </c>
       <c r="AC20">
-        <v>-0.0489619917784522</v>
+        <v>-0.04681212906183652</v>
       </c>
       <c r="AD20">
-        <v>4.64</v>
+        <v>151.7</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>4.64</v>
+        <v>151.7</v>
       </c>
       <c r="AG20">
-        <v>-3.430000000000001</v>
+        <v>117.4</v>
       </c>
       <c r="AH20">
-        <v>0.2788461538461538</v>
+        <v>0.3488960441582336</v>
       </c>
       <c r="AI20">
-        <v>0.2399172699069286</v>
+        <v>0.3386160714285714</v>
       </c>
       <c r="AJ20">
-        <v>-0.4002333722287049</v>
+        <v>0.2931335830212234</v>
       </c>
       <c r="AK20">
-        <v>-0.3043478260869566</v>
+        <v>0.2837805172830554</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -2963,7 +2987,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Axis Auto Finance Inc. (TSX:AXIS)</t>
+          <t>ECN Capital Corp. (TSX:ECN)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2972,7 +2996,7 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.399</v>
+        <v>0.331</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2981,103 +3005,97 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0.008352329187353321</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>0.008352329187353321</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>-0.054</v>
+        <v>-59.3</v>
       </c>
       <c r="L21">
-        <v>-0.003913043478260869</v>
+        <v>-0.5356820234869015</v>
       </c>
       <c r="M21">
-        <v>2.85</v>
+        <v>7.32</v>
       </c>
       <c r="N21">
-        <v>0.06581986143187067</v>
+        <v>0.01151124390627457</v>
       </c>
       <c r="O21">
-        <v>-52.77777777777778</v>
+        <v>-0.1234401349072513</v>
       </c>
       <c r="P21">
-        <v>-0</v>
+        <v>7.32</v>
       </c>
       <c r="Q21">
-        <v>-0</v>
+        <v>0.01151124390627457</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>-0.1234401349072513</v>
       </c>
       <c r="S21">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>2.39</v>
+        <v>23.8</v>
       </c>
       <c r="V21">
-        <v>0.05519630484988453</v>
+        <v>0.03742726843843372</v>
       </c>
       <c r="W21">
-        <v>-0.001849315068493151</v>
+        <v>-0.425089605734767</v>
       </c>
       <c r="X21">
-        <v>0.06574905945060838</v>
+        <v>0.06055962418003698</v>
       </c>
       <c r="Y21">
-        <v>-0.06759837451910153</v>
+        <v>-0.485649229914804</v>
       </c>
       <c r="Z21">
-        <v>0.1323630681960191</v>
+        <v>0.1023105360443623</v>
       </c>
       <c r="AA21">
-        <v>0.001105539917821249</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.05025746416766542</v>
+        <v>0.04734187519167659</v>
       </c>
       <c r="AC21">
-        <v>-0.04915192424984417</v>
+        <v>-0.04734187519167659</v>
       </c>
       <c r="AD21">
-        <v>108.7</v>
+        <v>843.6</v>
       </c>
       <c r="AE21">
-        <v>0.2386892860726209</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>108.9386892860726</v>
+        <v>843.6</v>
       </c>
       <c r="AG21">
-        <v>106.5486892860726</v>
+        <v>819.8000000000001</v>
       </c>
       <c r="AH21">
-        <v>0.7155782133762679</v>
+        <v>0.5701926326461643</v>
       </c>
       <c r="AI21">
-        <v>0.7490351420301524</v>
+        <v>0.7619219653179191</v>
       </c>
       <c r="AJ21">
-        <v>0.7110418502404318</v>
+        <v>0.5631654873943808</v>
       </c>
       <c r="AK21">
-        <v>0.7448421220623258</v>
+        <v>0.7566918958833303</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
         <v>0</v>
-      </c>
-      <c r="AN21">
-        <v>666.8711656441718</v>
-      </c>
-      <c r="AP21">
-        <v>653.6729404053535</v>
       </c>
     </row>
     <row r="22">
@@ -3088,7 +3106,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Element Fleet Management Corp. (TSX:EFN)</t>
+          <t>Axis Auto Finance Inc. (TSX:AXIS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3097,10 +3115,7 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.0337</v>
-      </c>
-      <c r="E22">
-        <v>0.0399</v>
+        <v>-0.08199999999999999</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3115,85 +3130,85 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>293.6</v>
+        <v>-20.4</v>
       </c>
       <c r="L22">
-        <v>0.2489401390537561</v>
+        <v>-3.756906077348066</v>
       </c>
       <c r="M22">
-        <v>296.705</v>
+        <v>0.831</v>
       </c>
       <c r="N22">
-        <v>0.0554557688353924</v>
+        <v>0.1814410480349345</v>
       </c>
       <c r="O22">
-        <v>1.010575613079019</v>
+        <v>-0.04073529411764706</v>
       </c>
       <c r="P22">
-        <v>88.705</v>
+        <v>-0</v>
       </c>
       <c r="Q22">
-        <v>0.01657944414331906</v>
+        <v>-0</v>
       </c>
       <c r="R22">
-        <v>0.3021287465940054</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>208</v>
+        <v>0.831</v>
       </c>
       <c r="T22">
-        <v>0.7010330125882611</v>
+        <v>1</v>
       </c>
       <c r="U22">
-        <v>40.1</v>
+        <v>2.7</v>
       </c>
       <c r="V22">
-        <v>0.007494906827654524</v>
+        <v>0.5895196506550219</v>
       </c>
       <c r="W22">
-        <v>0.1242225513010366</v>
+        <v>-0.558904109589041</v>
       </c>
       <c r="X22">
-        <v>0.05638867078589178</v>
+        <v>0.2964581747446731</v>
       </c>
       <c r="Y22">
-        <v>0.06783388051514483</v>
+        <v>-0.8553622843337141</v>
       </c>
       <c r="Z22">
-        <v>0.1384109846262176</v>
+        <v>0.04183036746013404</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.04973978720916776</v>
+        <v>0.0475133812488243</v>
       </c>
       <c r="AC22">
-        <v>-0.04973978720916776</v>
+        <v>-0.0475133812488243</v>
       </c>
       <c r="AD22">
-        <v>6307.6</v>
+        <v>139.5</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>6307.6</v>
+        <v>139.5</v>
       </c>
       <c r="AG22">
-        <v>6267.5</v>
+        <v>136.8</v>
       </c>
       <c r="AH22">
-        <v>0.5410579950076772</v>
+        <v>0.9682121043864519</v>
       </c>
       <c r="AI22">
-        <v>0.7071776128439132</v>
+        <v>0.8953786906290115</v>
       </c>
       <c r="AJ22">
-        <v>0.5394739107232006</v>
+        <v>0.9676050360729946</v>
       </c>
       <c r="AK22">
-        <v>0.7058551912876015</v>
+        <v>0.8935336381450032</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3210,7 +3225,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Terra Firma Capital Corporation (TSXV:TII)</t>
+          <t>Marble Financial Inc. (CNSX:MRBL)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3218,14 +3233,8 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D23">
-        <v>0.104</v>
-      </c>
-      <c r="E23">
-        <v>0.328</v>
-      </c>
       <c r="G23">
-        <v>0</v>
+        <v>0.08208955223880597</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -3237,85 +3246,82 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>2.67</v>
+        <v>-1.31</v>
       </c>
       <c r="L23">
-        <v>0.3593539703903096</v>
+        <v>-3.258706467661692</v>
       </c>
       <c r="M23">
-        <v>1.01</v>
+        <v>-0</v>
       </c>
       <c r="N23">
-        <v>0.04590909090909091</v>
+        <v>-0</v>
       </c>
       <c r="O23">
-        <v>0.3782771535580525</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>1.01</v>
+        <v>-0</v>
       </c>
       <c r="Q23">
-        <v>0.04590909090909091</v>
+        <v>-0</v>
       </c>
       <c r="R23">
-        <v>0.3782771535580525</v>
+        <v>0</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
       <c r="U23">
-        <v>13</v>
+        <v>0.013</v>
       </c>
       <c r="V23">
-        <v>0.5909090909090909</v>
+        <v>0.002333931777378815</v>
       </c>
       <c r="W23">
-        <v>0.06282352941176471</v>
+        <v>0.3385012919896641</v>
       </c>
       <c r="X23">
-        <v>0.07652129724541118</v>
+        <v>0.05144539336616979</v>
       </c>
       <c r="Y23">
-        <v>-0.01369776783364647</v>
+        <v>0.2870558986234943</v>
       </c>
       <c r="Z23">
-        <v>0.05457617158807111</v>
+        <v>1.552123552123551</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.05051428542625042</v>
+        <v>0.05032383166660176</v>
       </c>
       <c r="AC23">
-        <v>-0.05051428542625042</v>
+        <v>-0.05032383166660176</v>
       </c>
       <c r="AD23">
-        <v>89.2</v>
+        <v>1.12</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>89.2</v>
+        <v>1.12</v>
       </c>
       <c r="AG23">
-        <v>76.2</v>
+        <v>1.107</v>
       </c>
       <c r="AH23">
-        <v>0.802158273381295</v>
+        <v>0.1674140508221226</v>
       </c>
       <c r="AI23">
-        <v>0.6686656671664167</v>
+        <v>1.851239669421487</v>
       </c>
       <c r="AJ23">
-        <v>0.7759674134419552</v>
+        <v>0.1657930208177325</v>
       </c>
       <c r="AK23">
-        <v>0.632890365448505</v>
+        <v>1.869932432432432</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3332,7 +3338,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Marble Financial Inc. (CNSX:MRBL)</t>
+          <t>Mogo Inc. (TSX:MOGO)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3340,8 +3346,11 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D24">
+        <v>0.101</v>
+      </c>
       <c r="G24">
-        <v>0.4621848739495799</v>
+        <v>0.4086687306501548</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -3353,19 +3362,19 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>-3.3</v>
+        <v>-74.90000000000001</v>
       </c>
       <c r="L24">
-        <v>-27.73109243697479</v>
+        <v>-2.318885448916409</v>
       </c>
       <c r="M24">
-        <v>0.073</v>
+        <v>1</v>
       </c>
       <c r="N24">
-        <v>0.01084695393759287</v>
+        <v>0.02212389380530973</v>
       </c>
       <c r="O24">
-        <v>-0.02212121212121212</v>
+        <v>-0.01335113484646195</v>
       </c>
       <c r="P24">
         <v>-0</v>
@@ -3377,61 +3386,61 @@
         <v>0</v>
       </c>
       <c r="S24">
-        <v>0.073</v>
+        <v>1</v>
       </c>
       <c r="T24">
         <v>1</v>
       </c>
       <c r="U24">
-        <v>0.101</v>
+        <v>13.1</v>
       </c>
       <c r="V24">
-        <v>0.0150074294205052</v>
+        <v>0.2898230088495575</v>
       </c>
       <c r="W24">
-        <v>1.11864406779661</v>
+        <v>-0.5515463917525774</v>
       </c>
       <c r="X24">
-        <v>0.05358596521459046</v>
+        <v>0.06126486995306822</v>
       </c>
       <c r="Y24">
-        <v>1.06505810258202</v>
+        <v>-0.6128112617056456</v>
       </c>
       <c r="Z24">
-        <v>0.05343511450381679</v>
+        <v>0.2553359683794466</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.05314340400118578</v>
+        <v>0.0515897862087872</v>
       </c>
       <c r="AC24">
-        <v>-0.05314340400118578</v>
+        <v>-0.0515897862087872</v>
       </c>
       <c r="AD24">
-        <v>5.24</v>
+        <v>63.9</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>5.24</v>
+        <v>63.9</v>
       </c>
       <c r="AG24">
-        <v>5.139</v>
+        <v>50.8</v>
       </c>
       <c r="AH24">
-        <v>0.4377610693400167</v>
+        <v>0.5857011915673694</v>
       </c>
       <c r="AI24">
-        <v>3.824817518248175</v>
+        <v>0.5031496062992126</v>
       </c>
       <c r="AJ24">
-        <v>0.4329766618923246</v>
+        <v>0.5291666666666667</v>
       </c>
       <c r="AK24">
-        <v>4.049645390070922</v>
+        <v>0.4460052677787533</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3457,16 +3466,13 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.163</v>
+        <v>0.166</v>
       </c>
       <c r="E25">
-        <v>0.328</v>
-      </c>
-      <c r="F25">
-        <v>0.26</v>
+        <v>0.365</v>
       </c>
       <c r="G25">
-        <v>0.03391684901531729</v>
+        <v>0.04022112085398399</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -3478,91 +3484,91 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>117.7</v>
+        <v>149.2</v>
       </c>
       <c r="L25">
-        <v>0.2575492341356674</v>
+        <v>0.2844071673656118</v>
       </c>
       <c r="M25">
-        <v>132.4</v>
+        <v>50.6</v>
       </c>
       <c r="N25">
-        <v>0.1023975251353442</v>
+        <v>0.025429691426274</v>
       </c>
       <c r="O25">
-        <v>1.124893797790994</v>
+        <v>0.3391420911528151</v>
       </c>
       <c r="P25">
-        <v>34.9</v>
+        <v>44.1</v>
       </c>
       <c r="Q25">
-        <v>0.02699149265274555</v>
+        <v>0.02216303146044829</v>
       </c>
       <c r="R25">
-        <v>0.2965165675446049</v>
+        <v>0.2955764075067024</v>
       </c>
       <c r="S25">
-        <v>97.5</v>
+        <v>6.5</v>
       </c>
       <c r="T25">
-        <v>0.736404833836858</v>
+        <v>0.1284584980237154</v>
       </c>
       <c r="U25">
-        <v>53.9</v>
+        <v>62.1</v>
       </c>
       <c r="V25">
-        <v>0.04168600154679041</v>
+        <v>0.03120916675042718</v>
       </c>
       <c r="W25">
-        <v>0.1843382928739233</v>
+        <v>0.2586685159500693</v>
       </c>
       <c r="X25">
-        <v>0.05679612613527718</v>
+        <v>0.05808933862285447</v>
       </c>
       <c r="Y25">
-        <v>0.1275421667386461</v>
+        <v>0.2005791773272149</v>
       </c>
       <c r="Z25">
-        <v>0.2889661713563073</v>
+        <v>0.2635253930778119</v>
       </c>
       <c r="AA25">
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.05740656540583329</v>
+        <v>0.05307699168496105</v>
       </c>
       <c r="AC25">
-        <v>-0.05740656540583329</v>
+        <v>-0.05307699168496105</v>
       </c>
       <c r="AD25">
-        <v>1599.6</v>
+        <v>2032.7</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>1599.6</v>
+        <v>2032.7</v>
       </c>
       <c r="AG25">
-        <v>1545.7</v>
+        <v>1970.6</v>
       </c>
       <c r="AH25">
-        <v>0.5529973034640115</v>
+        <v>0.5053325046612803</v>
       </c>
       <c r="AI25">
-        <v>0.7349751883844883</v>
+        <v>0.7308978461759735</v>
       </c>
       <c r="AJ25">
-        <v>0.5445098108289005</v>
+        <v>0.4975760024239976</v>
       </c>
       <c r="AK25">
-        <v>0.7282449941107184</v>
+        <v>0.7247517469657963</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-0.753</v>
+        <v>-2.25</v>
       </c>
       <c r="AQ25">
         <v>-0</v>
@@ -3576,7 +3582,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mogo Inc. (TSX:MOGO)</t>
+          <t>Givex Corp. (TSX:GIVX)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3584,35 +3590,32 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D26">
-        <v>0.158</v>
-      </c>
       <c r="G26">
-        <v>0.6200607902735562</v>
+        <v>-0.09183673469387756</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>-0.09183673469387756</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>-0.03962585034013606</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>-0.03962585034013606</v>
       </c>
       <c r="K26">
-        <v>-87.7</v>
+        <v>-2.52</v>
       </c>
       <c r="L26">
-        <v>-2.66565349544073</v>
+        <v>-0.04285714285714286</v>
       </c>
       <c r="M26">
-        <v>0.696</v>
+        <v>0.897</v>
       </c>
       <c r="N26">
-        <v>0.0166109785202864</v>
+        <v>0.01625</v>
       </c>
       <c r="O26">
-        <v>-0.007936145952109463</v>
+        <v>-0.355952380952381</v>
       </c>
       <c r="P26">
         <v>-0</v>
@@ -3624,67 +3627,79 @@
         <v>0</v>
       </c>
       <c r="S26">
-        <v>0.696</v>
+        <v>0.897</v>
       </c>
       <c r="T26">
         <v>1</v>
       </c>
       <c r="U26">
-        <v>25.7</v>
+        <v>17.3</v>
       </c>
       <c r="V26">
-        <v>0.6133651551312649</v>
+        <v>0.3134057971014493</v>
       </c>
       <c r="W26">
-        <v>-0.4111579934364745</v>
+        <v>-0.075</v>
       </c>
       <c r="X26">
-        <v>0.05941354142996655</v>
+        <v>0.05080001110975649</v>
       </c>
       <c r="Y26">
-        <v>-0.470571534866441</v>
+        <v>-0.1258000111097565</v>
       </c>
       <c r="Z26">
-        <v>0.1611954924056835</v>
+        <v>3.559322033898306</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>-0.1410411622276029</v>
       </c>
       <c r="AB26">
-        <v>0.06505075307052649</v>
+        <v>0.04955960502840966</v>
       </c>
       <c r="AC26">
-        <v>-0.06505075307052649</v>
+        <v>-0.1906007672560126</v>
       </c>
       <c r="AD26">
-        <v>67.5</v>
+        <v>6.7</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>67.5</v>
+        <v>6.7</v>
       </c>
       <c r="AG26">
-        <v>41.8</v>
+        <v>-10.6</v>
       </c>
       <c r="AH26">
-        <v>0.6170018281535649</v>
+        <v>0.1082390953150242</v>
       </c>
       <c r="AI26">
-        <v>0.3320216428922774</v>
+        <v>0.1638141809290953</v>
       </c>
       <c r="AJ26">
-        <v>0.4994026284348865</v>
+        <v>-0.2376681614349776</v>
       </c>
       <c r="AK26">
-        <v>0.2353603603603603</v>
+        <v>-0.4491525423728814</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>0.521</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>0.521</v>
+      </c>
+      <c r="AN26">
+        <v>-9.165526675786595</v>
+      </c>
+      <c r="AO26">
+        <v>-4.472168905950096</v>
+      </c>
+      <c r="AP26">
+        <v>14.50068399452805</v>
+      </c>
+      <c r="AQ26">
+        <v>-4.472168905950096</v>
       </c>
     </row>
     <row r="27">
@@ -3695,7 +3710,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Everyday People Financial Corp. (TSXV:EPF)</t>
+          <t>The Mint Corporation (TSXV:MIT)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3703,23 +3718,8 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="G27">
-        <v>-0.2767441860465116</v>
-      </c>
-      <c r="H27">
-        <v>-0.2767441860465116</v>
-      </c>
-      <c r="I27">
-        <v>-0.3631646371159258</v>
-      </c>
-      <c r="J27">
-        <v>-0.3631646371159258</v>
-      </c>
       <c r="K27">
-        <v>-13.5</v>
-      </c>
-      <c r="L27">
-        <v>-1.046511627906977</v>
+        <v>-1.42</v>
       </c>
       <c r="M27">
         <v>-0</v>
@@ -3743,73 +3743,61 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>0.47</v>
+        <v>0.004</v>
       </c>
       <c r="V27">
-        <v>0.01437308868501529</v>
+        <v>0.0006400000000000001</v>
       </c>
       <c r="W27">
-        <v>-0.391304347826087</v>
+        <v>-0.8502994011976048</v>
       </c>
       <c r="X27">
-        <v>0.04973936130287607</v>
+        <v>0.05008663792928595</v>
       </c>
       <c r="Y27">
-        <v>-0.4410437091289631</v>
+        <v>-0.9003860391268907</v>
       </c>
       <c r="Z27">
-        <v>0.7153107913270997</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>-0.259775583957412</v>
+        <v>-0.2443031266560678</v>
       </c>
       <c r="AB27">
-        <v>0.04868791282806543</v>
+        <v>0.05063251077392958</v>
       </c>
       <c r="AC27">
-        <v>-0.3084634967854774</v>
+        <v>-0.2949356374299974</v>
       </c>
       <c r="AD27">
-        <v>7.48</v>
+        <v>0.208</v>
       </c>
       <c r="AE27">
-        <v>0.01411909397721617</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>7.494119093977217</v>
+        <v>0.208</v>
       </c>
       <c r="AG27">
-        <v>7.024119093977217</v>
+        <v>0.204</v>
       </c>
       <c r="AH27">
-        <v>0.1864481487069125</v>
+        <v>0.0322081139671725</v>
       </c>
       <c r="AI27">
-        <v>0.225088372899251</v>
+        <v>0.4397463002114165</v>
       </c>
       <c r="AJ27">
-        <v>0.1768225263185806</v>
+        <v>0.03160830492717694</v>
       </c>
       <c r="AK27">
-        <v>0.213992615426077</v>
+        <v>0.4349680170575693</v>
       </c>
       <c r="AL27">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AM27">
-        <v>1.07</v>
-      </c>
-      <c r="AN27">
-        <v>-2.099943851768669</v>
-      </c>
-      <c r="AO27">
-        <v>-4.383177570093458</v>
-      </c>
-      <c r="AP27">
-        <v>-1.971959318915558</v>
-      </c>
-      <c r="AQ27">
-        <v>-4.383177570093458</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -3820,7 +3808,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FRNT Financial Inc. (TSXV:FRNT)</t>
+          <t>Mobilum Technologies Inc. (CNSX:MBLM)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3829,115 +3817,112 @@
         </is>
       </c>
       <c r="G28">
-        <v>-5.445783132530121</v>
+        <v>-6.783783783783783</v>
       </c>
       <c r="H28">
-        <v>-5.542168674698795</v>
+        <v>-7.147147147147146</v>
       </c>
       <c r="I28">
-        <v>-5.602409638554217</v>
+        <v>-4.204204204204204</v>
       </c>
       <c r="J28">
-        <v>-5.602409638554217</v>
+        <v>-4.204204204204204</v>
       </c>
       <c r="K28">
-        <v>-2.26</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="L28">
-        <v>-6.80722891566265</v>
+        <v>-24.14414414414414</v>
       </c>
       <c r="M28">
-        <v>0.031</v>
+        <v>-0</v>
       </c>
       <c r="N28">
-        <v>0.003510758776896942</v>
+        <v>-0</v>
       </c>
       <c r="O28">
-        <v>-0.01371681415929204</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>0.031</v>
+        <v>-0</v>
       </c>
       <c r="Q28">
-        <v>0.003510758776896942</v>
+        <v>-0</v>
       </c>
       <c r="R28">
-        <v>-0.01371681415929204</v>
+        <v>0</v>
       </c>
       <c r="S28">
         <v>0</v>
       </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
       <c r="U28">
-        <v>2.1</v>
+        <v>0.011</v>
       </c>
       <c r="V28">
-        <v>0.2378255945639864</v>
+        <v>0.00901639344262295</v>
       </c>
       <c r="W28">
-        <v>-0.5750636132315521</v>
+        <v>-1.03209242618742</v>
       </c>
       <c r="X28">
-        <v>0.0484187056673833</v>
+        <v>0.05417127165863331</v>
       </c>
       <c r="Y28">
-        <v>-0.6234823188989354</v>
+        <v>-1.086263697846053</v>
       </c>
       <c r="Z28">
-        <v>0.09405099150141642</v>
+        <v>0.103641456582633</v>
       </c>
       <c r="AA28">
-        <v>-0.5269121813031161</v>
+        <v>-0.4357298474945533</v>
       </c>
       <c r="AB28">
-        <v>0.04825043219884573</v>
+        <v>0.04898511901041185</v>
       </c>
       <c r="AC28">
-        <v>-0.5751626135019619</v>
+        <v>-0.4847149665049652</v>
       </c>
       <c r="AD28">
-        <v>0.358</v>
+        <v>0.656</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>0.358</v>
+        <v>0.656</v>
       </c>
       <c r="AG28">
-        <v>-1.742</v>
+        <v>0.645</v>
       </c>
       <c r="AH28">
-        <v>0.03896386591205921</v>
+        <v>0.349680170575693</v>
       </c>
       <c r="AI28">
-        <v>0.06059580230196344</v>
+        <v>-1.96996996996997</v>
       </c>
       <c r="AJ28">
-        <v>-0.2457674943566591</v>
+        <v>0.3458445040214477</v>
       </c>
       <c r="AK28">
-        <v>-0.4574579831932774</v>
+        <v>-1.875</v>
       </c>
       <c r="AL28">
-        <v>0.023</v>
+        <v>0.007</v>
       </c>
       <c r="AM28">
-        <v>0.023</v>
+        <v>0.007</v>
       </c>
       <c r="AN28">
-        <v>-0.1935135135135135</v>
+        <v>-0.4895522388059702</v>
       </c>
       <c r="AO28">
-        <v>-80.86956521739131</v>
+        <v>-200</v>
       </c>
       <c r="AP28">
-        <v>0.9416216216216216</v>
+        <v>-0.4813432835820896</v>
       </c>
       <c r="AQ28">
-        <v>-80.86956521739131</v>
+        <v>-200</v>
       </c>
     </row>
     <row r="29">
@@ -3948,7 +3933,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fineqia International Inc. (CNSX:FNQ)</t>
+          <t>FRNT Financial Inc. (TSXV:FRNT)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3956,8 +3941,23 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="G29">
+        <v>-7.438271604938272</v>
+      </c>
+      <c r="H29">
+        <v>-7.438271604938272</v>
+      </c>
+      <c r="I29">
+        <v>-6.882716049382716</v>
+      </c>
+      <c r="J29">
+        <v>-6.882716049382716</v>
+      </c>
       <c r="K29">
-        <v>-1.19</v>
+        <v>-1.98</v>
+      </c>
+      <c r="L29">
+        <v>-6.111111111111111</v>
       </c>
       <c r="M29">
         <v>-0</v>
@@ -3981,67 +3981,73 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>0.075</v>
+        <v>0.403</v>
       </c>
       <c r="V29">
-        <v>0.01164596273291925</v>
+        <v>0.04658959537572254</v>
       </c>
       <c r="W29">
-        <v>1.166666666666667</v>
+        <v>-0.3567567567567568</v>
       </c>
       <c r="X29">
-        <v>0.04877517592697738</v>
+        <v>0.04999220768538395</v>
       </c>
       <c r="Y29">
-        <v>1.117891490739689</v>
+        <v>-0.4067489644421407</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>0.0850840336134454</v>
       </c>
       <c r="AA29">
-        <v>-1.352459016393443</v>
+        <v>-0.5856092436974791</v>
       </c>
       <c r="AB29">
-        <v>0.04838341627112454</v>
+        <v>0.04988119391576001</v>
       </c>
       <c r="AC29">
-        <v>-1.400842432664567</v>
+        <v>-0.6354904376132391</v>
       </c>
       <c r="AD29">
-        <v>0.589</v>
+        <v>0.187</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>0.589</v>
+        <v>0.187</v>
       </c>
       <c r="AG29">
-        <v>0.514</v>
+        <v>-0.216</v>
       </c>
       <c r="AH29">
-        <v>0.08379570351401337</v>
+        <v>0.02116102749801969</v>
       </c>
       <c r="AI29">
-        <v>0.6239406779661016</v>
+        <v>0.04531136418706082</v>
       </c>
       <c r="AJ29">
-        <v>0.07391429393155018</v>
+        <v>-0.02561062366611335</v>
       </c>
       <c r="AK29">
-        <v>0.5914844649021864</v>
+        <v>-0.05800214822771215</v>
       </c>
       <c r="AL29">
-        <v>0.005</v>
+        <v>0.023</v>
       </c>
       <c r="AM29">
-        <v>0.002</v>
+        <v>0.023</v>
+      </c>
+      <c r="AN29">
+        <v>-0.08348214285714285</v>
       </c>
       <c r="AO29">
-        <v>-330</v>
+        <v>-96.95652173913044</v>
+      </c>
+      <c r="AP29">
+        <v>0.09642857142857143</v>
       </c>
       <c r="AQ29">
-        <v>-824.9999999999999</v>
+        <v>-96.95652173913044</v>
       </c>
     </row>
     <row r="30">
@@ -4052,7 +4058,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PowerBand Solutions Inc. (TSXV:PBX)</t>
+          <t>Fineqia International Inc. (CNSX:FNQ)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4060,26 +4066,8 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D30">
-        <v>1.557</v>
-      </c>
-      <c r="G30">
-        <v>-0.5442953020134228</v>
-      </c>
-      <c r="H30">
-        <v>-0.5442953020134228</v>
-      </c>
-      <c r="I30">
-        <v>-0.9060402684563759</v>
-      </c>
-      <c r="J30">
-        <v>-0.9060402684563759</v>
-      </c>
       <c r="K30">
-        <v>-19.7</v>
-      </c>
-      <c r="L30">
-        <v>-1.322147651006711</v>
+        <v>-2.71</v>
       </c>
       <c r="M30">
         <v>-0</v>
@@ -4103,73 +4091,73 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>13.3</v>
+        <v>0.007</v>
       </c>
       <c r="V30">
-        <v>0.9300699300699301</v>
+        <v>0.001284403669724771</v>
       </c>
       <c r="W30">
-        <v>-2.545219638242894</v>
+        <v>-2.239669421487603</v>
       </c>
       <c r="X30">
-        <v>0.05024498821415889</v>
+        <v>0.05220928615312419</v>
       </c>
       <c r="Y30">
-        <v>-2.595464626457053</v>
+        <v>-2.291878707640727</v>
       </c>
       <c r="Z30">
-        <v>2.299382716049382</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>-2.083333333333333</v>
+        <v>-1.38755980861244</v>
       </c>
       <c r="AB30">
-        <v>0.06544463092221775</v>
+        <v>0.04927453752613695</v>
       </c>
       <c r="AC30">
-        <v>-2.148777964255551</v>
+        <v>-1.436834346138577</v>
       </c>
       <c r="AD30">
-        <v>4.31</v>
+        <v>1.61</v>
       </c>
       <c r="AE30">
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>4.31</v>
+        <v>1.61</v>
       </c>
       <c r="AG30">
-        <v>-8.990000000000002</v>
+        <v>1.603</v>
       </c>
       <c r="AH30">
-        <v>0.2315959161740999</v>
+        <v>0.2280453257790368</v>
       </c>
       <c r="AI30">
-        <v>0.2579293836026331</v>
+        <v>1.808988764044944</v>
       </c>
       <c r="AJ30">
-        <v>-1.693032015065914</v>
+        <v>0.2272791719835531</v>
       </c>
       <c r="AK30">
-        <v>-2.636363636363638</v>
+        <v>1.815402038505096</v>
       </c>
       <c r="AL30">
-        <v>0.998</v>
+        <v>0.016</v>
       </c>
       <c r="AM30">
-        <v>0.998</v>
+        <v>0.016</v>
       </c>
       <c r="AN30">
-        <v>-0.3265151515151515</v>
+        <v>-0.7931034482758622</v>
       </c>
       <c r="AO30">
-        <v>-13.52705410821643</v>
+        <v>-126.875</v>
       </c>
       <c r="AP30">
-        <v>0.6810606060606063</v>
+        <v>-0.7896551724137932</v>
       </c>
       <c r="AQ30">
-        <v>-13.52705410821643</v>
+        <v>-126.875</v>
       </c>
     </row>
     <row r="31">
@@ -4180,7 +4168,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>WonderFi Technologies Inc. (TSX:WNDR)</t>
+          <t>Pineapple Financial Inc. (NYSEAM:PAPL)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4189,31 +4177,31 @@
         </is>
       </c>
       <c r="G31">
-        <v>-5.489406779661017</v>
+        <v>-1.194</v>
       </c>
       <c r="H31">
-        <v>-5.741525423728814</v>
+        <v>-1.3</v>
       </c>
       <c r="I31">
-        <v>-6.546610169491525</v>
+        <v>-1.329724233889179</v>
       </c>
       <c r="J31">
-        <v>-6.546610169491525</v>
+        <v>-1.329724233889179</v>
       </c>
       <c r="K31">
-        <v>-25.9</v>
+        <v>-2.81</v>
       </c>
       <c r="L31">
-        <v>-5.487288135593221</v>
+        <v>-1.124</v>
       </c>
       <c r="M31">
-        <v>3.75</v>
+        <v>-0</v>
       </c>
       <c r="N31">
-        <v>0.1689189189189189</v>
+        <v>-0</v>
       </c>
       <c r="O31">
-        <v>-0.1447876447876448</v>
+        <v>0</v>
       </c>
       <c r="P31">
         <v>-0</v>
@@ -4225,79 +4213,76 @@
         <v>0</v>
       </c>
       <c r="S31">
-        <v>3.75</v>
-      </c>
-      <c r="T31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>6.04</v>
+        <v>0.72</v>
       </c>
       <c r="V31">
-        <v>0.2720720720720721</v>
+        <v>0.05581395348837209</v>
       </c>
       <c r="W31">
-        <v>-1.321428571428571</v>
+        <v>-0.6069114470842333</v>
       </c>
       <c r="X31">
-        <v>0.04928594265307902</v>
+        <v>0.05076912223314514</v>
       </c>
       <c r="Y31">
-        <v>-1.37071451408165</v>
+        <v>-0.6576805693173784</v>
       </c>
       <c r="Z31">
-        <v>1.32920304139679</v>
+        <v>1.376232956111886</v>
       </c>
       <c r="AA31">
-        <v>-8.701774148127292</v>
+        <v>-1.830010313218918</v>
       </c>
       <c r="AB31">
-        <v>0.048553691562799</v>
+        <v>0.04956684756239318</v>
       </c>
       <c r="AC31">
-        <v>-8.75032783969009</v>
+        <v>-1.879577160781311</v>
       </c>
       <c r="AD31">
-        <v>3.65</v>
+        <v>0.43</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.086552923614738</v>
       </c>
       <c r="AF31">
-        <v>3.65</v>
+        <v>1.516552923614738</v>
       </c>
       <c r="AG31">
-        <v>-2.39</v>
+        <v>0.7965529236147377</v>
       </c>
       <c r="AH31">
-        <v>0.1411992263056093</v>
+        <v>0.1051952524053499</v>
       </c>
       <c r="AI31">
-        <v>0.02942361950826279</v>
+        <v>0.4586507334522974</v>
       </c>
       <c r="AJ31">
-        <v>-0.1206461383139829</v>
+        <v>0.05815718217985863</v>
       </c>
       <c r="AK31">
-        <v>-0.02025252097279891</v>
+        <v>0.3079592597322717</v>
       </c>
       <c r="AL31">
-        <v>0.012</v>
+        <v>0.065</v>
       </c>
       <c r="AM31">
-        <v>-0.03999999999999999</v>
+        <v>0.065</v>
       </c>
       <c r="AN31">
-        <v>-0.1346863468634686</v>
+        <v>-0.1415870925255186</v>
       </c>
       <c r="AO31">
-        <v>-2575</v>
+        <v>-51.07692307692307</v>
       </c>
       <c r="AP31">
-        <v>0.08819188191881919</v>
+        <v>-0.2622828197611912</v>
       </c>
       <c r="AQ31">
-        <v>772.5000000000001</v>
+        <v>-51.07692307692307</v>
       </c>
     </row>
     <row r="32">
@@ -4308,7 +4293,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CoinSmart Financial Inc. (NEOE:SMRT)</t>
+          <t>RevoluGROUP Canada Inc. (TSXV:REVO)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4316,32 +4301,35 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D32">
+        <v>-0.201</v>
+      </c>
       <c r="G32">
-        <v>0.2638095238095238</v>
+        <v>-5.070422535211268</v>
       </c>
       <c r="H32">
-        <v>0.2638095238095238</v>
+        <v>-5.070422535211268</v>
       </c>
       <c r="I32">
-        <v>-0.1523809523809524</v>
+        <v>-5.549295774647888</v>
       </c>
       <c r="J32">
-        <v>-0.1523809523809524</v>
+        <v>-5.549295774647888</v>
       </c>
       <c r="K32">
-        <v>-8.92</v>
+        <v>-2.19</v>
       </c>
       <c r="L32">
-        <v>-0.8495238095238096</v>
+        <v>-6.169014084507042</v>
       </c>
       <c r="M32">
-        <v>0.07099999999999999</v>
+        <v>-0</v>
       </c>
       <c r="N32">
-        <v>0.015203426124197</v>
+        <v>-0</v>
       </c>
       <c r="O32">
-        <v>-0.007959641255605381</v>
+        <v>0</v>
       </c>
       <c r="P32">
         <v>-0</v>
@@ -4353,70 +4341,70 @@
         <v>0</v>
       </c>
       <c r="S32">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="T32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>20.2</v>
+        <v>0.538</v>
       </c>
       <c r="V32">
-        <v>4.325481798715203</v>
+        <v>0.04521008403361345</v>
       </c>
       <c r="W32">
-        <v>-6.281690140845071</v>
+        <v>-1.610294117647059</v>
       </c>
       <c r="X32">
-        <v>0.04920526415369803</v>
+        <v>0.05000223774935845</v>
       </c>
       <c r="Y32">
-        <v>-6.330895404998769</v>
+        <v>-1.660296355396417</v>
+      </c>
+      <c r="Z32">
+        <v>0.566188197767145</v>
+      </c>
+      <c r="AA32">
+        <v>-3.14194577352472</v>
       </c>
       <c r="AB32">
-        <v>0.05386930416006125</v>
+        <v>0.04988478137507112</v>
+      </c>
+      <c r="AC32">
+        <v>-3.191830554899791</v>
       </c>
       <c r="AD32">
-        <v>0.714</v>
+        <v>0.272</v>
       </c>
       <c r="AE32">
         <v>0</v>
       </c>
       <c r="AF32">
-        <v>0.714</v>
+        <v>0.272</v>
       </c>
       <c r="AG32">
-        <v>-19.486</v>
+        <v>-0.266</v>
       </c>
       <c r="AH32">
-        <v>0.1326151560178306</v>
+        <v>0.0223463687150838</v>
       </c>
       <c r="AI32">
-        <v>0.09125766871165644</v>
+        <v>0.323040380047506</v>
       </c>
       <c r="AJ32">
-        <v>1.315199784017279</v>
+        <v>-0.02286401925391095</v>
       </c>
       <c r="AK32">
-        <v>1.574499030381383</v>
+        <v>-0.8750000000000002</v>
       </c>
       <c r="AL32">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="AM32">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="AN32">
-        <v>-0.4407407407407407</v>
-      </c>
-      <c r="AO32">
-        <v>-47.05882352941176</v>
+        <v>-0.1373737373737374</v>
       </c>
       <c r="AP32">
-        <v>12.02839506172839</v>
-      </c>
-      <c r="AQ32">
-        <v>-47.05882352941176</v>
+        <v>0.1343434343434343</v>
       </c>
     </row>
     <row r="33">
@@ -4427,7 +4415,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Automotive Finco Corp. (TSXV:AFCC.H)</t>
+          <t>XTM Inc. (CNSX:PAID)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4435,80 +4423,110 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="G33">
+        <v>-0.9867549668874172</v>
+      </c>
+      <c r="H33">
+        <v>-0.9867549668874172</v>
+      </c>
+      <c r="I33">
+        <v>-1.487858719646799</v>
+      </c>
+      <c r="J33">
+        <v>-1.487858719646799</v>
+      </c>
       <c r="K33">
-        <v>-0.6820000000000001</v>
+        <v>-8.44</v>
+      </c>
+      <c r="L33">
+        <v>-1.863134657836644</v>
       </c>
       <c r="M33">
-        <v>3.04</v>
+        <v>-0</v>
       </c>
       <c r="N33">
-        <v>0.1345132743362832</v>
+        <v>-0</v>
       </c>
       <c r="O33">
-        <v>-4.457478005865102</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>3.04</v>
+        <v>-0</v>
       </c>
       <c r="Q33">
-        <v>0.1345132743362832</v>
+        <v>-0</v>
       </c>
       <c r="R33">
-        <v>-4.457478005865102</v>
+        <v>0</v>
       </c>
       <c r="S33">
         <v>0</v>
       </c>
-      <c r="T33">
-        <v>0</v>
-      </c>
       <c r="U33">
-        <v>17.5</v>
+        <v>0.308</v>
       </c>
       <c r="V33">
-        <v>0.7743362831858407</v>
+        <v>0.02169014084507042</v>
       </c>
       <c r="W33">
-        <v>-0.03004405286343613</v>
+        <v>-2.299727520435967</v>
       </c>
       <c r="X33">
-        <v>0.04813485421146283</v>
+        <v>0.04992150609405421</v>
       </c>
       <c r="Y33">
-        <v>-0.07817890707489895</v>
+        <v>-2.349649026530021</v>
+      </c>
+      <c r="Z33">
+        <v>19.19491525423732</v>
+      </c>
+      <c r="AA33">
+        <v>-28.55932203389835</v>
       </c>
       <c r="AB33">
-        <v>0.04813485421146283</v>
+        <v>0.04985565712511784</v>
+      </c>
+      <c r="AC33">
+        <v>-28.60917769102346</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="AE33">
         <v>0</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="AG33">
-        <v>-17.5</v>
+        <v>-0.125</v>
       </c>
       <c r="AH33">
-        <v>0</v>
+        <v>0.01272335395953556</v>
       </c>
       <c r="AI33">
-        <v>0</v>
+        <v>0.159825327510917</v>
       </c>
       <c r="AJ33">
-        <v>-3.431372549019607</v>
+        <v>-0.008880994671403198</v>
       </c>
       <c r="AK33">
-        <v>58.33333333333319</v>
+        <v>-0.1493428912783752</v>
       </c>
       <c r="AL33">
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>0</v>
+        <v>-0.078</v>
+      </c>
+      <c r="AN33">
+        <v>-0.02703101920236337</v>
+      </c>
+      <c r="AP33">
+        <v>0.01846381093057607</v>
+      </c>
+      <c r="AQ33">
+        <v>86.41025641025641</v>
       </c>
     </row>
     <row r="34">
@@ -4519,7 +4537,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Mint Corporation (TSXV:MIT)</t>
+          <t>Everyday People Financial Corp. (TSXV:EPF)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4527,17 +4545,32 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="G34">
+        <v>-0.2</v>
+      </c>
+      <c r="H34">
+        <v>-0.2</v>
+      </c>
+      <c r="I34">
+        <v>-0.1187859595477099</v>
+      </c>
+      <c r="J34">
+        <v>-0.1187859595477099</v>
+      </c>
       <c r="K34">
-        <v>22.4</v>
+        <v>-17</v>
+      </c>
+      <c r="L34">
+        <v>-0.7203389830508474</v>
       </c>
       <c r="M34">
-        <v>-0</v>
+        <v>0.188</v>
       </c>
       <c r="N34">
-        <v>-0</v>
+        <v>0.004351851851851852</v>
       </c>
       <c r="O34">
-        <v>-0</v>
+        <v>-0.01105882352941177</v>
       </c>
       <c r="P34">
         <v>-0</v>
@@ -4546,64 +4579,189 @@
         <v>-0</v>
       </c>
       <c r="R34">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>0.188</v>
+      </c>
+      <c r="T34">
+        <v>1</v>
       </c>
       <c r="U34">
-        <v>0.02</v>
+        <v>1.13</v>
       </c>
       <c r="V34">
-        <v>0.001639344262295082</v>
-      </c>
-      <c r="W34">
-        <v>-0.9955555555555555</v>
+        <v>0.0261574074074074</v>
       </c>
       <c r="X34">
-        <v>0.0482708599767159</v>
-      </c>
-      <c r="Y34">
-        <v>-1.043826415532271</v>
+        <v>0.05373694213862876</v>
+      </c>
+      <c r="Z34">
+        <v>2009.669126216015</v>
+      </c>
+      <c r="AA34">
+        <v>-238.720475530977</v>
       </c>
       <c r="AB34">
-        <v>0.0495591273390636</v>
+        <v>0.05080432941211837</v>
+      </c>
+      <c r="AC34">
+        <v>-238.7712798603891</v>
       </c>
       <c r="AD34">
-        <v>0.237</v>
+        <v>20.9</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>0.01174322662976676</v>
       </c>
       <c r="AF34">
-        <v>0.237</v>
+        <v>20.91174322662977</v>
       </c>
       <c r="AG34">
-        <v>0.217</v>
+        <v>19.78174322662977</v>
       </c>
       <c r="AH34">
-        <v>0.019056042453968</v>
+        <v>0.3261764877100357</v>
       </c>
       <c r="AI34">
-        <v>0.124278972207656</v>
+        <v>0.7430862778550815</v>
       </c>
       <c r="AJ34">
-        <v>0.01747604091165338</v>
+        <v>0.3140869435043789</v>
       </c>
       <c r="AK34">
-        <v>0.1149973502914679</v>
+        <v>0.7323386373348818</v>
       </c>
       <c r="AL34">
-        <v>0.921</v>
+        <v>1.22</v>
       </c>
       <c r="AM34">
-        <v>0.921</v>
+        <v>1.167</v>
+      </c>
+      <c r="AN34">
+        <v>-13.3888532991672</v>
       </c>
       <c r="AO34">
-        <v>-0.3159609120521172</v>
+        <v>-2.30327868852459</v>
+      </c>
+      <c r="AP34">
+        <v>-12.67248124704021</v>
       </c>
       <c r="AQ34">
-        <v>-0.3159609120521172</v>
+        <v>-2.407883461868038</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>WonderFi Technologies Inc. (TSX:WNDR)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G35">
+        <v>-1.222988505747127</v>
+      </c>
+      <c r="H35">
+        <v>-1.672413793103448</v>
+      </c>
+      <c r="I35">
+        <v>-1.28735632183908</v>
+      </c>
+      <c r="J35">
+        <v>-1.28735632183908</v>
+      </c>
+      <c r="K35">
+        <v>-32.5</v>
+      </c>
+      <c r="L35">
+        <v>-1.867816091954023</v>
+      </c>
+      <c r="M35">
+        <v>25.8</v>
+      </c>
+      <c r="N35">
+        <v>0.1774415405777166</v>
+      </c>
+      <c r="O35">
+        <v>-0.7938461538461539</v>
+      </c>
+      <c r="P35">
+        <v>-0</v>
+      </c>
+      <c r="Q35">
+        <v>-0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>25.8</v>
+      </c>
+      <c r="T35">
+        <v>1</v>
+      </c>
+      <c r="U35">
+        <v>18.5</v>
+      </c>
+      <c r="V35">
+        <v>0.1272352132049518</v>
+      </c>
+      <c r="X35">
+        <v>0.04992686271536334</v>
+      </c>
+      <c r="AB35">
+        <v>0.04978534243478205</v>
+      </c>
+      <c r="AD35">
+        <v>1.97</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>1.97</v>
+      </c>
+      <c r="AG35">
+        <v>-16.53</v>
+      </c>
+      <c r="AH35">
+        <v>0.01336771391735088</v>
+      </c>
+      <c r="AI35">
+        <v>0.02603409541429893</v>
+      </c>
+      <c r="AJ35">
+        <v>-0.128268798013502</v>
+      </c>
+      <c r="AK35">
+        <v>-0.2891376596116845</v>
+      </c>
+      <c r="AL35">
+        <v>2.4</v>
+      </c>
+      <c r="AM35">
+        <v>1.8</v>
+      </c>
+      <c r="AN35">
+        <v>-0.0933649289099526</v>
+      </c>
+      <c r="AO35">
+        <v>-9.333333333333334</v>
+      </c>
+      <c r="AP35">
+        <v>0.7834123222748816</v>
+      </c>
+      <c r="AQ35">
+        <v>-12.44444444444444</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/canada/canada_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,115 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.163</v>
+        <v>0.0486</v>
       </c>
       <c r="E2">
-        <v>0.31</v>
+        <v>0.0598</v>
       </c>
       <c r="F2">
         <v>0.223</v>
       </c>
       <c r="G2">
-        <v>0.044362292051756</v>
+        <v>0.195025253912923</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.1761215532709432</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.1740511183563092</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.1570005051509493</v>
       </c>
       <c r="K2">
-        <v>210.1</v>
+        <v>781.467</v>
       </c>
       <c r="L2">
-        <v>0.3530499075785582</v>
+        <v>0.2333857565064067</v>
       </c>
       <c r="M2">
-        <v>55.05</v>
+        <v>503.017</v>
       </c>
       <c r="N2">
-        <v>0.02840264162625116</v>
+        <v>0.03140676119137116</v>
       </c>
       <c r="O2">
-        <v>0.2620180866254165</v>
+        <v>0.6436829706180811</v>
       </c>
       <c r="P2">
-        <v>51.2</v>
+        <v>461.396</v>
       </c>
       <c r="Q2">
-        <v>0.02641626251160871</v>
+        <v>0.02880808001847629</v>
       </c>
       <c r="R2">
-        <v>0.2436934792955736</v>
+        <v>0.5904228841397013</v>
       </c>
       <c r="S2">
-        <v>3.850000000000001</v>
+        <v>41.621</v>
       </c>
       <c r="T2">
-        <v>0.06993642143505906</v>
+        <v>0.08274273036497772</v>
       </c>
       <c r="U2">
-        <v>111.8</v>
+        <v>662.222</v>
       </c>
       <c r="V2">
-        <v>0.05768238571870807</v>
+        <v>0.04134700856963521</v>
       </c>
       <c r="W2">
-        <v>0.2807322287546766</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="X2">
-        <v>0.06634415817175722</v>
+        <v>0.05964404389344573</v>
       </c>
       <c r="Y2">
-        <v>0.2143880705829194</v>
+        <v>0.02835595610655427</v>
       </c>
       <c r="Z2">
-        <v>0.2301860519088694</v>
+        <v>0.07082315789526826</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05699424463012514</v>
+        <v>0.05457439083255105</v>
       </c>
       <c r="AC2">
-        <v>-0.05699424463012514</v>
+        <v>-0.0489731334065909</v>
       </c>
       <c r="AD2">
-        <v>2583.6</v>
+        <v>46445.34</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.9731385234059474</v>
       </c>
       <c r="AF2">
-        <v>2583.6</v>
+        <v>46446.31313852341</v>
       </c>
       <c r="AG2">
-        <v>2471.8</v>
+        <v>45784.09113852341</v>
       </c>
       <c r="AH2">
-        <v>0.5713653854659648</v>
+        <v>0.7435869942013413</v>
       </c>
       <c r="AI2">
-        <v>0.7453050627434011</v>
+        <v>0.8636328048855123</v>
       </c>
       <c r="AJ2">
-        <v>0.5604988662131518</v>
+        <v>0.740839396614822</v>
       </c>
       <c r="AK2">
-        <v>0.7368170030107014</v>
+        <v>0.8619327134522318</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>104.632</v>
       </c>
       <c r="AM2">
-        <v>-16.5</v>
+        <v>66.476</v>
+      </c>
+      <c r="AN2">
+        <v>66.80005005112983</v>
+      </c>
+      <c r="AO2">
+        <v>5.569701429772919</v>
+      </c>
+      <c r="AP2">
+        <v>65.84900830952799</v>
       </c>
       <c r="AQ2">
-        <v>-0</v>
+        <v>8.766607497442687</v>
       </c>
     </row>
     <row r="3">
@@ -707,124 +716,2865 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Payfare Inc. (TSX:PAY)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G3">
+        <v>0.05545171339563863</v>
+      </c>
+      <c r="H3">
+        <v>0.05545171339563863</v>
+      </c>
+      <c r="I3">
+        <v>0.0778816199376947</v>
+      </c>
+      <c r="J3">
+        <v>0.07727468041680094</v>
+      </c>
+      <c r="K3">
+        <v>14.3</v>
+      </c>
+      <c r="L3">
+        <v>0.08909657320872275</v>
+      </c>
+      <c r="M3">
+        <v>0.141</v>
+      </c>
+      <c r="N3">
+        <v>0.001093871217998448</v>
+      </c>
+      <c r="O3">
+        <v>0.009860139860139859</v>
+      </c>
+      <c r="P3">
+        <v>-0</v>
+      </c>
+      <c r="Q3">
+        <v>-0</v>
+      </c>
+      <c r="R3">
+        <v>-0</v>
+      </c>
+      <c r="S3">
+        <v>0.141</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
+        <v>53.6</v>
+      </c>
+      <c r="V3">
+        <v>0.4158262218774244</v>
+      </c>
+      <c r="W3">
+        <v>0.2960662525879917</v>
+      </c>
+      <c r="X3">
+        <v>0.05617309272742672</v>
+      </c>
+      <c r="Y3">
+        <v>0.239893159860565</v>
+      </c>
+      <c r="Z3">
+        <v>24.31818181818184</v>
+      </c>
+      <c r="AA3">
+        <v>1.879179728317661</v>
+      </c>
+      <c r="AB3">
+        <v>0.05617649718145321</v>
+      </c>
+      <c r="AC3">
+        <v>1.823003231136208</v>
+      </c>
+      <c r="AD3">
+        <v>0.044</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0.044</v>
+      </c>
+      <c r="AG3">
+        <v>-53.556</v>
+      </c>
+      <c r="AH3">
+        <v>0.0003412334036480952</v>
+      </c>
+      <c r="AI3">
+        <v>0.0006806509498174619</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.7108197069441496</v>
+      </c>
+      <c r="AK3">
+        <v>-4.849329952915615</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>-1.47</v>
+      </c>
+      <c r="AN3">
+        <v>0.00352</v>
+      </c>
+      <c r="AP3">
+        <v>-4.28448</v>
+      </c>
+      <c r="AQ3">
+        <v>-8.503401360544219</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Propel Holdings Inc. (TSX:PRL)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="F4">
+        <v>0.42</v>
+      </c>
+      <c r="G4">
+        <v>0.1554514889529299</v>
+      </c>
+      <c r="H4">
+        <v>0.1460134486071085</v>
+      </c>
+      <c r="I4">
+        <v>0.2144572526416907</v>
+      </c>
+      <c r="J4">
+        <v>0.1557067783885889</v>
+      </c>
+      <c r="K4">
+        <v>43.3</v>
+      </c>
+      <c r="L4">
+        <v>0.1039865513928915</v>
+      </c>
+      <c r="M4">
+        <v>12.5</v>
+      </c>
+      <c r="N4">
+        <v>0.01266977498479627</v>
+      </c>
+      <c r="O4">
+        <v>0.2886836027713626</v>
+      </c>
+      <c r="P4">
+        <v>12.5</v>
+      </c>
+      <c r="Q4">
+        <v>0.01266977498479627</v>
+      </c>
+      <c r="R4">
+        <v>0.2886836027713626</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>17</v>
+      </c>
+      <c r="V4">
+        <v>0.01723089397932293</v>
+      </c>
+      <c r="W4">
+        <v>0.4557894736842105</v>
+      </c>
+      <c r="X4">
+        <v>0.05812049210938829</v>
+      </c>
+      <c r="Y4">
+        <v>0.3976689815748222</v>
+      </c>
+      <c r="Z4">
+        <v>1.599508316367687</v>
+      </c>
+      <c r="AA4">
+        <v>0.2490542869473684</v>
+      </c>
+      <c r="AB4">
+        <v>0.05493493681607949</v>
+      </c>
+      <c r="AC4">
+        <v>0.1941193501312889</v>
+      </c>
+      <c r="AD4">
+        <v>252.4</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>252.4</v>
+      </c>
+      <c r="AG4">
+        <v>235.4</v>
+      </c>
+      <c r="AH4">
+        <v>0.2037126715092817</v>
+      </c>
+      <c r="AI4">
+        <v>0.6633377135348226</v>
+      </c>
+      <c r="AJ4">
+        <v>0.1926350245499182</v>
+      </c>
+      <c r="AK4">
+        <v>0.6475928473177441</v>
+      </c>
+      <c r="AL4">
+        <v>29.8</v>
+      </c>
+      <c r="AM4">
+        <v>29.8</v>
+      </c>
+      <c r="AN4">
+        <v>2.820111731843575</v>
+      </c>
+      <c r="AO4">
+        <v>2.996644295302013</v>
+      </c>
+      <c r="AP4">
+        <v>2.630167597765363</v>
+      </c>
+      <c r="AQ4">
+        <v>2.996644295302013</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dominion Lending Centres Inc. (TSX:DLCG)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>-0.0441</v>
+      </c>
+      <c r="G5">
+        <v>0.3865384615384616</v>
+      </c>
+      <c r="H5">
+        <v>0.3865384615384616</v>
+      </c>
+      <c r="I5">
+        <v>0.3557692307692308</v>
+      </c>
+      <c r="J5">
+        <v>0.2199839743589744</v>
+      </c>
+      <c r="K5">
+        <v>7.39</v>
+      </c>
+      <c r="L5">
+        <v>0.1421153846153846</v>
+      </c>
+      <c r="M5">
+        <v>4.96</v>
+      </c>
+      <c r="N5">
+        <v>0.01906958861976163</v>
+      </c>
+      <c r="O5">
+        <v>0.6711772665764547</v>
+      </c>
+      <c r="P5">
+        <v>4.28</v>
+      </c>
+      <c r="Q5">
+        <v>0.01645520953479431</v>
+      </c>
+      <c r="R5">
+        <v>0.5791610284167795</v>
+      </c>
+      <c r="S5">
+        <v>0.6799999999999997</v>
+      </c>
+      <c r="T5">
+        <v>0.1370967741935483</v>
+      </c>
+      <c r="U5">
+        <v>7.31</v>
+      </c>
+      <c r="V5">
+        <v>0.02810457516339869</v>
+      </c>
+      <c r="W5">
+        <v>0.3405529953917051</v>
+      </c>
+      <c r="X5">
+        <v>0.05936183896315215</v>
+      </c>
+      <c r="Y5">
+        <v>0.2811911564285529</v>
+      </c>
+      <c r="Z5">
+        <v>0.5948295584534431</v>
+      </c>
+      <c r="AA5">
+        <v>0.1308529703347823</v>
+      </c>
+      <c r="AB5">
+        <v>0.05383823648866091</v>
+      </c>
+      <c r="AC5">
+        <v>0.0770147338461214</v>
+      </c>
+      <c r="AD5">
+        <v>108.9</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>108.9</v>
+      </c>
+      <c r="AG5">
+        <v>101.59</v>
+      </c>
+      <c r="AH5">
+        <v>0.2951219512195122</v>
+      </c>
+      <c r="AI5">
+        <v>0.813293502613891</v>
+      </c>
+      <c r="AJ5">
+        <v>0.2808758881915452</v>
+      </c>
+      <c r="AK5">
+        <v>0.8025120467651473</v>
+      </c>
+      <c r="AL5">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AM5">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AN5">
+        <v>4.391129032258065</v>
+      </c>
+      <c r="AO5">
+        <v>1.907216494845361</v>
+      </c>
+      <c r="AP5">
+        <v>4.096370967741936</v>
+      </c>
+      <c r="AQ5">
+        <v>1.907216494845361</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Automotive Finco Corp. (TSXV:AFCC.H)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>-0.153</v>
+      </c>
+      <c r="E6">
+        <v>-0.0857</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0.8558139534883722</v>
+      </c>
+      <c r="J6">
+        <v>0.8558139534883722</v>
+      </c>
+      <c r="K6">
+        <v>1.54</v>
+      </c>
+      <c r="L6">
+        <v>0.7162790697674419</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>-0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>-0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0.243</v>
+      </c>
+      <c r="V6">
+        <v>0.02209090909090909</v>
+      </c>
+      <c r="W6">
+        <v>0.08800000000000001</v>
+      </c>
+      <c r="X6">
+        <v>0.05617049085253012</v>
+      </c>
+      <c r="Y6">
+        <v>0.03182950914746989</v>
+      </c>
+      <c r="Z6">
+        <v>0.1251309509952276</v>
+      </c>
+      <c r="AA6">
+        <v>0.1070888138749855</v>
+      </c>
+      <c r="AB6">
+        <v>0.05617049085253012</v>
+      </c>
+      <c r="AC6">
+        <v>0.05091832302245534</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>-0.243</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.02258994143348517</v>
+      </c>
+      <c r="AK6">
+        <v>-0.01288646126107016</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>WonderFi Technologies Inc. (TSX:WNDR)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>0.0112</v>
+      </c>
+      <c r="H7">
+        <v>-0.07546666666666667</v>
+      </c>
+      <c r="I7">
+        <v>0.1085333333333333</v>
+      </c>
+      <c r="J7">
+        <v>0.09883567901234568</v>
+      </c>
+      <c r="K7">
+        <v>1.96</v>
+      </c>
+      <c r="L7">
+        <v>0.05226666666666666</v>
+      </c>
+      <c r="M7">
+        <v>0.956</v>
+      </c>
+      <c r="N7">
+        <v>0.007209653092006033</v>
+      </c>
+      <c r="O7">
+        <v>0.4877551020408163</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>-0</v>
+      </c>
+      <c r="S7">
+        <v>0.956</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>23.9</v>
+      </c>
+      <c r="V7">
+        <v>0.1802413273001508</v>
+      </c>
+      <c r="W7">
+        <v>0.02659430122116689</v>
+      </c>
+      <c r="X7">
+        <v>0.05618112529818376</v>
+      </c>
+      <c r="Y7">
+        <v>-0.02958682407701687</v>
+      </c>
+      <c r="Z7">
+        <v>1.063226538134392</v>
+      </c>
+      <c r="AA7">
+        <v>0.1050847168404583</v>
+      </c>
+      <c r="AB7">
+        <v>0.05618047309213516</v>
+      </c>
+      <c r="AC7">
+        <v>0.0489042437483231</v>
+      </c>
+      <c r="AD7">
+        <v>0.185</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0.185</v>
+      </c>
+      <c r="AG7">
+        <v>-23.715</v>
+      </c>
+      <c r="AH7">
+        <v>0.001393229656964265</v>
+      </c>
+      <c r="AI7">
+        <v>0.002441116315893646</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.2177985948477752</v>
+      </c>
+      <c r="AK7">
+        <v>-0.4570685169124025</v>
+      </c>
+      <c r="AL7">
+        <v>0.078</v>
+      </c>
+      <c r="AM7">
+        <v>-3.012</v>
+      </c>
+      <c r="AN7">
+        <v>0.0275297619047619</v>
+      </c>
+      <c r="AO7">
+        <v>52.17948717948718</v>
+      </c>
+      <c r="AP7">
+        <v>-3.529017857142857</v>
+      </c>
+      <c r="AQ7">
+        <v>-1.351261620185923</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TMX Group Limited (TSX:X)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.109</v>
+      </c>
+      <c r="E8">
+        <v>0.08539999999999999</v>
+      </c>
+      <c r="F8">
+        <v>0.122</v>
+      </c>
+      <c r="G8">
+        <v>0.5014810426540285</v>
+      </c>
+      <c r="H8">
+        <v>0.4841034755134281</v>
+      </c>
+      <c r="I8">
+        <v>0.439178515007899</v>
+      </c>
+      <c r="J8">
+        <v>0.3427785206632541</v>
+      </c>
+      <c r="K8">
+        <v>301</v>
+      </c>
+      <c r="L8">
+        <v>0.2971958925750395</v>
+      </c>
+      <c r="M8">
+        <v>181</v>
+      </c>
+      <c r="N8">
+        <v>0.02117132396804417</v>
+      </c>
+      <c r="O8">
+        <v>0.6013289036544851</v>
+      </c>
+      <c r="P8">
+        <v>151.8</v>
+      </c>
+      <c r="Q8">
+        <v>0.01775583965938732</v>
+      </c>
+      <c r="R8">
+        <v>0.5043189368770764</v>
+      </c>
+      <c r="S8">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="T8">
+        <v>0.1613259668508287</v>
+      </c>
+      <c r="U8">
+        <v>321.9</v>
+      </c>
+      <c r="V8">
+        <v>0.03765220544372054</v>
+      </c>
+      <c r="W8">
+        <v>0.09938913653623906</v>
+      </c>
+      <c r="X8">
+        <v>0.05771504902564354</v>
+      </c>
+      <c r="Y8">
+        <v>0.04167408751059552</v>
+      </c>
+      <c r="Z8">
+        <v>0.2778219722946098</v>
+      </c>
+      <c r="AA8">
+        <v>0.09523140467089392</v>
+      </c>
+      <c r="AB8">
+        <v>0.05440549071018744</v>
+      </c>
+      <c r="AC8">
+        <v>0.04082591396070647</v>
+      </c>
+      <c r="AD8">
+        <v>1732.4</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>1732.4</v>
+      </c>
+      <c r="AG8">
+        <v>1410.5</v>
+      </c>
+      <c r="AH8">
+        <v>0.1684935370609919</v>
+      </c>
+      <c r="AI8">
+        <v>0.3364471461032025</v>
+      </c>
+      <c r="AJ8">
+        <v>0.1416193096246913</v>
+      </c>
+      <c r="AK8">
+        <v>0.2921983758700696</v>
+      </c>
+      <c r="AL8">
+        <v>33.8</v>
+      </c>
+      <c r="AM8">
+        <v>16.9</v>
+      </c>
+      <c r="AN8">
+        <v>3.150963986904329</v>
+      </c>
+      <c r="AO8">
+        <v>13.15976331360947</v>
+      </c>
+      <c r="AP8">
+        <v>2.565478355765733</v>
+      </c>
+      <c r="AQ8">
+        <v>26.31952662721894</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Findev Inc. (TSXV:FDI)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="E9">
+        <v>0.0726</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0.9345454545454545</v>
+      </c>
+      <c r="J9">
+        <v>0.6271096681096681</v>
+      </c>
+      <c r="K9">
+        <v>1.7</v>
+      </c>
+      <c r="L9">
+        <v>0.6181818181818182</v>
+      </c>
+      <c r="M9">
+        <v>0.636</v>
+      </c>
+      <c r="N9">
+        <v>0.06</v>
+      </c>
+      <c r="O9">
+        <v>0.3741176470588236</v>
+      </c>
+      <c r="P9">
+        <v>0.636</v>
+      </c>
+      <c r="Q9">
+        <v>0.06</v>
+      </c>
+      <c r="R9">
+        <v>0.3741176470588236</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0.008</v>
+      </c>
+      <c r="V9">
+        <v>0.0007547169811320755</v>
+      </c>
+      <c r="W9">
+        <v>0.09392265193370165</v>
+      </c>
+      <c r="X9">
+        <v>0.05617049085253012</v>
+      </c>
+      <c r="Y9">
+        <v>0.03775216108117153</v>
+      </c>
+      <c r="Z9">
+        <v>0.1538203378453966</v>
+      </c>
+      <c r="AA9">
+        <v>0.09646222101474367</v>
+      </c>
+      <c r="AB9">
+        <v>0.05617049085253012</v>
+      </c>
+      <c r="AC9">
+        <v>0.04029173016221355</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>-0.008</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.0007552870090634441</v>
+      </c>
+      <c r="AK9">
+        <v>-0.0004168403501458941</v>
+      </c>
+      <c r="AL9">
+        <v>0.001</v>
+      </c>
+      <c r="AM9">
+        <v>0.001</v>
+      </c>
+      <c r="AO9">
+        <v>2570</v>
+      </c>
+      <c r="AQ9">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Solution Financial Inc. (TSX:SFI)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.0429</v>
+      </c>
+      <c r="E10">
+        <v>0.847</v>
+      </c>
+      <c r="G10">
+        <v>0.07454350161117078</v>
+      </c>
+      <c r="H10">
+        <v>0.07454350161117078</v>
+      </c>
+      <c r="I10">
+        <v>0.08259935553168636</v>
+      </c>
+      <c r="J10">
+        <v>0.08259935553168636</v>
+      </c>
+      <c r="K10">
+        <v>0.277</v>
+      </c>
+      <c r="L10">
+        <v>0.02975295381310419</v>
+      </c>
+      <c r="M10">
+        <v>0.33</v>
+      </c>
+      <c r="N10">
+        <v>0.01864406779661017</v>
+      </c>
+      <c r="O10">
+        <v>1.191335740072202</v>
+      </c>
+      <c r="P10">
+        <v>0.25</v>
+      </c>
+      <c r="Q10">
+        <v>0.01412429378531073</v>
+      </c>
+      <c r="R10">
+        <v>0.9025270758122743</v>
+      </c>
+      <c r="S10">
+        <v>0.08000000000000002</v>
+      </c>
+      <c r="T10">
+        <v>0.2424242424242425</v>
+      </c>
+      <c r="U10">
+        <v>0.407</v>
+      </c>
+      <c r="V10">
+        <v>0.02299435028248588</v>
+      </c>
+      <c r="W10">
+        <v>0.02861570247933885</v>
+      </c>
+      <c r="X10">
+        <v>0.06077832844065007</v>
+      </c>
+      <c r="Y10">
+        <v>-0.03216262596131123</v>
+      </c>
+      <c r="Z10">
+        <v>0.5195892398705212</v>
+      </c>
+      <c r="AA10">
+        <v>0.04291773635450385</v>
+      </c>
+      <c r="AB10">
+        <v>0.05319307265491219</v>
+      </c>
+      <c r="AC10">
+        <v>-0.01027533630040834</v>
+      </c>
+      <c r="AD10">
+        <v>10.7</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>10.7</v>
+      </c>
+      <c r="AG10">
+        <v>10.293</v>
+      </c>
+      <c r="AH10">
+        <v>0.3767605633802817</v>
+      </c>
+      <c r="AI10">
+        <v>0.5387713997985901</v>
+      </c>
+      <c r="AJ10">
+        <v>0.3676990676240489</v>
+      </c>
+      <c r="AK10">
+        <v>0.5291214722664884</v>
+      </c>
+      <c r="AL10">
+        <v>0.724</v>
+      </c>
+      <c r="AM10">
+        <v>0.724</v>
+      </c>
+      <c r="AN10">
+        <v>13.71794871794872</v>
+      </c>
+      <c r="AO10">
+        <v>1.062154696132597</v>
+      </c>
+      <c r="AP10">
+        <v>13.19615384615384</v>
+      </c>
+      <c r="AQ10">
+        <v>1.062154696132597</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Montfort Capital Corp. (TSXV:MONT)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G11">
+        <v>0.6373937677053825</v>
+      </c>
+      <c r="H11">
+        <v>0.6373937677053825</v>
+      </c>
+      <c r="I11">
+        <v>0.509915014164306</v>
+      </c>
+      <c r="J11">
+        <v>0.509915014164306</v>
+      </c>
+      <c r="K11">
+        <v>-9.77</v>
+      </c>
+      <c r="L11">
+        <v>-0.2767705382436261</v>
+      </c>
+      <c r="M11">
+        <v>2.54</v>
+      </c>
+      <c r="N11">
+        <v>0.9169675090252708</v>
+      </c>
+      <c r="O11">
+        <v>-0.2599795291709314</v>
+      </c>
+      <c r="P11">
+        <v>2.54</v>
+      </c>
+      <c r="Q11">
+        <v>0.9169675090252708</v>
+      </c>
+      <c r="R11">
+        <v>-0.2599795291709314</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="V11">
+        <v>3.108303249097473</v>
+      </c>
+      <c r="W11">
+        <v>-6.557046979865771</v>
+      </c>
+      <c r="X11">
+        <v>0.8860942923779696</v>
+      </c>
+      <c r="Y11">
+        <v>-7.443141272243741</v>
+      </c>
+      <c r="Z11">
+        <v>0.1540744620487975</v>
+      </c>
+      <c r="AA11">
+        <v>0.07856488149797042</v>
+      </c>
+      <c r="AB11">
+        <v>0.09444181354892715</v>
+      </c>
+      <c r="AC11">
+        <v>-0.01587693205095674</v>
+      </c>
+      <c r="AD11">
+        <v>301.6</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>301.6</v>
+      </c>
+      <c r="AG11">
+        <v>292.99</v>
+      </c>
+      <c r="AH11">
+        <v>0.9908992344843448</v>
+      </c>
+      <c r="AI11">
+        <v>0.9343246592317225</v>
+      </c>
+      <c r="AJ11">
+        <v>0.990634298079524</v>
+      </c>
+      <c r="AK11">
+        <v>0.9325249053120723</v>
+      </c>
+      <c r="AL11">
+        <v>28.4</v>
+      </c>
+      <c r="AM11">
+        <v>28.4</v>
+      </c>
+      <c r="AN11">
+        <v>15.79057591623037</v>
+      </c>
+      <c r="AO11">
+        <v>0.6338028169014085</v>
+      </c>
+      <c r="AP11">
+        <v>15.33979057591623</v>
+      </c>
+      <c r="AQ11">
+        <v>0.6338028169014085</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>First National Financial Corporation (TSX:FN)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.0552</v>
+      </c>
+      <c r="E12">
+        <v>0.0285</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>136.7</v>
+      </c>
+      <c r="L12">
+        <v>0.2888841927303465</v>
+      </c>
+      <c r="M12">
+        <v>108.6</v>
+      </c>
+      <c r="N12">
+        <v>0.06459287456135135</v>
+      </c>
+      <c r="O12">
+        <v>0.7944403803950257</v>
+      </c>
+      <c r="P12">
+        <v>108.6</v>
+      </c>
+      <c r="Q12">
+        <v>0.06459287456135135</v>
+      </c>
+      <c r="R12">
+        <v>0.7944403803950257</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0.2620279854322407</v>
+      </c>
+      <c r="X12">
+        <v>0.2216230986924701</v>
+      </c>
+      <c r="Y12">
+        <v>0.04040488673977058</v>
+      </c>
+      <c r="Z12">
+        <v>0.01431891355394708</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.04615664323666709</v>
+      </c>
+      <c r="AC12">
+        <v>-0.04615664323666709</v>
+      </c>
+      <c r="AD12">
+        <v>36494.9</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>36494.9</v>
+      </c>
+      <c r="AG12">
+        <v>36494.9</v>
+      </c>
+      <c r="AH12">
+        <v>0.9559594721318517</v>
+      </c>
+      <c r="AI12">
+        <v>0.9851903842779436</v>
+      </c>
+      <c r="AJ12">
+        <v>0.9559594721318517</v>
+      </c>
+      <c r="AK12">
+        <v>0.9851903842779436</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MCAN Mortgage Corporation (TSX:MKP)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.155</v>
+      </c>
+      <c r="E13">
+        <v>0.168</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="L13">
+        <v>0.6384615384615385</v>
+      </c>
+      <c r="M13">
+        <v>31.3</v>
+      </c>
+      <c r="N13">
+        <v>0.06382544861337684</v>
+      </c>
+      <c r="O13">
+        <v>0.4713855421686747</v>
+      </c>
+      <c r="P13">
+        <v>31.3</v>
+      </c>
+      <c r="Q13">
+        <v>0.06382544861337684</v>
+      </c>
+      <c r="R13">
+        <v>0.4713855421686747</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>64.2</v>
+      </c>
+      <c r="V13">
+        <v>0.1309135399673736</v>
+      </c>
+      <c r="W13">
+        <v>0.1702127659574468</v>
+      </c>
+      <c r="X13">
+        <v>0.08244912223510337</v>
+      </c>
+      <c r="Y13">
+        <v>0.08776364372234344</v>
+      </c>
+      <c r="Z13">
+        <v>0.05899370355663963</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.04805055735367231</v>
+      </c>
+      <c r="AC13">
+        <v>-0.04805055735367231</v>
+      </c>
+      <c r="AD13">
+        <v>1690.7</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>1690.7</v>
+      </c>
+      <c r="AG13">
+        <v>1626.5</v>
+      </c>
+      <c r="AH13">
+        <v>0.7751593232772455</v>
+      </c>
+      <c r="AI13">
+        <v>0.7914521112255408</v>
+      </c>
+      <c r="AJ13">
+        <v>0.7683404978978695</v>
+      </c>
+      <c r="AK13">
+        <v>0.7849903474903475</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Accord Financial Corp. (TSX:ACD)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.0162</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>-6.56</v>
+      </c>
+      <c r="L14">
+        <v>-0.2116129032258064</v>
+      </c>
+      <c r="M14">
+        <v>-0</v>
+      </c>
+      <c r="N14">
+        <v>-0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>-0</v>
+      </c>
+      <c r="Q14">
+        <v>-0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>6.57</v>
+      </c>
+      <c r="V14">
+        <v>0.2856521739130435</v>
+      </c>
+      <c r="W14">
+        <v>-0.09632892804698973</v>
+      </c>
+      <c r="X14">
+        <v>0.1339512012555859</v>
+      </c>
+      <c r="Y14">
+        <v>-0.2302801293025756</v>
+      </c>
+      <c r="Z14">
+        <v>0.08559516249275201</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.0489731334065909</v>
+      </c>
+      <c r="AC14">
+        <v>-0.0489731334065909</v>
+      </c>
+      <c r="AD14">
+        <v>234.7</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>234.7</v>
+      </c>
+      <c r="AG14">
+        <v>228.13</v>
+      </c>
+      <c r="AH14">
+        <v>0.9107489328676756</v>
+      </c>
+      <c r="AI14">
+        <v>0.7836393989983305</v>
+      </c>
+      <c r="AJ14">
+        <v>0.9084139688607494</v>
+      </c>
+      <c r="AK14">
+        <v>0.778786740859591</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Timbercreek Financial Corp. (TSX:TF)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.04190000000000001</v>
+      </c>
+      <c r="E15">
+        <v>0.01</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>43.5</v>
+      </c>
+      <c r="L15">
+        <v>0.6807511737089202</v>
+      </c>
+      <c r="M15">
+        <v>47.53</v>
+      </c>
+      <c r="N15">
+        <v>0.1165236577592547</v>
+      </c>
+      <c r="O15">
+        <v>1.09264367816092</v>
+      </c>
+      <c r="P15">
+        <v>41.5</v>
+      </c>
+      <c r="Q15">
+        <v>0.1017406227016426</v>
+      </c>
+      <c r="R15">
+        <v>0.9540229885057471</v>
+      </c>
+      <c r="S15">
+        <v>6.030000000000001</v>
+      </c>
+      <c r="T15">
+        <v>0.1268672417420577</v>
+      </c>
+      <c r="U15">
+        <v>4.65</v>
+      </c>
+      <c r="V15">
+        <v>0.01139985290512381</v>
+      </c>
+      <c r="W15">
+        <v>0.08375048132460532</v>
+      </c>
+      <c r="X15">
+        <v>0.06802721109709696</v>
+      </c>
+      <c r="Y15">
+        <v>0.01572327022750836</v>
+      </c>
+      <c r="Z15">
+        <v>0.04825555052106933</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0.04979433797631029</v>
+      </c>
+      <c r="AC15">
+        <v>-0.04979433797631029</v>
+      </c>
+      <c r="AD15">
+        <v>634.5</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>634.5</v>
+      </c>
+      <c r="AG15">
+        <v>629.85</v>
+      </c>
+      <c r="AH15">
+        <v>0.608691481197237</v>
+      </c>
+      <c r="AI15">
+        <v>0.5509725599166377</v>
+      </c>
+      <c r="AJ15">
+        <v>0.6069380872079018</v>
+      </c>
+      <c r="AK15">
+        <v>0.5491520990452941</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Chesswood Group Limited (OTCPK:CHWW.Q)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.08689999999999999</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>-27.3</v>
+      </c>
+      <c r="L16">
+        <v>-0.3796940194714882</v>
+      </c>
+      <c r="M16">
+        <v>5.29</v>
+      </c>
+      <c r="N16">
+        <v>480.9090909090909</v>
+      </c>
+      <c r="O16">
+        <v>-0.1937728937728938</v>
+      </c>
+      <c r="P16">
+        <v>5.29</v>
+      </c>
+      <c r="Q16">
+        <v>480.9090909090909</v>
+      </c>
+      <c r="R16">
+        <v>-0.1937728937728938</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>12.9</v>
+      </c>
+      <c r="V16">
+        <v>1172.727272727273</v>
+      </c>
+      <c r="W16">
+        <v>-0.1756756756756757</v>
+      </c>
+      <c r="X16">
+        <v>839.9655243389018</v>
+      </c>
+      <c r="Y16">
+        <v>-840.1412000145774</v>
+      </c>
+      <c r="Z16">
+        <v>0.04080590238365493</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0.05010536581859337</v>
+      </c>
+      <c r="AC16">
+        <v>-0.05010536581859337</v>
+      </c>
+      <c r="AD16">
+        <v>1212.1</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>1212.1</v>
+      </c>
+      <c r="AG16">
+        <v>1199.2</v>
+      </c>
+      <c r="AH16">
+        <v>0.9999909249235425</v>
+      </c>
+      <c r="AI16">
+        <v>0.8993841359352972</v>
+      </c>
+      <c r="AJ16">
+        <v>0.9999908273022846</v>
+      </c>
+      <c r="AK16">
+        <v>0.898411747078214</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Atrium Mortgage Investment Corporation (TSX:AI)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>0.0474</v>
+      </c>
+      <c r="E17">
+        <v>0.047</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>34.8</v>
+      </c>
+      <c r="L17">
+        <v>0.8169014084507041</v>
+      </c>
+      <c r="M17">
+        <v>18.08</v>
+      </c>
+      <c r="N17">
+        <v>0.05060173523649594</v>
+      </c>
+      <c r="O17">
+        <v>0.5195402298850575</v>
+      </c>
+      <c r="P17">
+        <v>17.8</v>
+      </c>
+      <c r="Q17">
+        <v>0.0498180800447803</v>
+      </c>
+      <c r="R17">
+        <v>0.5114942528735633</v>
+      </c>
+      <c r="S17">
+        <v>0.2800000000000011</v>
+      </c>
+      <c r="T17">
+        <v>0.01548672566371687</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0.09573590096286107</v>
+      </c>
+      <c r="X17">
+        <v>0.06251494992043863</v>
+      </c>
+      <c r="Y17">
+        <v>0.03322095104242244</v>
+      </c>
+      <c r="Z17">
+        <v>0.06723484848484848</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0.0514120999031201</v>
+      </c>
+      <c r="AC17">
+        <v>-0.0514120999031201</v>
+      </c>
+      <c r="AD17">
+        <v>297.4</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>297.4</v>
+      </c>
+      <c r="AG17">
+        <v>297.4</v>
+      </c>
+      <c r="AH17">
+        <v>0.4542538567282724</v>
+      </c>
+      <c r="AI17">
+        <v>0.4487024743512372</v>
+      </c>
+      <c r="AJ17">
+        <v>0.4542538567282724</v>
+      </c>
+      <c r="AK17">
+        <v>0.4487024743512372</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Firm Capital Mortgage Investment Corporation (TSX:FC)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>0.0498</v>
+      </c>
+      <c r="E18">
+        <v>0.0464</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>25.5</v>
+      </c>
+      <c r="L18">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="M18">
+        <v>25.4</v>
+      </c>
+      <c r="N18">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="O18">
+        <v>0.9960784313725489</v>
+      </c>
+      <c r="P18">
+        <v>25.4</v>
+      </c>
+      <c r="Q18">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="R18">
+        <v>0.9960784313725489</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0.08606142423219709</v>
+      </c>
+      <c r="X18">
+        <v>0.05964404389344573</v>
+      </c>
+      <c r="Y18">
+        <v>0.02641738033875136</v>
+      </c>
+      <c r="Z18">
+        <v>0.07396664249456128</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0.05289124245824264</v>
+      </c>
+      <c r="AC18">
+        <v>-0.05289124245824264</v>
+      </c>
+      <c r="AD18">
+        <v>138.9</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>138.9</v>
+      </c>
+      <c r="AG18">
+        <v>138.9</v>
+      </c>
+      <c r="AH18">
+        <v>0.3130493576741041</v>
+      </c>
+      <c r="AI18">
+        <v>0.3063520070577856</v>
+      </c>
+      <c r="AJ18">
+        <v>0.3130493576741041</v>
+      </c>
+      <c r="AK18">
+        <v>0.3063520070577856</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ECN Capital Corp. (TSX:ECN)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>-0.103</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>-44.9</v>
+      </c>
+      <c r="L19">
+        <v>-0.3464506172839506</v>
+      </c>
+      <c r="M19">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="N19">
+        <v>0.0134434726271461</v>
+      </c>
+      <c r="O19">
+        <v>-0.1848552338530067</v>
+      </c>
+      <c r="P19">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Q19">
+        <v>0.0134434726271461</v>
+      </c>
+      <c r="R19">
+        <v>-0.1848552338530067</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>20.3</v>
+      </c>
+      <c r="V19">
+        <v>0.03287981859410431</v>
+      </c>
+      <c r="W19">
+        <v>-0.3218637992831541</v>
+      </c>
+      <c r="X19">
+        <v>0.06440885816906983</v>
+      </c>
+      <c r="Y19">
+        <v>-0.3862726574522239</v>
+      </c>
+      <c r="Z19">
+        <v>0.1354798243780054</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0.05302010970155189</v>
+      </c>
+      <c r="AC19">
+        <v>-0.05302010970155189</v>
+      </c>
+      <c r="AD19">
+        <v>667.3</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>667.3</v>
+      </c>
+      <c r="AG19">
+        <v>647</v>
+      </c>
+      <c r="AH19">
+        <v>0.5194208764692146</v>
+      </c>
+      <c r="AI19">
+        <v>0.7559759827801065</v>
+      </c>
+      <c r="AJ19">
+        <v>0.5117051565960139</v>
+      </c>
+      <c r="AK19">
+        <v>0.7502319109461967</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Mogo Inc. (TSX:MOGO)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>0.168</v>
+      </c>
+      <c r="G20">
+        <v>0.3709677419354839</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>-11.5</v>
+      </c>
+      <c r="L20">
+        <v>-0.3709677419354839</v>
+      </c>
+      <c r="M20">
+        <v>0.404</v>
+      </c>
+      <c r="N20">
+        <v>0.01278481012658228</v>
+      </c>
+      <c r="O20">
+        <v>-0.0351304347826087</v>
+      </c>
+      <c r="P20">
+        <v>-0</v>
+      </c>
+      <c r="Q20">
+        <v>-0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0.404</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>7.23</v>
+      </c>
+      <c r="V20">
+        <v>0.2287974683544304</v>
+      </c>
+      <c r="W20">
+        <v>-0.1822503961965135</v>
+      </c>
+      <c r="X20">
+        <v>0.07170456724536749</v>
+      </c>
+      <c r="Y20">
+        <v>-0.253954963441881</v>
+      </c>
+      <c r="Z20">
+        <v>0.3625730994152047</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0.05520805963493347</v>
+      </c>
+      <c r="AC20">
+        <v>-0.05520805963493347</v>
+      </c>
+      <c r="AD20">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AG20">
+        <v>57.17</v>
+      </c>
+      <c r="AH20">
+        <v>0.6708333333333334</v>
+      </c>
+      <c r="AI20">
+        <v>0.5518423307626393</v>
+      </c>
+      <c r="AJ20">
+        <v>0.6440238819420975</v>
+      </c>
+      <c r="AK20">
+        <v>0.522243537042112</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>goeasy Ltd. (TSX:GSY)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D21">
         <v>0.163</v>
       </c>
-      <c r="E3">
+      <c r="E21">
         <v>0.31</v>
       </c>
-      <c r="F3">
+      <c r="F21">
         <v>0.223</v>
       </c>
-      <c r="G3">
+      <c r="G21">
         <v>0.044362292051756</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
         <v>210.1</v>
       </c>
-      <c r="L3">
+      <c r="L21">
         <v>0.3530499075785582</v>
       </c>
-      <c r="M3">
+      <c r="M21">
         <v>55.05</v>
       </c>
-      <c r="N3">
+      <c r="N21">
         <v>0.02840264162625116</v>
       </c>
-      <c r="O3">
+      <c r="O21">
         <v>0.2620180866254165</v>
       </c>
-      <c r="P3">
+      <c r="P21">
         <v>51.2</v>
       </c>
-      <c r="Q3">
+      <c r="Q21">
         <v>0.02641626251160871</v>
       </c>
-      <c r="R3">
+      <c r="R21">
         <v>0.2436934792955736</v>
       </c>
-      <c r="S3">
+      <c r="S21">
         <v>3.850000000000001</v>
       </c>
-      <c r="T3">
+      <c r="T21">
         <v>0.06993642143505906</v>
       </c>
-      <c r="U3">
+      <c r="U21">
         <v>111.8</v>
       </c>
-      <c r="V3">
+      <c r="V21">
         <v>0.05768238571870807</v>
       </c>
-      <c r="W3">
+      <c r="W21">
         <v>0.2807322287546766</v>
       </c>
-      <c r="X3">
-        <v>0.06634415817175722</v>
-      </c>
-      <c r="Y3">
-        <v>0.2143880705829194</v>
-      </c>
-      <c r="Z3">
+      <c r="X21">
+        <v>0.06633095010464479</v>
+      </c>
+      <c r="Y21">
+        <v>0.2144012786500318</v>
+      </c>
+      <c r="Z21">
         <v>0.2301860519088694</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.05699424463012514</v>
-      </c>
-      <c r="AC3">
-        <v>-0.05699424463012514</v>
-      </c>
-      <c r="AD3">
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0.05698858319536966</v>
+      </c>
+      <c r="AC21">
+        <v>-0.05698858319536966</v>
+      </c>
+      <c r="AD21">
         <v>2583.6</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
         <v>2583.6</v>
       </c>
-      <c r="AG3">
+      <c r="AG21">
         <v>2471.8</v>
       </c>
-      <c r="AH3">
+      <c r="AH21">
         <v>0.5713653854659648</v>
       </c>
-      <c r="AI3">
+      <c r="AI21">
         <v>0.7453050627434011</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ21">
         <v>0.5604988662131518</v>
       </c>
-      <c r="AK3">
+      <c r="AK21">
         <v>0.7368170030107014</v>
       </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
         <v>-16.5</v>
       </c>
-      <c r="AQ3">
-        <v>-0</v>
+      <c r="AQ21">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Everyday People Financial Corp. (TSXV:EPF)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>-0.0648018648018648</v>
+      </c>
+      <c r="H22">
+        <v>-0.0648018648018648</v>
+      </c>
+      <c r="I22">
+        <v>-0.0268065268065268</v>
+      </c>
+      <c r="J22">
+        <v>-0.01619114219114219</v>
+      </c>
+      <c r="K22">
+        <v>1.51</v>
+      </c>
+      <c r="L22">
+        <v>0.0351981351981352</v>
+      </c>
+      <c r="M22">
+        <v>-0</v>
+      </c>
+      <c r="N22">
+        <v>-0</v>
+      </c>
+      <c r="O22">
+        <v>-0</v>
+      </c>
+      <c r="P22">
+        <v>-0</v>
+      </c>
+      <c r="Q22">
+        <v>-0</v>
+      </c>
+      <c r="R22">
+        <v>-0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0.497</v>
+      </c>
+      <c r="V22">
+        <v>0.01218137254901961</v>
+      </c>
+      <c r="W22">
+        <v>0.2088520055325034</v>
+      </c>
+      <c r="X22">
+        <v>0.05962668568996342</v>
+      </c>
+      <c r="Y22">
+        <v>0.14922531984254</v>
+      </c>
+      <c r="Z22">
+        <v>2.067469879518072</v>
+      </c>
+      <c r="AA22">
+        <v>-0.03347469879518072</v>
+      </c>
+      <c r="AB22">
+        <v>0.05572290937859203</v>
+      </c>
+      <c r="AC22">
+        <v>-0.08919760817377274</v>
+      </c>
+      <c r="AD22">
+        <v>18.5</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>18.5</v>
+      </c>
+      <c r="AG22">
+        <v>18.003</v>
+      </c>
+      <c r="AH22">
+        <v>0.3119730185497471</v>
+      </c>
+      <c r="AI22">
+        <v>0.6401384083044983</v>
+      </c>
+      <c r="AJ22">
+        <v>0.3061578490893322</v>
+      </c>
+      <c r="AK22">
+        <v>0.6338414956166603</v>
+      </c>
+      <c r="AL22">
+        <v>1.78</v>
+      </c>
+      <c r="AM22">
+        <v>1.656</v>
+      </c>
+      <c r="AN22">
+        <v>87.26415094339623</v>
+      </c>
+      <c r="AO22">
+        <v>-0.646067415730337</v>
+      </c>
+      <c r="AP22">
+        <v>84.91981132075472</v>
+      </c>
+      <c r="AQ22">
+        <v>-0.6944444444444443</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FRNT Financial Inc. (TSXV:FRNT)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>-1.683760683760684</v>
+      </c>
+      <c r="H23">
+        <v>-1.683760683760684</v>
+      </c>
+      <c r="I23">
+        <v>-1.846153846153846</v>
+      </c>
+      <c r="J23">
+        <v>-1.846153846153846</v>
+      </c>
+      <c r="K23">
+        <v>-1.84</v>
+      </c>
+      <c r="L23">
+        <v>-1.572649572649573</v>
+      </c>
+      <c r="M23">
+        <v>-0</v>
+      </c>
+      <c r="N23">
+        <v>-0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>-0</v>
+      </c>
+      <c r="Q23">
+        <v>-0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0.489</v>
+      </c>
+      <c r="V23">
+        <v>0.03443661971830986</v>
+      </c>
+      <c r="W23">
+        <v>-0.467005076142132</v>
+      </c>
+      <c r="X23">
+        <v>0.0562032345819226</v>
+      </c>
+      <c r="Y23">
+        <v>-0.5232083107240546</v>
+      </c>
+      <c r="Z23">
+        <v>0.3141783029001074</v>
+      </c>
+      <c r="AA23">
+        <v>-0.5800214822771215</v>
+      </c>
+      <c r="AB23">
+        <v>0.05620113765257</v>
+      </c>
+      <c r="AC23">
+        <v>-0.6362226199296914</v>
+      </c>
+      <c r="AD23">
+        <v>0.061</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0.061</v>
+      </c>
+      <c r="AG23">
+        <v>-0.428</v>
+      </c>
+      <c r="AH23">
+        <v>0.004277399901830166</v>
+      </c>
+      <c r="AI23">
+        <v>0.01853539957459739</v>
+      </c>
+      <c r="AJ23">
+        <v>-0.03107754864943364</v>
+      </c>
+      <c r="AK23">
+        <v>-0.1527480371163455</v>
+      </c>
+      <c r="AL23">
+        <v>0.012</v>
+      </c>
+      <c r="AM23">
+        <v>0.012</v>
+      </c>
+      <c r="AN23">
+        <v>-0.02824074074074074</v>
+      </c>
+      <c r="AO23">
+        <v>-180</v>
+      </c>
+      <c r="AP23">
+        <v>0.1981481481481481</v>
+      </c>
+      <c r="AQ23">
+        <v>-180</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Fineqia International Inc. (CNSX:FNQ)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G24">
+        <v>-102.2727272727273</v>
+      </c>
+      <c r="H24">
+        <v>-102.2727272727273</v>
+      </c>
+      <c r="I24">
+        <v>-110.9090909090909</v>
+      </c>
+      <c r="J24">
+        <v>-110.9090909090909</v>
+      </c>
+      <c r="K24">
+        <v>-2.54</v>
+      </c>
+      <c r="L24">
+        <v>-115.4545454545455</v>
+      </c>
+      <c r="M24">
+        <v>-0</v>
+      </c>
+      <c r="N24">
+        <v>-0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>-0</v>
+      </c>
+      <c r="Q24">
+        <v>-0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0.028</v>
+      </c>
+      <c r="V24">
+        <v>0.004878048780487805</v>
+      </c>
+      <c r="W24">
+        <v>3.527777777777778</v>
+      </c>
+      <c r="X24">
+        <v>0.05889274470131928</v>
+      </c>
+      <c r="Y24">
+        <v>3.468885033076459</v>
+      </c>
+      <c r="Z24">
+        <v>0.02491506228765571</v>
+      </c>
+      <c r="AA24">
+        <v>-1</v>
+      </c>
+      <c r="AB24">
+        <v>0.05457439083255105</v>
+      </c>
+      <c r="AC24">
+        <v>-1.054574390832551</v>
+      </c>
+      <c r="AD24">
+        <v>2.05</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>2.05</v>
+      </c>
+      <c r="AG24">
+        <v>2.022</v>
+      </c>
+      <c r="AH24">
+        <v>0.2631578947368421</v>
+      </c>
+      <c r="AI24">
+        <v>12.81250000000001</v>
+      </c>
+      <c r="AJ24">
+        <v>0.2604998711672249</v>
+      </c>
+      <c r="AK24">
+        <v>15.31818181818183</v>
+      </c>
+      <c r="AL24">
+        <v>0.051</v>
+      </c>
+      <c r="AM24">
+        <v>-0.021</v>
+      </c>
+      <c r="AN24">
+        <v>-0.8401639344262295</v>
+      </c>
+      <c r="AO24">
+        <v>-47.84313725490196</v>
+      </c>
+      <c r="AP24">
+        <v>-0.8286885245901638</v>
+      </c>
+      <c r="AQ24">
+        <v>116.1904761904762</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pineapple Financial Inc. (NYSEAM:PAPL)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>-1.160966542750929</v>
+      </c>
+      <c r="H25">
+        <v>-1.390334572490706</v>
+      </c>
+      <c r="I25">
+        <v>-1.415474983152859</v>
+      </c>
+      <c r="J25">
+        <v>-1.415474983152859</v>
+      </c>
+      <c r="K25">
+        <v>-4.1</v>
+      </c>
+      <c r="L25">
+        <v>-1.524163568773234</v>
+      </c>
+      <c r="M25">
+        <v>-0</v>
+      </c>
+      <c r="N25">
+        <v>-0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>-0</v>
+      </c>
+      <c r="Q25">
+        <v>-0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0.58</v>
+      </c>
+      <c r="V25">
+        <v>0.1457286432160804</v>
+      </c>
+      <c r="W25">
+        <v>-2.290502793296089</v>
+      </c>
+      <c r="X25">
+        <v>0.05803420046411081</v>
+      </c>
+      <c r="Y25">
+        <v>-2.3485369937602</v>
+      </c>
+      <c r="Z25">
+        <v>1.087686748858449</v>
+      </c>
+      <c r="AA25">
+        <v>-1</v>
+      </c>
+      <c r="AB25">
+        <v>0.05497887055857278</v>
+      </c>
+      <c r="AC25">
+        <v>-1.054978870558573</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0.9731385234059474</v>
+      </c>
+      <c r="AF25">
+        <v>0.9731385234059474</v>
+      </c>
+      <c r="AG25">
+        <v>0.3931385234059475</v>
+      </c>
+      <c r="AH25">
+        <v>0.1964690708340586</v>
+      </c>
+      <c r="AI25">
+        <v>0.4188895813148634</v>
+      </c>
+      <c r="AJ25">
+        <v>0.08989848396107014</v>
+      </c>
+      <c r="AK25">
+        <v>0.2255348717999689</v>
+      </c>
+      <c r="AL25">
+        <v>0.286</v>
+      </c>
+      <c r="AM25">
+        <v>0.286</v>
+      </c>
+      <c r="AN25">
+        <v>-0</v>
+      </c>
+      <c r="AO25">
+        <v>-13.39160839160839</v>
+      </c>
+      <c r="AP25">
+        <v>-0.1115919737172715</v>
+      </c>
+      <c r="AQ25">
+        <v>-13.39160839160839</v>
       </c>
     </row>
   </sheetData>
